--- a/計画-事例集.xlsx
+++ b/計画-事例集.xlsx
@@ -1625,22 +1625,130 @@
     <t>十字形プランを 8 枚の HP シェルで構成。</t>
   </si>
   <si>
+    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/03_18.png</t>
+  </si>
+  <si>
+    <t>/03_18.png</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>モントリオール万博アメリカ館</t>
+  </si>
+  <si>
+    <t>R.バックミンスター・フラー</t>
+  </si>
+  <si>
+    <t>カナダ</t>
+  </si>
+  <si>
+    <t>「ジオデシック・ド ー ム」の実施例の 1 つで、多数の均質な構造材を組み上げた巨大なド ー ム状構造物である。</t>
+  </si>
+  <si>
+    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/03_19.png</t>
+  </si>
+  <si>
+    <t>/03_19.png</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>ロンシャンの教会</t>
+  </si>
+  <si>
+    <t>ル・コルビュジエ</t>
+  </si>
+  <si>
+    <t>フランス・ロンシャン</t>
+  </si>
+  <si>
+    <t>白い塔、覆いかぶさるニ重の打放しのコンクリ ー トの屋根、壁に任意の配置で開けられた窓をもつ、コンクリ ー トの重量感を生かした建築。</t>
+  </si>
+  <si>
+    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/03_20.png</t>
+  </si>
+  <si>
+    <t>/03_20.png</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>イリノイ工科大学</t>
+  </si>
+  <si>
+    <t>ミース・ファン・デル・ローエ</t>
+  </si>
+  <si>
+    <t>アメリカ・シカゴ</t>
+  </si>
+  <si>
+    <t>鉄とガラスを使った校舎群。クラウンホ ー ルが特に有名。</t>
+  </si>
+  <si>
+    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/03_21.png</t>
+  </si>
+  <si>
+    <t>/03_21.png</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>旧開智学校校舎</t>
+  </si>
+  <si>
+    <t>立石清重</t>
+  </si>
+  <si>
+    <t>近現代</t>
+  </si>
+  <si>
+    <t>長野県松本市</t>
+  </si>
+  <si>
+    <t>地元の大工棟梁の設計・施工により、1876 年に竣工し、アーチや隅石などの洋風の意匠と、瓦屋根や唐破風などの和風の意匠とが混在した様式であり、疑洋風とよばれている。</t>
+  </si>
+  <si>
+    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_01.png</t>
+  </si>
+  <si>
+    <t>/04_01.png</t>
+  </si>
+  <si>
+    <t>豊平館</t>
+  </si>
+  <si>
+    <t>安達喜幸</t>
+  </si>
+  <si>
+    <t>北海道札幌市</t>
+  </si>
+  <si>
+    <t>北方開拓使の宿舎として 1880 年に竣工し,後に民営のホテルとして営業した木造総 2 階建ての宿泊施設であり,中央人口の上部に架かる半円形に張り出したバルコニ ー をコリント式の柱で支えている。</t>
+  </si>
+  <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_02.png</t>
   </si>
   <si>
     <t>/04_02.png</t>
   </si>
   <si>
-    <t>モントリオール万博アメリカ館</t>
-  </si>
-  <si>
-    <t>R.バックミンスター・フラー</t>
-  </si>
-  <si>
-    <t>カナダ</t>
-  </si>
-  <si>
-    <t>「ジオデシック・ド ー ム」の実施例の 1 つで、多数の均質な構造材を組み上げた巨大なド ー ム状構造物である。</t>
+    <t>迎賓館赤坂離宮</t>
+  </si>
+  <si>
+    <t>片山東熊</t>
+  </si>
+  <si>
+    <t>東京都</t>
+  </si>
+  <si>
+    <t>ネオバロック様式の洋風建築</t>
+  </si>
+  <si>
+    <t>地下 1 階・地上 2 階建,石造および煉瓦造によるネオバロック様式の洋風建築で,設計者は片山東熊である。皇太子(後の大正天皇)の東宮御所として建設され, 1969 年から 5 年にわたり村野藤吾により改修が行われ,現在は国の迎賓施設として使用されている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_03.png</t>
@@ -1649,16 +1757,19 @@
     <t>/04_03.png</t>
   </si>
   <si>
-    <t>ロンシャンの教会</t>
-  </si>
-  <si>
-    <t>ル・コルビュジエ</t>
-  </si>
-  <si>
-    <t>フランス・ロンシャン</t>
-  </si>
-  <si>
-    <t>白い塔、覆いかぶさるニ重の打放しのコンクリ ー トの屋根、壁に任意の配置で開けられた窓をもつ、コンクリ ー トの重量感を生かした建築。</t>
+    <t>作成中-4_歴史的建造物の保全・活用 [31問]</t>
+  </si>
+  <si>
+    <t>首里城復元事業</t>
+  </si>
+  <si>
+    <t>保全・活用</t>
+  </si>
+  <si>
+    <t>沖縄県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1992 年に復元事業が完成した。また、今帰仁城跡や首里城跡等は、「琉球王国のグスク(城)及び関連遺産群」として 2000 年にユネスコの世界遺産に登録されている。 </t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_04.png</t>
@@ -1667,37 +1778,28 @@
     <t>/04_04.png</t>
   </si>
   <si>
-    <t>イリノイ工科大学</t>
-  </si>
-  <si>
-    <t>ミース・ファン・デル・ローエ</t>
-  </si>
-  <si>
-    <t>アメリカ・シカゴ</t>
-  </si>
-  <si>
-    <t>鉄とガラスを使った校舎群。クラウンホ ー ルが特に有名。</t>
+    <t>サッポロファクトリー</t>
+  </si>
+  <si>
+    <t>公共空間(アトリウム)や地下通路等で結び付けて、店舗・ホテル・事務所・映画館等の複合商業施設としている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_05.png</t>
   </si>
   <si>
-    <t>/04_05.png</t>
-  </si>
-  <si>
-    <t>旧開智学校校舎</t>
-  </si>
-  <si>
-    <t>立石清重</t>
-  </si>
-  <si>
-    <t>近現代</t>
-  </si>
-  <si>
-    <t>長野県松本市</t>
-  </si>
-  <si>
-    <t>地元の大工棟梁の設計・施工により、1876 年に竣工し、アーチや隅石などの洋風の意匠と、瓦屋根や唐破風などの和風の意匠とが混在した様式であり、疑洋風とよばれている。</t>
+    <t>04_05.png</t>
+  </si>
+  <si>
+    <t>倉敷アイビースクエア</t>
+  </si>
+  <si>
+    <t>浦辺鎮太郎</t>
+  </si>
+  <si>
+    <t>岡山県倉敷市</t>
+  </si>
+  <si>
+    <t>紡績工場をホテルや展示などの複合商業施設に再生した近代産業遺産の保存活用事例。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_06.png</t>
@@ -1706,16 +1808,7 @@
     <t>/04_06.png</t>
   </si>
   <si>
-    <t>豊平館</t>
-  </si>
-  <si>
-    <t>安達喜幸</t>
-  </si>
-  <si>
-    <t>北海道札幌市</t>
-  </si>
-  <si>
-    <t>北方開拓使の宿舎として 1880 年に竣工し,後に民営のホテルとして営業した木造総 2 階建ての宿泊施設であり,中央人口の上部に架かる半円形に張り出したバルコニ ー をコリント式の柱で支えている。</t>
+    <t>横浜赤レンガ倉庫</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_07.png</t>
@@ -1724,19 +1817,7 @@
     <t>/04_07.png</t>
   </si>
   <si>
-    <t>迎賓館赤坂離宮</t>
-  </si>
-  <si>
-    <t>片山東熊</t>
-  </si>
-  <si>
-    <t>東京都</t>
-  </si>
-  <si>
-    <t>ネオバロック様式の洋風建築</t>
-  </si>
-  <si>
-    <t>地下 1 階・地上 2 階建,石造および煉瓦造によるネオバロック様式の洋風建築で,設計者は片山東熊である。皇太子(後の大正天皇)の東宮御所として建設され, 1969 年から 5 年にわたり村野藤吾により改修が行われ,現在は国の迎賓施設として使用されている。</t>
+    <t>同潤会青山アパート</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_08.png</t>
@@ -1745,19 +1826,7 @@
     <t>/04_08.png</t>
   </si>
   <si>
-    <t>作成中-4_歴史的建造物の保全・活用 [31問]</t>
-  </si>
-  <si>
-    <t>首里城復元事業</t>
-  </si>
-  <si>
-    <t>保全・活用</t>
-  </si>
-  <si>
-    <t>沖縄県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1992 年に復元事業が完成した。また、今帰仁城跡や首里城跡等は、「琉球王国のグスク(城)及び関連遺産群」として 2000 年にユネスコの世界遺産に登録されている。 </t>
+    <t>アートプラザ</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_09.png</t>
@@ -1766,10 +1835,7 @@
     <t>/04_09.png</t>
   </si>
   <si>
-    <t>サッポロファクトリー</t>
-  </si>
-  <si>
-    <t>公共空間(アトリウム)や地下通路等で結び付けて、店舗・ホテル・事務所・映画館等の複合商業施設としている。</t>
+    <t>京都文化博物館別館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_10.png</t>
@@ -1778,16 +1844,7 @@
     <t>/04_10.png</t>
   </si>
   <si>
-    <t>倉敷アイビースクエア</t>
-  </si>
-  <si>
-    <t>浦辺鎮太郎</t>
-  </si>
-  <si>
-    <t>岡山県倉敷市</t>
-  </si>
-  <si>
-    <t>紡績工場をホテルや展示などの複合商業施設に再生した近代産業遺産の保存活用事例。</t>
+    <t>旧東京国立近代美術館工芸館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_11.png</t>
@@ -1796,7 +1853,7 @@
     <t>/04_11.png</t>
   </si>
   <si>
-    <t>横浜赤レンガ倉庫</t>
+    <t>国立西洋美術館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_12.png</t>
@@ -1805,7 +1862,7 @@
     <t>/04_12.png</t>
   </si>
   <si>
-    <t>同潤会青山アパート</t>
+    <t>名古屋市市政資料館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_13.png</t>
@@ -1814,7 +1871,7 @@
     <t>/04_13.png</t>
   </si>
   <si>
-    <t>アートプラザ</t>
+    <t>横浜市の歴史的建造物</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_14.png</t>
@@ -1823,7 +1880,7 @@
     <t>/04_14.png</t>
   </si>
   <si>
-    <t>京都文化博物館別館</t>
+    <t>中京郵便局</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_15.png</t>
@@ -1832,7 +1889,7 @@
     <t>/04_15.png</t>
   </si>
   <si>
-    <t>旧東京国立近代美術館工芸館</t>
+    <t>自由学園明日館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_16.png</t>
@@ -1841,7 +1898,7 @@
     <t>/04_16.png</t>
   </si>
   <si>
-    <t>国立西洋美術館</t>
+    <t>東京駅丸の内駅舎</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_17.png</t>
@@ -1850,7 +1907,7 @@
     <t>/04_17.png</t>
   </si>
   <si>
-    <t>名古屋市市政資料館</t>
+    <t>旧大社駅舎</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_18.png</t>
@@ -1859,7 +1916,7 @@
     <t>/04_18.png</t>
   </si>
   <si>
-    <t>横浜市の歴史的建造物</t>
+    <t>山梨市庁舎東棟</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_19.png</t>
@@ -1868,7 +1925,7 @@
     <t>/04_19.png</t>
   </si>
   <si>
-    <t>中京郵便局</t>
+    <t>金沢市民芸術村</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_20.png</t>
@@ -1877,7 +1934,7 @@
     <t>/04_20.png</t>
   </si>
   <si>
-    <t>自由学園明日館</t>
+    <t>目黒区総合庁舎</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_21.png</t>
@@ -1886,7 +1943,7 @@
     <t>/04_21.png</t>
   </si>
   <si>
-    <t>東京駅丸の内駅舎</t>
+    <t>旧神奈川県立近代美術館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_22.png</t>
@@ -1895,7 +1952,7 @@
     <t>/04_22.png</t>
   </si>
   <si>
-    <t>旧大社駅舎</t>
+    <t>犬島精練所美術館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_23.png</t>
@@ -1904,7 +1961,7 @@
     <t>/04_23.png</t>
   </si>
   <si>
-    <t>山梨市庁舎東棟</t>
+    <t>3331ArtsChiyoda</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_24.png</t>
@@ -1913,7 +1970,7 @@
     <t>/04_24.png</t>
   </si>
   <si>
-    <t>金沢市民芸術村</t>
+    <t>石巻市庁舎</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_25.png</t>
@@ -1922,7 +1979,7 @@
     <t>/04_25.png</t>
   </si>
   <si>
-    <t>目黒区総合庁舎</t>
+    <t>大田区役所庁舎</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_26.png</t>
@@ -1931,7 +1988,7 @@
     <t>/04_26.png</t>
   </si>
   <si>
-    <t>旧神奈川県立近代美術館</t>
+    <t>千葉市美術館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_27.png</t>
@@ -1940,7 +1997,7 @@
     <t>/04_27.png</t>
   </si>
   <si>
-    <t>犬島精練所美術館</t>
+    <t>ロームシアター京都</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_28.png</t>
@@ -1949,7 +2006,7 @@
     <t>/04_28.png</t>
   </si>
   <si>
-    <t>3331ArtsChiyoda</t>
+    <t>アイアンブリッジ渓谷博物館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_29.png</t>
@@ -1958,7 +2015,7 @@
     <t>/04_29.png</t>
   </si>
   <si>
-    <t>石巻市庁舎</t>
+    <t>リンゴット工場再開発</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_30.png</t>
@@ -1967,7 +2024,7 @@
     <t>/04_30.png</t>
   </si>
   <si>
-    <t>大田区役所庁舎</t>
+    <t>テイト・モダン</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_31.png</t>
@@ -1976,7 +2033,7 @@
     <t>/04_31.png</t>
   </si>
   <si>
-    <t>千葉市美術館</t>
+    <t>オルセー美術館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_32.png</t>
@@ -1985,7 +2042,7 @@
     <t>/04_32.png</t>
   </si>
   <si>
-    <t>ロームシアター京都</t>
+    <t>カステルヴェッキオ美術館</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_33.png</t>
@@ -1994,7 +2051,7 @@
     <t>/04_33.png</t>
   </si>
   <si>
-    <t>アイアンブリッジ渓谷博物館</t>
+    <t>ジェミニレジデンス</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_34.png</t>
@@ -2003,51 +2060,6 @@
     <t>/04_34.png</t>
   </si>
   <si>
-    <t>リンゴット工場再開発</t>
-  </si>
-  <si>
-    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_35.png</t>
-  </si>
-  <si>
-    <t>/04_35.png</t>
-  </si>
-  <si>
-    <t>テイト・モダン</t>
-  </si>
-  <si>
-    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_36.png</t>
-  </si>
-  <si>
-    <t>/04_36.png</t>
-  </si>
-  <si>
-    <t>オルセー美術館</t>
-  </si>
-  <si>
-    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_37.png</t>
-  </si>
-  <si>
-    <t>/04_37.png</t>
-  </si>
-  <si>
-    <t>カステルヴェッキオ美術館</t>
-  </si>
-  <si>
-    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_38.png</t>
-  </si>
-  <si>
-    <t>/04_38.png</t>
-  </si>
-  <si>
-    <t>ジェミニレジデンス</t>
-  </si>
-  <si>
-    <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/04_39.png</t>
-  </si>
-  <si>
-    <t>/04_39.png</t>
-  </si>
-  <si>
     <t>作成中-5_独立住宅（日本） [22問]</t>
   </si>
   <si>
@@ -2723,9 +2735,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//18_01.png</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//18_02.png</t>
   </si>
   <si>
@@ -2750,9 +2759,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_01.png</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_02.png</t>
   </si>
   <si>
@@ -2840,9 +2846,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//20_01.png</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//20_02.png</t>
   </si>
   <si>
@@ -2859,9 +2862,6 @@
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//21_01.png</t>
-  </si>
-  <si>
-    <t>21</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//21_02.png</t>
@@ -3006,7 +3006,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -3032,6 +3032,11 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3047,7 +3052,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -3079,6 +3084,9 @@
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6648,20 +6656,20 @@
       <c r="G86" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="I86" s="10" t="s">
         <v>520</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K86" s="8" t="s">
+      <c r="K86" s="4" t="s">
         <v>521</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M86" s="8" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>522</v>
       </c>
       <c r="O86" s="8"/>
     </row>
@@ -6670,31 +6678,31 @@
         <v>420</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="I87" s="1" t="s">
         <v>526</v>
+      </c>
+      <c r="I87" s="11" t="s">
+        <v>527</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K87" s="8" t="s">
-        <v>527</v>
+      <c r="K87" s="4" t="s">
+        <v>528</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M87" s="8" t="s">
         <v>30</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>529</v>
       </c>
       <c r="O87" s="8"/>
     </row>
@@ -6703,31 +6711,31 @@
         <v>420</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
+      </c>
+      <c r="I88" s="11" t="s">
+        <v>534</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K88" s="8" t="s">
-        <v>533</v>
+      <c r="K88" s="4" t="s">
+        <v>535</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M88" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>536</v>
       </c>
       <c r="O88" s="8"/>
     </row>
@@ -6736,31 +6744,31 @@
         <v>420</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>541</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K89" s="8" t="s">
-        <v>539</v>
+      <c r="K89" s="4" t="s">
+        <v>542</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M89" s="8" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>543</v>
       </c>
       <c r="O89" s="8"/>
     </row>
@@ -6769,28 +6777,28 @@
         <v>420</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>549</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K90" s="8" t="s">
-        <v>546</v>
+      <c r="K90" s="5" t="s">
+        <v>550</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>38</v>
@@ -6805,28 +6813,28 @@
         <v>420</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>555</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K91" s="8" t="s">
-        <v>552</v>
+      <c r="K91" s="5" t="s">
+        <v>556</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>38</v>
@@ -6841,31 +6849,31 @@
         <v>420</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>562</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K92" s="8" t="s">
-        <v>559</v>
+      <c r="K92" s="5" t="s">
+        <v>563</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>38</v>
@@ -6877,31 +6885,31 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>569</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K93" s="8" t="s">
-        <v>566</v>
+      <c r="K93" s="5" t="s">
+        <v>570</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>38</v>
@@ -6913,31 +6921,31 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>573</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K94" s="8" t="s">
-        <v>570</v>
+      <c r="K94" s="5" t="s">
+        <v>574</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>38</v>
@@ -6949,31 +6957,31 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="L95" s="8" t="s">
         <v>38</v>
@@ -6985,19 +6993,19 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>38</v>
@@ -7009,19 +7017,19 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>38</v>
@@ -7033,19 +7041,19 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>38</v>
@@ -7057,19 +7065,19 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>38</v>
@@ -7081,19 +7089,19 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>38</v>
@@ -7105,19 +7113,19 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>38</v>
@@ -7129,19 +7137,19 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>38</v>
@@ -7153,19 +7161,19 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>38</v>
@@ -7177,19 +7185,19 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K104" s="8" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="L104" s="8" t="s">
         <v>38</v>
@@ -7201,19 +7209,19 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>38</v>
@@ -7225,19 +7233,19 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>38</v>
@@ -7249,19 +7257,19 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K107" s="8" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>38</v>
@@ -7273,19 +7281,19 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K108" s="8" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>38</v>
@@ -7297,19 +7305,19 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K109" s="8" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>38</v>
@@ -7321,19 +7329,19 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>38</v>
@@ -7345,19 +7353,19 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>38</v>
@@ -7369,19 +7377,19 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="L112" s="8" t="s">
         <v>38</v>
@@ -7393,19 +7401,19 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>38</v>
@@ -7417,19 +7425,19 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K114" s="8" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>38</v>
@@ -7441,19 +7449,19 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K115" s="8" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>38</v>
@@ -7465,19 +7473,19 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K116" s="8" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>38</v>
@@ -7489,19 +7497,19 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K117" s="8" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L117" s="8" t="s">
         <v>38</v>
@@ -7513,19 +7521,19 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K118" s="8" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>38</v>
@@ -7537,19 +7545,19 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K119" s="8" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>38</v>
@@ -7561,19 +7569,19 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>38</v>
@@ -7585,19 +7593,19 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K121" s="8" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>38</v>
@@ -7609,19 +7617,19 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K122" s="8" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>38</v>
@@ -7633,19 +7641,19 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K123" s="8" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>38</v>
@@ -7657,13 +7665,13 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K124" s="1" t="str">
         <f t="shared" ref="K124:K405" si="1">"/"&amp;L124&amp;"_"&amp;M124&amp;".png"</f>
@@ -7679,13 +7687,13 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K125" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7701,13 +7709,13 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K126" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7723,13 +7731,13 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K127" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7745,13 +7753,13 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K128" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7767,13 +7775,13 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K129" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7789,13 +7797,13 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K130" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7811,13 +7819,13 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K131" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7833,13 +7841,13 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K132" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7855,13 +7863,13 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K133" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7877,13 +7885,13 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K134" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7899,13 +7907,13 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K135" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7921,13 +7929,13 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="J136" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K136" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7943,13 +7951,13 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K137" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7965,13 +7973,13 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K138" s="1" t="str">
         <f t="shared" si="1"/>
@@ -7987,13 +7995,13 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K139" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8009,13 +8017,13 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K140" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8031,13 +8039,13 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K141" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8054,13 +8062,13 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K142" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8077,13 +8085,13 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K143" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8100,13 +8108,13 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K144" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8123,13 +8131,13 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K145" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8146,13 +8154,13 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K146" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8169,13 +8177,13 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K147" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8192,13 +8200,13 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K148" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8215,13 +8223,13 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="J149" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K149" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8238,13 +8246,13 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K150" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8261,13 +8269,13 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K151" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8284,13 +8292,13 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K152" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8307,13 +8315,13 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K153" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8330,13 +8338,13 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K154" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8353,13 +8361,13 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K155" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8376,13 +8384,13 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K156" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8399,13 +8407,13 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K157" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8422,13 +8430,13 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K158" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8445,13 +8453,13 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="J159" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K159" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8468,13 +8476,13 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="J160" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K160" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8491,13 +8499,13 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="J161" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K161" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8514,13 +8522,13 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="J162" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K162" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8537,13 +8545,13 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="J163" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K163" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8560,13 +8568,13 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="J164" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K164" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8583,13 +8591,13 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K165" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8605,13 +8613,13 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K166" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8627,13 +8635,13 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="J167" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K167" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8649,13 +8657,13 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="J168" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K168" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8671,13 +8679,13 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="J169" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K169" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8693,13 +8701,13 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="J170" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K170" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8715,13 +8723,13 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="J171" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K171" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8737,13 +8745,13 @@
     </row>
     <row r="172">
       <c r="A172" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="J172" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K172" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8759,13 +8767,13 @@
     </row>
     <row r="173">
       <c r="A173" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="J173" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K173" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8781,13 +8789,13 @@
     </row>
     <row r="174">
       <c r="A174" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="J174" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K174" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8803,13 +8811,13 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="J175" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K175" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8825,13 +8833,13 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="J176" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K176" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8847,13 +8855,13 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J177" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K177" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8869,13 +8877,13 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="J178" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K178" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8891,13 +8899,13 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="J179" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K179" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8913,13 +8921,13 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="J180" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K180" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8935,13 +8943,13 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="J181" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K181" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8957,13 +8965,13 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="J182" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K182" s="1" t="str">
         <f t="shared" si="1"/>
@@ -8980,13 +8988,13 @@
     </row>
     <row r="183">
       <c r="A183" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="J183" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K183" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9003,13 +9011,13 @@
     </row>
     <row r="184">
       <c r="A184" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="J184" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K184" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9026,13 +9034,13 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="J185" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K185" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9049,13 +9057,13 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="J186" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K186" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9072,13 +9080,13 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="J187" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K187" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9095,13 +9103,13 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="J188" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K188" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9118,13 +9126,13 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="J189" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K189" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9141,13 +9149,13 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="J190" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K190" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9164,13 +9172,13 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="J191" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K191" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9187,13 +9195,13 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="J192" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K192" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9210,13 +9218,13 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="J193" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K193" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9233,13 +9241,13 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K194" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9256,13 +9264,13 @@
     </row>
     <row r="195">
       <c r="A195" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J195" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K195" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9279,13 +9287,13 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="J196" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K196" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9302,13 +9310,13 @@
     </row>
     <row r="197">
       <c r="A197" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="J197" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K197" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9325,13 +9333,13 @@
     </row>
     <row r="198">
       <c r="A198" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="J198" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K198" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9348,13 +9356,13 @@
     </row>
     <row r="199">
       <c r="A199" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="J199" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K199" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9371,13 +9379,13 @@
     </row>
     <row r="200">
       <c r="A200" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="J200" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K200" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9394,13 +9402,13 @@
     </row>
     <row r="201">
       <c r="A201" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="J201" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K201" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9417,13 +9425,13 @@
     </row>
     <row r="202">
       <c r="A202" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="J202" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K202" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9440,13 +9448,13 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="J203" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K203" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9463,13 +9471,13 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="J204" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K204" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9486,13 +9494,13 @@
     </row>
     <row r="205">
       <c r="A205" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="J205" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K205" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9509,13 +9517,13 @@
     </row>
     <row r="206">
       <c r="A206" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="J206" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K206" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9532,13 +9540,13 @@
     </row>
     <row r="207">
       <c r="A207" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="J207" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K207" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9555,13 +9563,13 @@
     </row>
     <row r="208">
       <c r="A208" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="J208" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K208" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9578,13 +9586,13 @@
     </row>
     <row r="209">
       <c r="A209" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="J209" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K209" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9601,13 +9609,13 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="J210" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K210" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9624,13 +9632,13 @@
     </row>
     <row r="211">
       <c r="A211" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="J211" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K211" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9647,13 +9655,13 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="J212" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K212" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9670,13 +9678,13 @@
     </row>
     <row r="213">
       <c r="A213" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="J213" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K213" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9693,13 +9701,13 @@
     </row>
     <row r="214">
       <c r="A214" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J214" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K214" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9716,13 +9724,13 @@
     </row>
     <row r="215">
       <c r="A215" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="J215" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K215" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9738,13 +9746,13 @@
     </row>
     <row r="216">
       <c r="A216" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="J216" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K216" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9760,13 +9768,13 @@
     </row>
     <row r="217">
       <c r="A217" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="J217" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K217" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9782,13 +9790,13 @@
     </row>
     <row r="218">
       <c r="A218" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="J218" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K218" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9804,13 +9812,13 @@
     </row>
     <row r="219">
       <c r="A219" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="J219" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K219" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9826,13 +9834,13 @@
     </row>
     <row r="220">
       <c r="A220" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="J220" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K220" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9848,13 +9856,13 @@
     </row>
     <row r="221">
       <c r="A221" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="J221" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K221" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9870,13 +9878,13 @@
     </row>
     <row r="222">
       <c r="A222" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="J222" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K222" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9892,13 +9900,13 @@
     </row>
     <row r="223">
       <c r="A223" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="J223" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K223" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9914,13 +9922,13 @@
     </row>
     <row r="224">
       <c r="A224" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="J224" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K224" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9936,13 +9944,13 @@
     </row>
     <row r="225">
       <c r="A225" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="J225" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K225" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9958,13 +9966,13 @@
     </row>
     <row r="226">
       <c r="A226" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J226" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K226" s="1" t="str">
         <f t="shared" si="1"/>
@@ -9980,13 +9988,13 @@
     </row>
     <row r="227">
       <c r="A227" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="J227" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K227" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10002,13 +10010,13 @@
     </row>
     <row r="228">
       <c r="A228" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="J228" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K228" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10024,13 +10032,13 @@
     </row>
     <row r="229">
       <c r="A229" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="J229" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K229" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10046,13 +10054,13 @@
     </row>
     <row r="230">
       <c r="A230" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="J230" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K230" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10068,13 +10076,13 @@
     </row>
     <row r="231">
       <c r="A231" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="J231" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K231" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10090,13 +10098,13 @@
     </row>
     <row r="232">
       <c r="A232" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="J232" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K232" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10112,13 +10120,13 @@
     </row>
     <row r="233">
       <c r="A233" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="J233" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K233" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10134,13 +10142,13 @@
     </row>
     <row r="234">
       <c r="A234" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="J234" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K234" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10156,13 +10164,13 @@
     </row>
     <row r="235">
       <c r="A235" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="J235" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K235" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10178,13 +10186,13 @@
     </row>
     <row r="236">
       <c r="A236" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="J236" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K236" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10200,13 +10208,13 @@
     </row>
     <row r="237">
       <c r="A237" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="J237" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K237" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10222,13 +10230,13 @@
     </row>
     <row r="238">
       <c r="A238" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="J238" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K238" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10244,13 +10252,13 @@
     </row>
     <row r="239">
       <c r="A239" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="J239" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K239" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10266,13 +10274,13 @@
     </row>
     <row r="240">
       <c r="A240" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="J240" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K240" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10288,13 +10296,13 @@
     </row>
     <row r="241">
       <c r="A241" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="J241" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K241" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10310,13 +10318,13 @@
     </row>
     <row r="242">
       <c r="A242" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="J242" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K242" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10332,13 +10340,13 @@
     </row>
     <row r="243">
       <c r="A243" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="J243" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K243" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10354,13 +10362,13 @@
     </row>
     <row r="244">
       <c r="A244" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="J244" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K244" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10376,13 +10384,13 @@
     </row>
     <row r="245">
       <c r="A245" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="J245" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K245" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10398,13 +10406,13 @@
     </row>
     <row r="246">
       <c r="A246" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="J246" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K246" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10420,13 +10428,13 @@
     </row>
     <row r="247">
       <c r="A247" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="J247" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K247" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10442,13 +10450,13 @@
     </row>
     <row r="248">
       <c r="A248" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="J248" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K248" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10464,13 +10472,13 @@
     </row>
     <row r="249">
       <c r="A249" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="J249" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K249" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10486,13 +10494,13 @@
     </row>
     <row r="250">
       <c r="A250" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="J250" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K250" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10508,13 +10516,13 @@
     </row>
     <row r="251">
       <c r="A251" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="J251" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K251" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10530,13 +10538,13 @@
     </row>
     <row r="252">
       <c r="A252" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="J252" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K252" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10552,13 +10560,13 @@
     </row>
     <row r="253">
       <c r="A253" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="J253" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K253" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10574,13 +10582,13 @@
     </row>
     <row r="254">
       <c r="A254" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="J254" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K254" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10596,20 +10604,20 @@
     </row>
     <row r="255">
       <c r="A255" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="J255" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K255" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_01.png</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M255" s="8" t="s">
         <v>21</v>
@@ -10618,20 +10626,20 @@
     </row>
     <row r="256">
       <c r="A256" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="J256" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K256" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_02.png</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M256" s="8" t="s">
         <v>22</v>
@@ -10640,20 +10648,20 @@
     </row>
     <row r="257">
       <c r="A257" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="J257" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K257" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_03.png</v>
       </c>
       <c r="L257" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M257" s="8" t="s">
         <v>30</v>
@@ -10662,20 +10670,20 @@
     </row>
     <row r="258">
       <c r="A258" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="J258" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K258" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_04.png</v>
       </c>
       <c r="L258" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M258" s="8" t="s">
         <v>38</v>
@@ -10684,20 +10692,20 @@
     </row>
     <row r="259">
       <c r="A259" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I259" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="J259" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="K259" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/11_05.png</v>
+      </c>
+      <c r="L259" s="4" t="s">
         <v>805</v>
-      </c>
-      <c r="J259" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K259" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/11_05.png</v>
-      </c>
-      <c r="L259" s="4" t="s">
-        <v>801</v>
       </c>
       <c r="M259" s="8" t="s">
         <v>47</v>
@@ -10706,20 +10714,20 @@
     </row>
     <row r="260">
       <c r="A260" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="J260" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K260" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_06.png</v>
       </c>
       <c r="L260" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M260" s="8" t="s">
         <v>55</v>
@@ -10728,20 +10736,20 @@
     </row>
     <row r="261">
       <c r="A261" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="J261" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K261" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_07.png</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M261" s="8" t="s">
         <v>63</v>
@@ -10750,20 +10758,20 @@
     </row>
     <row r="262">
       <c r="A262" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="J262" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K262" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_08.png</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M262" s="8" t="s">
         <v>70</v>
@@ -10772,20 +10780,20 @@
     </row>
     <row r="263">
       <c r="A263" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="J263" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K263" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_09.png</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M263" s="8" t="s">
         <v>77</v>
@@ -10794,20 +10802,20 @@
     </row>
     <row r="264">
       <c r="A264" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="J264" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K264" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_10.png</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M264" s="8" t="s">
         <v>85</v>
@@ -10816,20 +10824,20 @@
     </row>
     <row r="265">
       <c r="A265" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="J265" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K265" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_11.png</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M265" s="3">
         <v>11.0</v>
@@ -10838,20 +10846,20 @@
     </row>
     <row r="266">
       <c r="A266" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="J266" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K266" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_12.png</v>
       </c>
       <c r="L266" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M266" s="3">
         <v>12.0</v>
@@ -10860,20 +10868,20 @@
     </row>
     <row r="267">
       <c r="A267" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="J267" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K267" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_13.png</v>
       </c>
       <c r="L267" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M267" s="3">
         <v>13.0</v>
@@ -10882,20 +10890,20 @@
     </row>
     <row r="268">
       <c r="A268" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="J268" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K268" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_14.png</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M268" s="3">
         <v>14.0</v>
@@ -10904,20 +10912,20 @@
     </row>
     <row r="269">
       <c r="A269" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="J269" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K269" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_15.png</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M269" s="3">
         <v>15.0</v>
@@ -10926,20 +10934,20 @@
     </row>
     <row r="270">
       <c r="A270" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="J270" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K270" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_16.png</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M270" s="3">
         <v>16.0</v>
@@ -10948,20 +10956,20 @@
     </row>
     <row r="271">
       <c r="A271" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="J271" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K271" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_17.png</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M271" s="3">
         <f t="shared" ref="M271:M276" si="4">M270+1</f>
@@ -10971,20 +10979,20 @@
     </row>
     <row r="272">
       <c r="A272" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="J272" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K272" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_18.png</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M272" s="3">
         <f t="shared" si="4"/>
@@ -10994,20 +11002,20 @@
     </row>
     <row r="273">
       <c r="A273" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="J273" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K273" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_19.png</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M273" s="3">
         <f t="shared" si="4"/>
@@ -11017,20 +11025,20 @@
     </row>
     <row r="274">
       <c r="A274" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="J274" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K274" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_20.png</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M274" s="3">
         <f t="shared" si="4"/>
@@ -11040,20 +11048,20 @@
     </row>
     <row r="275">
       <c r="A275" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="J275" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K275" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_21.png</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M275" s="3">
         <f t="shared" si="4"/>
@@ -11063,20 +11071,20 @@
     </row>
     <row r="276">
       <c r="A276" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="J276" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K276" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/11_22.png</v>
       </c>
       <c r="L276" s="4" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M276" s="3">
         <f t="shared" si="4"/>
@@ -11086,20 +11094,20 @@
     </row>
     <row r="277">
       <c r="A277" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="J277" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K277" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/12_01.png</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M277" s="8" t="s">
         <v>21</v>
@@ -11108,20 +11116,20 @@
     </row>
     <row r="278">
       <c r="A278" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K278" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/12_02.png</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M278" s="8" t="s">
         <v>22</v>
@@ -11130,20 +11138,20 @@
     </row>
     <row r="279">
       <c r="A279" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="J279" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K279" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/12_03.png</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M279" s="8" t="s">
         <v>30</v>
@@ -11152,20 +11160,20 @@
     </row>
     <row r="280">
       <c r="A280" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K280" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/12_04.png</v>
       </c>
       <c r="L280" s="4" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M280" s="8" t="s">
         <v>38</v>
@@ -11174,20 +11182,20 @@
     </row>
     <row r="281">
       <c r="A281" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="I281" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="J281" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="K281" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/12_05.png</v>
+      </c>
+      <c r="L281" s="4" t="s">
         <v>829</v>
-      </c>
-      <c r="J281" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K281" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/12_05.png</v>
-      </c>
-      <c r="L281" s="4" t="s">
-        <v>825</v>
       </c>
       <c r="M281" s="8" t="s">
         <v>47</v>
@@ -11196,20 +11204,20 @@
     </row>
     <row r="282">
       <c r="A282" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="J282" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K282" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/13_01.png</v>
       </c>
       <c r="L282" s="4" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="M282" s="8" t="s">
         <v>21</v>
@@ -11218,20 +11226,20 @@
     </row>
     <row r="283">
       <c r="A283" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="J283" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K283" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/13_02.png</v>
       </c>
       <c r="L283" s="4" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="M283" s="8" t="s">
         <v>22</v>
@@ -11240,20 +11248,20 @@
     </row>
     <row r="284">
       <c r="A284" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="J284" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K284" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/13_03.png</v>
       </c>
       <c r="L284" s="4" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="M284" s="8" t="s">
         <v>30</v>
@@ -11262,20 +11270,20 @@
     </row>
     <row r="285">
       <c r="A285" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="J285" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K285" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/13_04.png</v>
       </c>
       <c r="L285" s="4" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="M285" s="8" t="s">
         <v>38</v>
@@ -11284,20 +11292,20 @@
     </row>
     <row r="286">
       <c r="A286" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="J286" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K286" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_01.png</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M286" s="8" t="s">
         <v>21</v>
@@ -11306,20 +11314,20 @@
     </row>
     <row r="287">
       <c r="A287" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="J287" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K287" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_02.png</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M287" s="8" t="s">
         <v>22</v>
@@ -11328,20 +11336,20 @@
     </row>
     <row r="288">
       <c r="A288" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="J288" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K288" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_03.png</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M288" s="8" t="s">
         <v>30</v>
@@ -11350,20 +11358,20 @@
     </row>
     <row r="289">
       <c r="A289" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="J289" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K289" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_04.png</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M289" s="8" t="s">
         <v>38</v>
@@ -11372,20 +11380,20 @@
     </row>
     <row r="290">
       <c r="A290" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I290" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="J290" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="K290" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/14_05.png</v>
+      </c>
+      <c r="L290" s="4" t="s">
         <v>842</v>
-      </c>
-      <c r="J290" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K290" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/14_05.png</v>
-      </c>
-      <c r="L290" s="4" t="s">
-        <v>838</v>
       </c>
       <c r="M290" s="8" t="s">
         <v>47</v>
@@ -11394,20 +11402,20 @@
     </row>
     <row r="291">
       <c r="A291" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J291" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K291" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_06.png</v>
       </c>
       <c r="L291" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M291" s="8" t="s">
         <v>55</v>
@@ -11416,20 +11424,20 @@
     </row>
     <row r="292">
       <c r="A292" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="J292" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K292" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_07.png</v>
       </c>
       <c r="L292" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M292" s="8" t="s">
         <v>63</v>
@@ -11438,20 +11446,20 @@
     </row>
     <row r="293">
       <c r="A293" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="J293" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K293" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_08.png</v>
       </c>
       <c r="L293" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M293" s="8" t="s">
         <v>70</v>
@@ -11460,20 +11468,20 @@
     </row>
     <row r="294">
       <c r="A294" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="J294" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K294" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_09.png</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M294" s="8" t="s">
         <v>77</v>
@@ -11482,20 +11490,20 @@
     </row>
     <row r="295">
       <c r="A295" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="J295" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K295" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_10.png</v>
       </c>
       <c r="L295" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M295" s="8" t="s">
         <v>85</v>
@@ -11504,20 +11512,20 @@
     </row>
     <row r="296">
       <c r="A296" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="J296" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K296" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_11.png</v>
       </c>
       <c r="L296" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M296" s="3">
         <v>11.0</v>
@@ -11526,20 +11534,20 @@
     </row>
     <row r="297">
       <c r="A297" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="J297" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K297" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_12.png</v>
       </c>
       <c r="L297" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M297" s="3">
         <v>12.0</v>
@@ -11548,20 +11556,20 @@
     </row>
     <row r="298">
       <c r="A298" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="J298" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K298" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_13.png</v>
       </c>
       <c r="L298" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M298" s="3">
         <v>13.0</v>
@@ -11570,20 +11578,20 @@
     </row>
     <row r="299">
       <c r="A299" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="J299" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K299" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_14.png</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M299" s="3">
         <v>14.0</v>
@@ -11592,20 +11600,20 @@
     </row>
     <row r="300">
       <c r="A300" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="J300" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K300" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_15.png</v>
       </c>
       <c r="L300" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M300" s="3">
         <v>15.0</v>
@@ -11614,20 +11622,20 @@
     </row>
     <row r="301">
       <c r="A301" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="J301" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K301" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_16.png</v>
       </c>
       <c r="L301" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M301" s="3">
         <f t="shared" ref="M301:M304" si="5">M300+1</f>
@@ -11637,20 +11645,20 @@
     </row>
     <row r="302">
       <c r="A302" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="J302" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K302" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_17.png</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M302" s="3">
         <f t="shared" si="5"/>
@@ -11660,20 +11668,20 @@
     </row>
     <row r="303">
       <c r="A303" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="J303" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K303" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_18.png</v>
       </c>
       <c r="L303" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M303" s="3">
         <f t="shared" si="5"/>
@@ -11683,20 +11691,20 @@
     </row>
     <row r="304">
       <c r="A304" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="J304" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K304" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/14_19.png</v>
       </c>
       <c r="L304" s="4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M304" s="3">
         <f t="shared" si="5"/>
@@ -11706,20 +11714,20 @@
     </row>
     <row r="305">
       <c r="A305" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="J305" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K305" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_01.png</v>
       </c>
       <c r="L305" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M305" s="8" t="s">
         <v>21</v>
@@ -11728,20 +11736,20 @@
     </row>
     <row r="306">
       <c r="A306" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="J306" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K306" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_02.png</v>
       </c>
       <c r="L306" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M306" s="8" t="s">
         <v>22</v>
@@ -11750,20 +11758,20 @@
     </row>
     <row r="307">
       <c r="A307" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="J307" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K307" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_03.png</v>
       </c>
       <c r="L307" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M307" s="8" t="s">
         <v>30</v>
@@ -11772,20 +11780,20 @@
     </row>
     <row r="308">
       <c r="A308" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="J308" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K308" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_04.png</v>
       </c>
       <c r="L308" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M308" s="8" t="s">
         <v>38</v>
@@ -11794,20 +11802,20 @@
     </row>
     <row r="309">
       <c r="A309" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I309" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="J309" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="K309" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/15_05.png</v>
+      </c>
+      <c r="L309" s="4" t="s">
         <v>863</v>
-      </c>
-      <c r="J309" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K309" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/15_05.png</v>
-      </c>
-      <c r="L309" s="4" t="s">
-        <v>859</v>
       </c>
       <c r="M309" s="8" t="s">
         <v>47</v>
@@ -11816,20 +11824,20 @@
     </row>
     <row r="310">
       <c r="A310" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="J310" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K310" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_06.png</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M310" s="8" t="s">
         <v>55</v>
@@ -11838,20 +11846,20 @@
     </row>
     <row r="311">
       <c r="A311" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="J311" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K311" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_07.png</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M311" s="8" t="s">
         <v>63</v>
@@ -11860,20 +11868,20 @@
     </row>
     <row r="312">
       <c r="A312" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="J312" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K312" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/15_08.png</v>
       </c>
       <c r="L312" s="4" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="M312" s="8" t="s">
         <v>70</v>
@@ -11882,20 +11890,20 @@
     </row>
     <row r="313">
       <c r="A313" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="J313" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K313" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/16_01.png</v>
       </c>
       <c r="L313" s="4" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="M313" s="8" t="s">
         <v>21</v>
@@ -11904,20 +11912,20 @@
     </row>
     <row r="314">
       <c r="A314" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="J314" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K314" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/16_02.png</v>
       </c>
       <c r="L314" s="4" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="M314" s="8" t="s">
         <v>22</v>
@@ -11926,20 +11934,20 @@
     </row>
     <row r="315">
       <c r="A315" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="J315" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K315" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/16_03.png</v>
       </c>
       <c r="L315" s="4" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="M315" s="8" t="s">
         <v>30</v>
@@ -11948,20 +11956,20 @@
     </row>
     <row r="316">
       <c r="A316" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="J316" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K316" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/16_04.png</v>
       </c>
       <c r="L316" s="4" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="M316" s="8" t="s">
         <v>38</v>
@@ -11970,20 +11978,20 @@
     </row>
     <row r="317">
       <c r="A317" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="J317" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K317" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_01.png</v>
       </c>
       <c r="L317" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M317" s="8" t="s">
         <v>21</v>
@@ -11992,20 +12000,20 @@
     </row>
     <row r="318">
       <c r="A318" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="J318" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K318" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_02.png</v>
       </c>
       <c r="L318" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M318" s="8" t="s">
         <v>22</v>
@@ -12014,20 +12022,20 @@
     </row>
     <row r="319">
       <c r="A319" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="J319" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K319" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_03.png</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M319" s="8" t="s">
         <v>30</v>
@@ -12036,20 +12044,20 @@
     </row>
     <row r="320">
       <c r="A320" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="J320" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K320" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_04.png</v>
       </c>
       <c r="L320" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M320" s="8" t="s">
         <v>38</v>
@@ -12058,20 +12066,20 @@
     </row>
     <row r="321">
       <c r="A321" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I321" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="J321" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="K321" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/17_05.png</v>
+      </c>
+      <c r="L321" s="4" t="s">
         <v>879</v>
-      </c>
-      <c r="J321" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K321" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/17_05.png</v>
-      </c>
-      <c r="L321" s="4" t="s">
-        <v>875</v>
       </c>
       <c r="M321" s="8" t="s">
         <v>47</v>
@@ -12080,20 +12088,20 @@
     </row>
     <row r="322">
       <c r="A322" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="J322" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K322" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_06.png</v>
       </c>
       <c r="L322" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M322" s="8" t="s">
         <v>55</v>
@@ -12102,20 +12110,20 @@
     </row>
     <row r="323">
       <c r="A323" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="J323" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K323" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_07.png</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M323" s="8" t="s">
         <v>63</v>
@@ -12124,20 +12132,20 @@
     </row>
     <row r="324">
       <c r="A324" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="J324" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K324" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_08.png</v>
       </c>
       <c r="L324" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M324" s="8" t="s">
         <v>70</v>
@@ -12146,20 +12154,20 @@
     </row>
     <row r="325">
       <c r="A325" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="J325" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K325" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/17_09.png</v>
       </c>
       <c r="L325" s="4" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M325" s="8" t="s">
         <v>77</v>
@@ -12168,20 +12176,20 @@
     </row>
     <row r="326">
       <c r="A326" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="J326" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K326" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_01.png</v>
       </c>
       <c r="L326" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M326" s="8" t="s">
         <v>21</v>
@@ -12190,20 +12198,20 @@
     </row>
     <row r="327">
       <c r="A327" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="J327" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K327" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_02.png</v>
       </c>
       <c r="L327" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M327" s="8" t="s">
         <v>22</v>
@@ -12212,20 +12220,20 @@
     </row>
     <row r="328">
       <c r="A328" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="J328" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K328" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_03.png</v>
       </c>
       <c r="L328" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M328" s="8" t="s">
         <v>30</v>
@@ -12234,20 +12242,20 @@
     </row>
     <row r="329">
       <c r="A329" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="J329" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K329" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_04.png</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M329" s="8" t="s">
         <v>38</v>
@@ -12256,20 +12264,20 @@
     </row>
     <row r="330">
       <c r="A330" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="J330" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K330" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_05.png</v>
       </c>
       <c r="L330" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M330" s="8" t="s">
         <v>47</v>
@@ -12278,20 +12286,20 @@
     </row>
     <row r="331">
       <c r="A331" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="J331" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K331" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_06.png</v>
       </c>
       <c r="L331" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M331" s="8" t="s">
         <v>55</v>
@@ -12300,20 +12308,20 @@
     </row>
     <row r="332">
       <c r="A332" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="J332" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K332" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/18_07.png</v>
       </c>
       <c r="L332" s="4" t="s">
-        <v>886</v>
+        <v>522</v>
       </c>
       <c r="M332" s="8" t="s">
         <v>63</v>
@@ -12322,20 +12330,20 @@
     </row>
     <row r="333">
       <c r="A333" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="J333" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K333" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_01.png</v>
       </c>
       <c r="L333" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M333" s="8" t="s">
         <v>21</v>
@@ -12344,20 +12352,20 @@
     </row>
     <row r="334">
       <c r="A334" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="J334" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K334" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_02.png</v>
       </c>
       <c r="L334" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M334" s="8" t="s">
         <v>22</v>
@@ -12366,20 +12374,20 @@
     </row>
     <row r="335">
       <c r="A335" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="J335" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K335" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_03.png</v>
       </c>
       <c r="L335" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M335" s="8" t="s">
         <v>30</v>
@@ -12388,20 +12396,20 @@
     </row>
     <row r="336">
       <c r="A336" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="J336" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K336" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_04.png</v>
       </c>
       <c r="L336" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M336" s="8" t="s">
         <v>38</v>
@@ -12410,20 +12418,20 @@
     </row>
     <row r="337">
       <c r="A337" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="J337" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K337" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_05.png</v>
       </c>
       <c r="L337" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M337" s="8" t="s">
         <v>47</v>
@@ -12432,20 +12440,20 @@
     </row>
     <row r="338">
       <c r="A338" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="J338" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K338" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_06.png</v>
       </c>
       <c r="L338" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M338" s="8" t="s">
         <v>55</v>
@@ -12454,20 +12462,20 @@
     </row>
     <row r="339">
       <c r="A339" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="J339" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K339" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_07.png</v>
       </c>
       <c r="L339" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M339" s="8" t="s">
         <v>63</v>
@@ -12476,20 +12484,20 @@
     </row>
     <row r="340">
       <c r="A340" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="J340" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K340" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_08.png</v>
       </c>
       <c r="L340" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M340" s="8" t="s">
         <v>70</v>
@@ -12498,20 +12506,20 @@
     </row>
     <row r="341">
       <c r="A341" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="J341" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K341" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_09.png</v>
       </c>
       <c r="L341" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M341" s="8" t="s">
         <v>77</v>
@@ -12520,20 +12528,20 @@
     </row>
     <row r="342">
       <c r="A342" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="J342" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K342" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_10.png</v>
       </c>
       <c r="L342" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M342" s="8" t="s">
         <v>85</v>
@@ -12542,20 +12550,20 @@
     </row>
     <row r="343">
       <c r="A343" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J343" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K343" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_11.png</v>
       </c>
       <c r="L343" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M343" s="3">
         <v>11.0</v>
@@ -12564,20 +12572,20 @@
     </row>
     <row r="344">
       <c r="A344" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="J344" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K344" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_12.png</v>
       </c>
       <c r="L344" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M344" s="3">
         <v>12.0</v>
@@ -12586,20 +12594,20 @@
     </row>
     <row r="345">
       <c r="A345" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="J345" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K345" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_13.png</v>
       </c>
       <c r="L345" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M345" s="3">
         <v>13.0</v>
@@ -12608,20 +12616,20 @@
     </row>
     <row r="346">
       <c r="A346" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="J346" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K346" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_14.png</v>
       </c>
       <c r="L346" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M346" s="3">
         <v>14.0</v>
@@ -12630,20 +12638,20 @@
     </row>
     <row r="347">
       <c r="A347" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I347" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="J347" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K347" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_15.png</v>
       </c>
       <c r="L347" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M347" s="3">
         <v>15.0</v>
@@ -12652,20 +12660,20 @@
     </row>
     <row r="348">
       <c r="A348" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="J348" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K348" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_16.png</v>
       </c>
       <c r="L348" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M348" s="3">
         <v>16.0</v>
@@ -12674,20 +12682,20 @@
     </row>
     <row r="349">
       <c r="A349" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="J349" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K349" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_17.png</v>
       </c>
       <c r="L349" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M349" s="3">
         <v>17.0</v>
@@ -12696,20 +12704,20 @@
     </row>
     <row r="350">
       <c r="A350" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="J350" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K350" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_18.png</v>
       </c>
       <c r="L350" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M350" s="8">
         <f t="shared" ref="M350:M360" si="6">M349+1</f>
@@ -12719,20 +12727,20 @@
     </row>
     <row r="351">
       <c r="A351" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="J351" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K351" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_19.png</v>
       </c>
       <c r="L351" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M351" s="8">
         <f t="shared" si="6"/>
@@ -12742,20 +12750,20 @@
     </row>
     <row r="352">
       <c r="A352" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="J352" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K352" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_20.png</v>
       </c>
       <c r="L352" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M352" s="8">
         <f t="shared" si="6"/>
@@ -12765,20 +12773,20 @@
     </row>
     <row r="353">
       <c r="A353" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="J353" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K353" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_21.png</v>
       </c>
       <c r="L353" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M353" s="8">
         <f t="shared" si="6"/>
@@ -12788,20 +12796,20 @@
     </row>
     <row r="354">
       <c r="A354" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="J354" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K354" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_22.png</v>
       </c>
       <c r="L354" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M354" s="8">
         <f t="shared" si="6"/>
@@ -12811,20 +12819,20 @@
     </row>
     <row r="355">
       <c r="A355" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="J355" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K355" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_23.png</v>
       </c>
       <c r="L355" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M355" s="8">
         <f t="shared" si="6"/>
@@ -12834,20 +12842,20 @@
     </row>
     <row r="356">
       <c r="A356" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J356" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K356" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_24.png</v>
       </c>
       <c r="L356" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M356" s="8">
         <f t="shared" si="6"/>
@@ -12857,20 +12865,20 @@
     </row>
     <row r="357">
       <c r="A357" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="J357" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K357" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_25.png</v>
       </c>
       <c r="L357" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M357" s="8">
         <f t="shared" si="6"/>
@@ -12880,20 +12888,20 @@
     </row>
     <row r="358">
       <c r="A358" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I358" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="J358" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K358" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_26.png</v>
       </c>
       <c r="L358" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M358" s="8">
         <f t="shared" si="6"/>
@@ -12903,20 +12911,20 @@
     </row>
     <row r="359">
       <c r="A359" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="J359" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K359" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_27.png</v>
       </c>
       <c r="L359" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M359" s="8">
         <f t="shared" si="6"/>
@@ -12926,20 +12934,20 @@
     </row>
     <row r="360">
       <c r="A360" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I360" s="1" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="J360" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K360" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/19_28.png</v>
       </c>
       <c r="L360" s="4" t="s">
-        <v>895</v>
+        <v>529</v>
       </c>
       <c r="M360" s="8">
         <f t="shared" si="6"/>
@@ -12949,20 +12957,20 @@
     </row>
     <row r="361">
       <c r="A361" s="5" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="J361" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K361" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/20_01.png</v>
       </c>
       <c r="L361" s="4" t="s">
-        <v>925</v>
+        <v>536</v>
       </c>
       <c r="M361" s="8" t="s">
         <v>21</v>
@@ -12971,20 +12979,20 @@
     </row>
     <row r="362">
       <c r="A362" s="5" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J362" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K362" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/20_02.png</v>
       </c>
       <c r="L362" s="4" t="s">
-        <v>925</v>
+        <v>536</v>
       </c>
       <c r="M362" s="8" t="s">
         <v>22</v>
@@ -12993,20 +13001,20 @@
     </row>
     <row r="363">
       <c r="A363" s="5" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J363" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K363" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/20_03.png</v>
       </c>
       <c r="L363" s="4" t="s">
-        <v>925</v>
+        <v>536</v>
       </c>
       <c r="M363" s="8" t="s">
         <v>30</v>
@@ -13015,20 +13023,20 @@
     </row>
     <row r="364">
       <c r="A364" s="5" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="J364" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K364" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/20_04.png</v>
       </c>
       <c r="L364" s="4" t="s">
-        <v>925</v>
+        <v>536</v>
       </c>
       <c r="M364" s="8" t="s">
         <v>38</v>
@@ -13037,20 +13045,20 @@
     </row>
     <row r="365">
       <c r="A365" s="5" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="J365" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K365" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/20_05.png</v>
       </c>
       <c r="L365" s="4" t="s">
-        <v>925</v>
+        <v>536</v>
       </c>
       <c r="M365" s="8" t="s">
         <v>47</v>
@@ -13059,20 +13067,20 @@
     </row>
     <row r="366">
       <c r="A366" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I366" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J366" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K366" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_01.png</v>
       </c>
       <c r="L366" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M366" s="8" t="s">
         <v>21</v>
@@ -13081,20 +13089,20 @@
     </row>
     <row r="367">
       <c r="A367" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>933</v>
       </c>
       <c r="J367" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K367" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_02.png</v>
       </c>
       <c r="L367" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M367" s="8" t="s">
         <v>22</v>
@@ -13103,20 +13111,20 @@
     </row>
     <row r="368">
       <c r="A368" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>934</v>
       </c>
       <c r="J368" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K368" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_03.png</v>
       </c>
       <c r="L368" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M368" s="8" t="s">
         <v>30</v>
@@ -13125,20 +13133,20 @@
     </row>
     <row r="369">
       <c r="A369" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>935</v>
       </c>
       <c r="J369" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K369" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_04.png</v>
       </c>
       <c r="L369" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M369" s="8" t="s">
         <v>38</v>
@@ -13147,20 +13155,20 @@
     </row>
     <row r="370">
       <c r="A370" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>936</v>
       </c>
       <c r="J370" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K370" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_05.png</v>
       </c>
       <c r="L370" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M370" s="8" t="s">
         <v>47</v>
@@ -13169,20 +13177,20 @@
     </row>
     <row r="371">
       <c r="A371" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>937</v>
       </c>
       <c r="J371" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K371" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_06.png</v>
       </c>
       <c r="L371" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M371" s="8" t="s">
         <v>55</v>
@@ -13191,20 +13199,20 @@
     </row>
     <row r="372">
       <c r="A372" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>938</v>
       </c>
       <c r="J372" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K372" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_07.png</v>
       </c>
       <c r="L372" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M372" s="8" t="s">
         <v>63</v>
@@ -13213,20 +13221,20 @@
     </row>
     <row r="373">
       <c r="A373" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>939</v>
       </c>
       <c r="J373" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K373" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_08.png</v>
       </c>
       <c r="L373" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M373" s="8" t="s">
         <v>70</v>
@@ -13235,20 +13243,20 @@
     </row>
     <row r="374">
       <c r="A374" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>940</v>
       </c>
       <c r="J374" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K374" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_09.png</v>
       </c>
       <c r="L374" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M374" s="8" t="s">
         <v>77</v>
@@ -13257,20 +13265,20 @@
     </row>
     <row r="375">
       <c r="A375" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>941</v>
       </c>
       <c r="J375" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K375" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_10.png</v>
       </c>
       <c r="L375" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M375" s="8" t="s">
         <v>85</v>
@@ -13279,20 +13287,20 @@
     </row>
     <row r="376">
       <c r="A376" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>942</v>
       </c>
       <c r="J376" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K376" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_11.png</v>
       </c>
       <c r="L376" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M376" s="3">
         <v>11.0</v>
@@ -13301,20 +13309,20 @@
     </row>
     <row r="377">
       <c r="A377" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>943</v>
       </c>
       <c r="J377" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K377" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_12.png</v>
       </c>
       <c r="L377" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M377" s="3">
         <v>12.0</v>
@@ -13323,20 +13331,20 @@
     </row>
     <row r="378">
       <c r="A378" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>944</v>
       </c>
       <c r="J378" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K378" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_13.png</v>
       </c>
       <c r="L378" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M378" s="3">
         <v>13.0</v>
@@ -13345,20 +13353,20 @@
     </row>
     <row r="379">
       <c r="A379" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>945</v>
       </c>
       <c r="J379" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K379" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_14.png</v>
       </c>
       <c r="L379" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M379" s="3">
         <v>14.0</v>
@@ -13367,20 +13375,20 @@
     </row>
     <row r="380">
       <c r="A380" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>946</v>
       </c>
       <c r="J380" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K380" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_15.png</v>
       </c>
       <c r="L380" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M380" s="3">
         <v>15.0</v>
@@ -13389,20 +13397,20 @@
     </row>
     <row r="381">
       <c r="A381" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>947</v>
       </c>
       <c r="J381" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K381" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_16.png</v>
       </c>
       <c r="L381" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M381" s="3">
         <v>16.0</v>
@@ -13411,20 +13419,20 @@
     </row>
     <row r="382">
       <c r="A382" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>948</v>
       </c>
       <c r="J382" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K382" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_17.png</v>
       </c>
       <c r="L382" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M382" s="3">
         <v>17.0</v>
@@ -13433,20 +13441,20 @@
     </row>
     <row r="383">
       <c r="A383" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>949</v>
       </c>
       <c r="J383" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K383" s="1" t="str">
         <f t="shared" si="1"/>
         <v>/21_18.png</v>
       </c>
       <c r="L383" s="4" t="s">
-        <v>932</v>
+        <v>543</v>
       </c>
       <c r="M383" s="8">
         <f>M382+1</f>
@@ -13462,7 +13470,7 @@
         <v>951</v>
       </c>
       <c r="J384" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K384" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13484,7 +13492,7 @@
         <v>953</v>
       </c>
       <c r="J385" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K385" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13506,7 +13514,7 @@
         <v>954</v>
       </c>
       <c r="J386" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K386" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13528,7 +13536,7 @@
         <v>955</v>
       </c>
       <c r="J387" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K387" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13550,7 +13558,7 @@
         <v>956</v>
       </c>
       <c r="J388" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K388" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13572,7 +13580,7 @@
         <v>957</v>
       </c>
       <c r="J389" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K389" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13594,7 +13602,7 @@
         <v>958</v>
       </c>
       <c r="J390" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K390" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13616,7 +13624,7 @@
         <v>959</v>
       </c>
       <c r="J391" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K391" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13638,7 +13646,7 @@
         <v>961</v>
       </c>
       <c r="J392" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K392" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13660,7 +13668,7 @@
         <v>963</v>
       </c>
       <c r="J393" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K393" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13682,7 +13690,7 @@
         <v>964</v>
       </c>
       <c r="J394" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K394" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13704,7 +13712,7 @@
         <v>965</v>
       </c>
       <c r="J395" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K395" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13726,7 +13734,7 @@
         <v>966</v>
       </c>
       <c r="J396" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K396" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13748,7 +13756,7 @@
         <v>967</v>
       </c>
       <c r="J397" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K397" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13770,7 +13778,7 @@
         <v>969</v>
       </c>
       <c r="J398" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K398" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13792,7 +13800,7 @@
         <v>971</v>
       </c>
       <c r="J399" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K399" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13814,7 +13822,7 @@
         <v>972</v>
       </c>
       <c r="J400" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K400" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13836,7 +13844,7 @@
         <v>973</v>
       </c>
       <c r="J401" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K401" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13858,7 +13866,7 @@
         <v>974</v>
       </c>
       <c r="J402" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K402" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13880,7 +13888,7 @@
         <v>975</v>
       </c>
       <c r="J403" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K403" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13902,7 +13910,7 @@
         <v>976</v>
       </c>
       <c r="J404" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K404" s="1" t="str">
         <f t="shared" si="1"/>
@@ -13924,7 +13932,7 @@
         <v>977</v>
       </c>
       <c r="J405" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K405" s="1" t="str">
         <f t="shared" si="1"/>
@@ -17535,293 +17543,302 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J124"/>
-    <hyperlink r:id="rId2" ref="J125"/>
-    <hyperlink r:id="rId3" ref="J126"/>
-    <hyperlink r:id="rId4" ref="J127"/>
-    <hyperlink r:id="rId5" ref="J128"/>
-    <hyperlink r:id="rId6" ref="J129"/>
-    <hyperlink r:id="rId7" ref="J130"/>
-    <hyperlink r:id="rId8" ref="J131"/>
-    <hyperlink r:id="rId9" ref="J132"/>
-    <hyperlink r:id="rId10" ref="J133"/>
-    <hyperlink r:id="rId11" ref="J134"/>
-    <hyperlink r:id="rId12" ref="J135"/>
-    <hyperlink r:id="rId13" ref="J136"/>
-    <hyperlink r:id="rId14" ref="J137"/>
-    <hyperlink r:id="rId15" ref="J138"/>
-    <hyperlink r:id="rId16" ref="J139"/>
-    <hyperlink r:id="rId17" ref="J140"/>
-    <hyperlink r:id="rId18" ref="J141"/>
-    <hyperlink r:id="rId19" ref="J142"/>
-    <hyperlink r:id="rId20" ref="J143"/>
-    <hyperlink r:id="rId21" ref="J144"/>
-    <hyperlink r:id="rId22" ref="J145"/>
-    <hyperlink r:id="rId23" ref="J146"/>
-    <hyperlink r:id="rId24" ref="J147"/>
-    <hyperlink r:id="rId25" ref="J148"/>
-    <hyperlink r:id="rId26" ref="J149"/>
-    <hyperlink r:id="rId27" ref="J150"/>
-    <hyperlink r:id="rId28" ref="J151"/>
-    <hyperlink r:id="rId29" ref="J152"/>
-    <hyperlink r:id="rId30" ref="J153"/>
-    <hyperlink r:id="rId31" ref="J154"/>
-    <hyperlink r:id="rId32" ref="J155"/>
-    <hyperlink r:id="rId33" ref="J156"/>
-    <hyperlink r:id="rId34" ref="J157"/>
-    <hyperlink r:id="rId35" ref="J158"/>
-    <hyperlink r:id="rId36" ref="J159"/>
-    <hyperlink r:id="rId37" ref="J160"/>
-    <hyperlink r:id="rId38" ref="J161"/>
-    <hyperlink r:id="rId39" ref="J162"/>
-    <hyperlink r:id="rId40" ref="J163"/>
-    <hyperlink r:id="rId41" ref="J164"/>
-    <hyperlink r:id="rId42" ref="J165"/>
-    <hyperlink r:id="rId43" ref="J166"/>
-    <hyperlink r:id="rId44" ref="J167"/>
-    <hyperlink r:id="rId45" ref="J168"/>
-    <hyperlink r:id="rId46" ref="J169"/>
-    <hyperlink r:id="rId47" ref="J170"/>
-    <hyperlink r:id="rId48" ref="J171"/>
-    <hyperlink r:id="rId49" ref="J172"/>
-    <hyperlink r:id="rId50" ref="J173"/>
-    <hyperlink r:id="rId51" ref="J174"/>
-    <hyperlink r:id="rId52" ref="J175"/>
-    <hyperlink r:id="rId53" ref="J176"/>
-    <hyperlink r:id="rId54" ref="J177"/>
-    <hyperlink r:id="rId55" ref="J178"/>
-    <hyperlink r:id="rId56" ref="J179"/>
-    <hyperlink r:id="rId57" ref="J180"/>
-    <hyperlink r:id="rId58" ref="J181"/>
-    <hyperlink r:id="rId59" ref="J182"/>
-    <hyperlink r:id="rId60" ref="J183"/>
-    <hyperlink r:id="rId61" ref="J184"/>
-    <hyperlink r:id="rId62" ref="J185"/>
-    <hyperlink r:id="rId63" ref="J186"/>
-    <hyperlink r:id="rId64" ref="J187"/>
-    <hyperlink r:id="rId65" ref="J188"/>
-    <hyperlink r:id="rId66" ref="J189"/>
-    <hyperlink r:id="rId67" ref="J190"/>
-    <hyperlink r:id="rId68" ref="J191"/>
-    <hyperlink r:id="rId69" ref="J192"/>
-    <hyperlink r:id="rId70" ref="J193"/>
-    <hyperlink r:id="rId71" ref="J194"/>
-    <hyperlink r:id="rId72" ref="J195"/>
-    <hyperlink r:id="rId73" ref="J196"/>
-    <hyperlink r:id="rId74" ref="J197"/>
-    <hyperlink r:id="rId75" ref="J198"/>
-    <hyperlink r:id="rId76" ref="J199"/>
-    <hyperlink r:id="rId77" ref="J200"/>
-    <hyperlink r:id="rId78" ref="J201"/>
-    <hyperlink r:id="rId79" ref="J202"/>
-    <hyperlink r:id="rId80" ref="J203"/>
-    <hyperlink r:id="rId81" ref="J204"/>
-    <hyperlink r:id="rId82" ref="J205"/>
-    <hyperlink r:id="rId83" ref="J206"/>
-    <hyperlink r:id="rId84" ref="J207"/>
-    <hyperlink r:id="rId85" ref="J208"/>
-    <hyperlink r:id="rId86" ref="J209"/>
-    <hyperlink r:id="rId87" ref="J210"/>
-    <hyperlink r:id="rId88" ref="J211"/>
-    <hyperlink r:id="rId89" ref="J212"/>
-    <hyperlink r:id="rId90" ref="J213"/>
-    <hyperlink r:id="rId91" ref="J214"/>
-    <hyperlink r:id="rId92" ref="J215"/>
-    <hyperlink r:id="rId93" ref="J216"/>
-    <hyperlink r:id="rId94" ref="J217"/>
-    <hyperlink r:id="rId95" ref="J218"/>
-    <hyperlink r:id="rId96" ref="J219"/>
-    <hyperlink r:id="rId97" ref="J220"/>
-    <hyperlink r:id="rId98" ref="J221"/>
-    <hyperlink r:id="rId99" ref="J222"/>
-    <hyperlink r:id="rId100" ref="J223"/>
-    <hyperlink r:id="rId101" ref="J224"/>
-    <hyperlink r:id="rId102" ref="J225"/>
-    <hyperlink r:id="rId103" ref="J226"/>
-    <hyperlink r:id="rId104" ref="J227"/>
-    <hyperlink r:id="rId105" ref="J228"/>
-    <hyperlink r:id="rId106" ref="J229"/>
-    <hyperlink r:id="rId107" ref="J230"/>
-    <hyperlink r:id="rId108" ref="J231"/>
-    <hyperlink r:id="rId109" ref="J232"/>
-    <hyperlink r:id="rId110" ref="J233"/>
-    <hyperlink r:id="rId111" ref="J234"/>
-    <hyperlink r:id="rId112" ref="J235"/>
-    <hyperlink r:id="rId113" ref="J236"/>
-    <hyperlink r:id="rId114" ref="J237"/>
-    <hyperlink r:id="rId115" ref="J238"/>
-    <hyperlink r:id="rId116" ref="J239"/>
-    <hyperlink r:id="rId117" ref="J240"/>
-    <hyperlink r:id="rId118" ref="J241"/>
-    <hyperlink r:id="rId119" ref="J242"/>
-    <hyperlink r:id="rId120" ref="J243"/>
-    <hyperlink r:id="rId121" ref="J244"/>
-    <hyperlink r:id="rId122" ref="J245"/>
-    <hyperlink r:id="rId123" ref="J246"/>
-    <hyperlink r:id="rId124" ref="J247"/>
-    <hyperlink r:id="rId125" ref="J248"/>
-    <hyperlink r:id="rId126" ref="J249"/>
-    <hyperlink r:id="rId127" ref="J250"/>
-    <hyperlink r:id="rId128" ref="J251"/>
-    <hyperlink r:id="rId129" ref="J252"/>
-    <hyperlink r:id="rId130" ref="J253"/>
-    <hyperlink r:id="rId131" ref="J254"/>
-    <hyperlink r:id="rId132" ref="J255"/>
-    <hyperlink r:id="rId133" ref="J256"/>
-    <hyperlink r:id="rId134" ref="J257"/>
-    <hyperlink r:id="rId135" ref="J258"/>
-    <hyperlink r:id="rId136" ref="J259"/>
-    <hyperlink r:id="rId137" ref="J260"/>
-    <hyperlink r:id="rId138" ref="J261"/>
-    <hyperlink r:id="rId139" ref="J262"/>
-    <hyperlink r:id="rId140" ref="J263"/>
-    <hyperlink r:id="rId141" ref="J264"/>
-    <hyperlink r:id="rId142" ref="J265"/>
-    <hyperlink r:id="rId143" ref="J266"/>
-    <hyperlink r:id="rId144" ref="J267"/>
-    <hyperlink r:id="rId145" ref="J268"/>
-    <hyperlink r:id="rId146" ref="J269"/>
-    <hyperlink r:id="rId147" ref="J270"/>
-    <hyperlink r:id="rId148" ref="J271"/>
-    <hyperlink r:id="rId149" ref="J272"/>
-    <hyperlink r:id="rId150" ref="J273"/>
-    <hyperlink r:id="rId151" ref="J274"/>
-    <hyperlink r:id="rId152" ref="J275"/>
-    <hyperlink r:id="rId153" ref="J276"/>
-    <hyperlink r:id="rId154" ref="J277"/>
-    <hyperlink r:id="rId155" ref="J278"/>
-    <hyperlink r:id="rId156" ref="J279"/>
-    <hyperlink r:id="rId157" ref="J280"/>
-    <hyperlink r:id="rId158" ref="J281"/>
-    <hyperlink r:id="rId159" ref="J282"/>
-    <hyperlink r:id="rId160" ref="J283"/>
-    <hyperlink r:id="rId161" ref="J284"/>
-    <hyperlink r:id="rId162" ref="J285"/>
-    <hyperlink r:id="rId163" ref="J286"/>
-    <hyperlink r:id="rId164" ref="J287"/>
-    <hyperlink r:id="rId165" ref="J288"/>
-    <hyperlink r:id="rId166" ref="J289"/>
-    <hyperlink r:id="rId167" ref="J290"/>
-    <hyperlink r:id="rId168" ref="J291"/>
-    <hyperlink r:id="rId169" ref="J292"/>
-    <hyperlink r:id="rId170" ref="J293"/>
-    <hyperlink r:id="rId171" ref="J294"/>
-    <hyperlink r:id="rId172" ref="J295"/>
-    <hyperlink r:id="rId173" ref="J296"/>
-    <hyperlink r:id="rId174" ref="J297"/>
-    <hyperlink r:id="rId175" ref="J298"/>
-    <hyperlink r:id="rId176" ref="J299"/>
-    <hyperlink r:id="rId177" ref="J300"/>
-    <hyperlink r:id="rId178" ref="J301"/>
-    <hyperlink r:id="rId179" ref="J302"/>
-    <hyperlink r:id="rId180" ref="J303"/>
-    <hyperlink r:id="rId181" ref="J304"/>
-    <hyperlink r:id="rId182" ref="J305"/>
-    <hyperlink r:id="rId183" ref="J306"/>
-    <hyperlink r:id="rId184" ref="J307"/>
-    <hyperlink r:id="rId185" ref="J308"/>
-    <hyperlink r:id="rId186" ref="J309"/>
-    <hyperlink r:id="rId187" ref="J310"/>
-    <hyperlink r:id="rId188" ref="J311"/>
-    <hyperlink r:id="rId189" ref="J312"/>
-    <hyperlink r:id="rId190" ref="J313"/>
-    <hyperlink r:id="rId191" ref="J314"/>
-    <hyperlink r:id="rId192" ref="J315"/>
-    <hyperlink r:id="rId193" ref="J316"/>
-    <hyperlink r:id="rId194" ref="J317"/>
-    <hyperlink r:id="rId195" ref="J318"/>
-    <hyperlink r:id="rId196" ref="J319"/>
-    <hyperlink r:id="rId197" ref="J320"/>
-    <hyperlink r:id="rId198" ref="J321"/>
-    <hyperlink r:id="rId199" ref="J322"/>
-    <hyperlink r:id="rId200" ref="J323"/>
-    <hyperlink r:id="rId201" ref="J324"/>
-    <hyperlink r:id="rId202" ref="J325"/>
-    <hyperlink r:id="rId203" ref="J326"/>
-    <hyperlink r:id="rId204" ref="J327"/>
-    <hyperlink r:id="rId205" ref="J328"/>
-    <hyperlink r:id="rId206" ref="J329"/>
-    <hyperlink r:id="rId207" ref="J330"/>
-    <hyperlink r:id="rId208" ref="J331"/>
-    <hyperlink r:id="rId209" ref="J332"/>
-    <hyperlink r:id="rId210" ref="J333"/>
-    <hyperlink r:id="rId211" ref="J334"/>
-    <hyperlink r:id="rId212" ref="J335"/>
-    <hyperlink r:id="rId213" ref="J336"/>
-    <hyperlink r:id="rId214" ref="J337"/>
-    <hyperlink r:id="rId215" ref="J338"/>
-    <hyperlink r:id="rId216" ref="J339"/>
-    <hyperlink r:id="rId217" ref="J340"/>
-    <hyperlink r:id="rId218" ref="J341"/>
-    <hyperlink r:id="rId219" ref="J342"/>
-    <hyperlink r:id="rId220" ref="J343"/>
-    <hyperlink r:id="rId221" ref="J344"/>
-    <hyperlink r:id="rId222" ref="J345"/>
-    <hyperlink r:id="rId223" ref="J346"/>
-    <hyperlink r:id="rId224" ref="J347"/>
-    <hyperlink r:id="rId225" ref="J348"/>
-    <hyperlink r:id="rId226" ref="J349"/>
-    <hyperlink r:id="rId227" ref="J350"/>
-    <hyperlink r:id="rId228" ref="J351"/>
-    <hyperlink r:id="rId229" ref="J352"/>
-    <hyperlink r:id="rId230" ref="J353"/>
-    <hyperlink r:id="rId231" ref="J354"/>
-    <hyperlink r:id="rId232" ref="J355"/>
-    <hyperlink r:id="rId233" ref="J356"/>
-    <hyperlink r:id="rId234" ref="J357"/>
-    <hyperlink r:id="rId235" ref="J358"/>
-    <hyperlink r:id="rId236" ref="J359"/>
-    <hyperlink r:id="rId237" ref="J360"/>
-    <hyperlink r:id="rId238" ref="J361"/>
-    <hyperlink r:id="rId239" ref="J362"/>
-    <hyperlink r:id="rId240" ref="J363"/>
-    <hyperlink r:id="rId241" ref="J364"/>
-    <hyperlink r:id="rId242" ref="J365"/>
-    <hyperlink r:id="rId243" ref="J366"/>
-    <hyperlink r:id="rId244" ref="J367"/>
-    <hyperlink r:id="rId245" ref="J368"/>
-    <hyperlink r:id="rId246" ref="J369"/>
-    <hyperlink r:id="rId247" ref="J370"/>
-    <hyperlink r:id="rId248" ref="J371"/>
-    <hyperlink r:id="rId249" ref="J372"/>
-    <hyperlink r:id="rId250" ref="J373"/>
-    <hyperlink r:id="rId251" ref="J374"/>
-    <hyperlink r:id="rId252" ref="J375"/>
-    <hyperlink r:id="rId253" ref="J376"/>
-    <hyperlink r:id="rId254" ref="J377"/>
-    <hyperlink r:id="rId255" ref="J378"/>
-    <hyperlink r:id="rId256" ref="J379"/>
-    <hyperlink r:id="rId257" ref="J380"/>
-    <hyperlink r:id="rId258" ref="J381"/>
-    <hyperlink r:id="rId259" ref="J382"/>
-    <hyperlink r:id="rId260" ref="J383"/>
-    <hyperlink r:id="rId261" ref="J384"/>
-    <hyperlink r:id="rId262" ref="J385"/>
-    <hyperlink r:id="rId263" ref="J386"/>
-    <hyperlink r:id="rId264" ref="J387"/>
-    <hyperlink r:id="rId265" ref="J388"/>
-    <hyperlink r:id="rId266" ref="J389"/>
-    <hyperlink r:id="rId267" ref="J390"/>
-    <hyperlink r:id="rId268" ref="J391"/>
-    <hyperlink r:id="rId269" ref="J392"/>
-    <hyperlink r:id="rId270" ref="J393"/>
-    <hyperlink r:id="rId271" ref="J394"/>
-    <hyperlink r:id="rId272" ref="J395"/>
-    <hyperlink r:id="rId273" ref="J396"/>
-    <hyperlink r:id="rId274" ref="J397"/>
-    <hyperlink r:id="rId275" ref="J398"/>
-    <hyperlink r:id="rId276" ref="J399"/>
-    <hyperlink r:id="rId277" ref="J400"/>
-    <hyperlink r:id="rId278" ref="J401"/>
-    <hyperlink r:id="rId279" ref="J402"/>
-    <hyperlink r:id="rId280" ref="J403"/>
-    <hyperlink r:id="rId281" ref="J404"/>
-    <hyperlink r:id="rId282" ref="J405"/>
+    <hyperlink r:id="rId1" ref="I86"/>
+    <hyperlink r:id="rId2" ref="I87"/>
+    <hyperlink r:id="rId3" ref="I88"/>
+    <hyperlink r:id="rId4" ref="I89"/>
+    <hyperlink r:id="rId5" ref="I90"/>
+    <hyperlink r:id="rId6" ref="I91"/>
+    <hyperlink r:id="rId7" ref="I92"/>
+    <hyperlink r:id="rId8" ref="I93"/>
+    <hyperlink r:id="rId9" ref="I94"/>
+    <hyperlink r:id="rId10" ref="J124"/>
+    <hyperlink r:id="rId11" ref="J125"/>
+    <hyperlink r:id="rId12" ref="J126"/>
+    <hyperlink r:id="rId13" ref="J127"/>
+    <hyperlink r:id="rId14" ref="J128"/>
+    <hyperlink r:id="rId15" ref="J129"/>
+    <hyperlink r:id="rId16" ref="J130"/>
+    <hyperlink r:id="rId17" ref="J131"/>
+    <hyperlink r:id="rId18" ref="J132"/>
+    <hyperlink r:id="rId19" ref="J133"/>
+    <hyperlink r:id="rId20" ref="J134"/>
+    <hyperlink r:id="rId21" ref="J135"/>
+    <hyperlink r:id="rId22" ref="J136"/>
+    <hyperlink r:id="rId23" ref="J137"/>
+    <hyperlink r:id="rId24" ref="J138"/>
+    <hyperlink r:id="rId25" ref="J139"/>
+    <hyperlink r:id="rId26" ref="J140"/>
+    <hyperlink r:id="rId27" ref="J141"/>
+    <hyperlink r:id="rId28" ref="J142"/>
+    <hyperlink r:id="rId29" ref="J143"/>
+    <hyperlink r:id="rId30" ref="J144"/>
+    <hyperlink r:id="rId31" ref="J145"/>
+    <hyperlink r:id="rId32" ref="J146"/>
+    <hyperlink r:id="rId33" ref="J147"/>
+    <hyperlink r:id="rId34" ref="J148"/>
+    <hyperlink r:id="rId35" ref="J149"/>
+    <hyperlink r:id="rId36" ref="J150"/>
+    <hyperlink r:id="rId37" ref="J151"/>
+    <hyperlink r:id="rId38" ref="J152"/>
+    <hyperlink r:id="rId39" ref="J153"/>
+    <hyperlink r:id="rId40" ref="J154"/>
+    <hyperlink r:id="rId41" ref="J155"/>
+    <hyperlink r:id="rId42" ref="J156"/>
+    <hyperlink r:id="rId43" ref="J157"/>
+    <hyperlink r:id="rId44" ref="J158"/>
+    <hyperlink r:id="rId45" ref="J159"/>
+    <hyperlink r:id="rId46" ref="J160"/>
+    <hyperlink r:id="rId47" ref="J161"/>
+    <hyperlink r:id="rId48" ref="J162"/>
+    <hyperlink r:id="rId49" ref="J163"/>
+    <hyperlink r:id="rId50" ref="J164"/>
+    <hyperlink r:id="rId51" ref="J165"/>
+    <hyperlink r:id="rId52" ref="J166"/>
+    <hyperlink r:id="rId53" ref="J167"/>
+    <hyperlink r:id="rId54" ref="J168"/>
+    <hyperlink r:id="rId55" ref="J169"/>
+    <hyperlink r:id="rId56" ref="J170"/>
+    <hyperlink r:id="rId57" ref="J171"/>
+    <hyperlink r:id="rId58" ref="J172"/>
+    <hyperlink r:id="rId59" ref="J173"/>
+    <hyperlink r:id="rId60" ref="J174"/>
+    <hyperlink r:id="rId61" ref="J175"/>
+    <hyperlink r:id="rId62" ref="J176"/>
+    <hyperlink r:id="rId63" ref="J177"/>
+    <hyperlink r:id="rId64" ref="J178"/>
+    <hyperlink r:id="rId65" ref="J179"/>
+    <hyperlink r:id="rId66" ref="J180"/>
+    <hyperlink r:id="rId67" ref="J181"/>
+    <hyperlink r:id="rId68" ref="J182"/>
+    <hyperlink r:id="rId69" ref="J183"/>
+    <hyperlink r:id="rId70" ref="J184"/>
+    <hyperlink r:id="rId71" ref="J185"/>
+    <hyperlink r:id="rId72" ref="J186"/>
+    <hyperlink r:id="rId73" ref="J187"/>
+    <hyperlink r:id="rId74" ref="J188"/>
+    <hyperlink r:id="rId75" ref="J189"/>
+    <hyperlink r:id="rId76" ref="J190"/>
+    <hyperlink r:id="rId77" ref="J191"/>
+    <hyperlink r:id="rId78" ref="J192"/>
+    <hyperlink r:id="rId79" ref="J193"/>
+    <hyperlink r:id="rId80" ref="J194"/>
+    <hyperlink r:id="rId81" ref="J195"/>
+    <hyperlink r:id="rId82" ref="J196"/>
+    <hyperlink r:id="rId83" ref="J197"/>
+    <hyperlink r:id="rId84" ref="J198"/>
+    <hyperlink r:id="rId85" ref="J199"/>
+    <hyperlink r:id="rId86" ref="J200"/>
+    <hyperlink r:id="rId87" ref="J201"/>
+    <hyperlink r:id="rId88" ref="J202"/>
+    <hyperlink r:id="rId89" ref="J203"/>
+    <hyperlink r:id="rId90" ref="J204"/>
+    <hyperlink r:id="rId91" ref="J205"/>
+    <hyperlink r:id="rId92" ref="J206"/>
+    <hyperlink r:id="rId93" ref="J207"/>
+    <hyperlink r:id="rId94" ref="J208"/>
+    <hyperlink r:id="rId95" ref="J209"/>
+    <hyperlink r:id="rId96" ref="J210"/>
+    <hyperlink r:id="rId97" ref="J211"/>
+    <hyperlink r:id="rId98" ref="J212"/>
+    <hyperlink r:id="rId99" ref="J213"/>
+    <hyperlink r:id="rId100" ref="J214"/>
+    <hyperlink r:id="rId101" ref="J215"/>
+    <hyperlink r:id="rId102" ref="J216"/>
+    <hyperlink r:id="rId103" ref="J217"/>
+    <hyperlink r:id="rId104" ref="J218"/>
+    <hyperlink r:id="rId105" ref="J219"/>
+    <hyperlink r:id="rId106" ref="J220"/>
+    <hyperlink r:id="rId107" ref="J221"/>
+    <hyperlink r:id="rId108" ref="J222"/>
+    <hyperlink r:id="rId109" ref="J223"/>
+    <hyperlink r:id="rId110" ref="J224"/>
+    <hyperlink r:id="rId111" ref="J225"/>
+    <hyperlink r:id="rId112" ref="J226"/>
+    <hyperlink r:id="rId113" ref="J227"/>
+    <hyperlink r:id="rId114" ref="J228"/>
+    <hyperlink r:id="rId115" ref="J229"/>
+    <hyperlink r:id="rId116" ref="J230"/>
+    <hyperlink r:id="rId117" ref="J231"/>
+    <hyperlink r:id="rId118" ref="J232"/>
+    <hyperlink r:id="rId119" ref="J233"/>
+    <hyperlink r:id="rId120" ref="J234"/>
+    <hyperlink r:id="rId121" ref="J235"/>
+    <hyperlink r:id="rId122" ref="J236"/>
+    <hyperlink r:id="rId123" ref="J237"/>
+    <hyperlink r:id="rId124" ref="J238"/>
+    <hyperlink r:id="rId125" ref="J239"/>
+    <hyperlink r:id="rId126" ref="J240"/>
+    <hyperlink r:id="rId127" ref="J241"/>
+    <hyperlink r:id="rId128" ref="J242"/>
+    <hyperlink r:id="rId129" ref="J243"/>
+    <hyperlink r:id="rId130" ref="J244"/>
+    <hyperlink r:id="rId131" ref="J245"/>
+    <hyperlink r:id="rId132" ref="J246"/>
+    <hyperlink r:id="rId133" ref="J247"/>
+    <hyperlink r:id="rId134" ref="J248"/>
+    <hyperlink r:id="rId135" ref="J249"/>
+    <hyperlink r:id="rId136" ref="J250"/>
+    <hyperlink r:id="rId137" ref="J251"/>
+    <hyperlink r:id="rId138" ref="J252"/>
+    <hyperlink r:id="rId139" ref="J253"/>
+    <hyperlink r:id="rId140" ref="J254"/>
+    <hyperlink r:id="rId141" ref="J255"/>
+    <hyperlink r:id="rId142" ref="J256"/>
+    <hyperlink r:id="rId143" ref="J257"/>
+    <hyperlink r:id="rId144" ref="J258"/>
+    <hyperlink r:id="rId145" ref="J259"/>
+    <hyperlink r:id="rId146" ref="J260"/>
+    <hyperlink r:id="rId147" ref="J261"/>
+    <hyperlink r:id="rId148" ref="J262"/>
+    <hyperlink r:id="rId149" ref="J263"/>
+    <hyperlink r:id="rId150" ref="J264"/>
+    <hyperlink r:id="rId151" ref="J265"/>
+    <hyperlink r:id="rId152" ref="J266"/>
+    <hyperlink r:id="rId153" ref="J267"/>
+    <hyperlink r:id="rId154" ref="J268"/>
+    <hyperlink r:id="rId155" ref="J269"/>
+    <hyperlink r:id="rId156" ref="J270"/>
+    <hyperlink r:id="rId157" ref="J271"/>
+    <hyperlink r:id="rId158" ref="J272"/>
+    <hyperlink r:id="rId159" ref="J273"/>
+    <hyperlink r:id="rId160" ref="J274"/>
+    <hyperlink r:id="rId161" ref="J275"/>
+    <hyperlink r:id="rId162" ref="J276"/>
+    <hyperlink r:id="rId163" ref="J277"/>
+    <hyperlink r:id="rId164" ref="J278"/>
+    <hyperlink r:id="rId165" ref="J279"/>
+    <hyperlink r:id="rId166" ref="J280"/>
+    <hyperlink r:id="rId167" ref="J281"/>
+    <hyperlink r:id="rId168" ref="J282"/>
+    <hyperlink r:id="rId169" ref="J283"/>
+    <hyperlink r:id="rId170" ref="J284"/>
+    <hyperlink r:id="rId171" ref="J285"/>
+    <hyperlink r:id="rId172" ref="J286"/>
+    <hyperlink r:id="rId173" ref="J287"/>
+    <hyperlink r:id="rId174" ref="J288"/>
+    <hyperlink r:id="rId175" ref="J289"/>
+    <hyperlink r:id="rId176" ref="J290"/>
+    <hyperlink r:id="rId177" ref="J291"/>
+    <hyperlink r:id="rId178" ref="J292"/>
+    <hyperlink r:id="rId179" ref="J293"/>
+    <hyperlink r:id="rId180" ref="J294"/>
+    <hyperlink r:id="rId181" ref="J295"/>
+    <hyperlink r:id="rId182" ref="J296"/>
+    <hyperlink r:id="rId183" ref="J297"/>
+    <hyperlink r:id="rId184" ref="J298"/>
+    <hyperlink r:id="rId185" ref="J299"/>
+    <hyperlink r:id="rId186" ref="J300"/>
+    <hyperlink r:id="rId187" ref="J301"/>
+    <hyperlink r:id="rId188" ref="J302"/>
+    <hyperlink r:id="rId189" ref="J303"/>
+    <hyperlink r:id="rId190" ref="J304"/>
+    <hyperlink r:id="rId191" ref="J305"/>
+    <hyperlink r:id="rId192" ref="J306"/>
+    <hyperlink r:id="rId193" ref="J307"/>
+    <hyperlink r:id="rId194" ref="J308"/>
+    <hyperlink r:id="rId195" ref="J309"/>
+    <hyperlink r:id="rId196" ref="J310"/>
+    <hyperlink r:id="rId197" ref="J311"/>
+    <hyperlink r:id="rId198" ref="J312"/>
+    <hyperlink r:id="rId199" ref="J313"/>
+    <hyperlink r:id="rId200" ref="J314"/>
+    <hyperlink r:id="rId201" ref="J315"/>
+    <hyperlink r:id="rId202" ref="J316"/>
+    <hyperlink r:id="rId203" ref="J317"/>
+    <hyperlink r:id="rId204" ref="J318"/>
+    <hyperlink r:id="rId205" ref="J319"/>
+    <hyperlink r:id="rId206" ref="J320"/>
+    <hyperlink r:id="rId207" ref="J321"/>
+    <hyperlink r:id="rId208" ref="J322"/>
+    <hyperlink r:id="rId209" ref="J323"/>
+    <hyperlink r:id="rId210" ref="J324"/>
+    <hyperlink r:id="rId211" ref="J325"/>
+    <hyperlink r:id="rId212" ref="J326"/>
+    <hyperlink r:id="rId213" ref="J327"/>
+    <hyperlink r:id="rId214" ref="J328"/>
+    <hyperlink r:id="rId215" ref="J329"/>
+    <hyperlink r:id="rId216" ref="J330"/>
+    <hyperlink r:id="rId217" ref="J331"/>
+    <hyperlink r:id="rId218" ref="J332"/>
+    <hyperlink r:id="rId219" ref="J333"/>
+    <hyperlink r:id="rId220" ref="J334"/>
+    <hyperlink r:id="rId221" ref="J335"/>
+    <hyperlink r:id="rId222" ref="J336"/>
+    <hyperlink r:id="rId223" ref="J337"/>
+    <hyperlink r:id="rId224" ref="J338"/>
+    <hyperlink r:id="rId225" ref="J339"/>
+    <hyperlink r:id="rId226" ref="J340"/>
+    <hyperlink r:id="rId227" ref="J341"/>
+    <hyperlink r:id="rId228" ref="J342"/>
+    <hyperlink r:id="rId229" ref="J343"/>
+    <hyperlink r:id="rId230" ref="J344"/>
+    <hyperlink r:id="rId231" ref="J345"/>
+    <hyperlink r:id="rId232" ref="J346"/>
+    <hyperlink r:id="rId233" ref="J347"/>
+    <hyperlink r:id="rId234" ref="J348"/>
+    <hyperlink r:id="rId235" ref="J349"/>
+    <hyperlink r:id="rId236" ref="J350"/>
+    <hyperlink r:id="rId237" ref="J351"/>
+    <hyperlink r:id="rId238" ref="J352"/>
+    <hyperlink r:id="rId239" ref="J353"/>
+    <hyperlink r:id="rId240" ref="J354"/>
+    <hyperlink r:id="rId241" ref="J355"/>
+    <hyperlink r:id="rId242" ref="J356"/>
+    <hyperlink r:id="rId243" ref="J357"/>
+    <hyperlink r:id="rId244" ref="J358"/>
+    <hyperlink r:id="rId245" ref="J359"/>
+    <hyperlink r:id="rId246" ref="J360"/>
+    <hyperlink r:id="rId247" ref="J361"/>
+    <hyperlink r:id="rId248" ref="J362"/>
+    <hyperlink r:id="rId249" ref="J363"/>
+    <hyperlink r:id="rId250" ref="J364"/>
+    <hyperlink r:id="rId251" ref="J365"/>
+    <hyperlink r:id="rId252" ref="J366"/>
+    <hyperlink r:id="rId253" ref="J367"/>
+    <hyperlink r:id="rId254" ref="J368"/>
+    <hyperlink r:id="rId255" ref="J369"/>
+    <hyperlink r:id="rId256" ref="J370"/>
+    <hyperlink r:id="rId257" ref="J371"/>
+    <hyperlink r:id="rId258" ref="J372"/>
+    <hyperlink r:id="rId259" ref="J373"/>
+    <hyperlink r:id="rId260" ref="J374"/>
+    <hyperlink r:id="rId261" ref="J375"/>
+    <hyperlink r:id="rId262" ref="J376"/>
+    <hyperlink r:id="rId263" ref="J377"/>
+    <hyperlink r:id="rId264" ref="J378"/>
+    <hyperlink r:id="rId265" ref="J379"/>
+    <hyperlink r:id="rId266" ref="J380"/>
+    <hyperlink r:id="rId267" ref="J381"/>
+    <hyperlink r:id="rId268" ref="J382"/>
+    <hyperlink r:id="rId269" ref="J383"/>
+    <hyperlink r:id="rId270" ref="J384"/>
+    <hyperlink r:id="rId271" ref="J385"/>
+    <hyperlink r:id="rId272" ref="J386"/>
+    <hyperlink r:id="rId273" ref="J387"/>
+    <hyperlink r:id="rId274" ref="J388"/>
+    <hyperlink r:id="rId275" ref="J389"/>
+    <hyperlink r:id="rId276" ref="J390"/>
+    <hyperlink r:id="rId277" ref="J391"/>
+    <hyperlink r:id="rId278" ref="J392"/>
+    <hyperlink r:id="rId279" ref="J393"/>
+    <hyperlink r:id="rId280" ref="J394"/>
+    <hyperlink r:id="rId281" ref="J395"/>
+    <hyperlink r:id="rId282" ref="J396"/>
+    <hyperlink r:id="rId283" ref="J397"/>
+    <hyperlink r:id="rId284" ref="J398"/>
+    <hyperlink r:id="rId285" ref="J399"/>
+    <hyperlink r:id="rId286" ref="J400"/>
+    <hyperlink r:id="rId287" ref="J401"/>
+    <hyperlink r:id="rId288" ref="J402"/>
+    <hyperlink r:id="rId289" ref="J403"/>
+    <hyperlink r:id="rId290" ref="J404"/>
+    <hyperlink r:id="rId291" ref="J405"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId283"/>
+  <drawing r:id="rId292"/>
 </worksheet>
 </file>
 

--- a/計画-事例集.xlsx
+++ b/計画-事例集.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1446">
   <si>
     <t>ジャンル</t>
   </si>
@@ -2436,38 +2436,7 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//08_09.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
+    <t>9_学校・幼稚園・保育園 [16問]</t>
   </si>
   <si>
     <t>公立はこだて未来大学</t>
@@ -2485,40 +2454,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_01.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>立命館大学大阪いばらきキャンパス</t>
   </si>
   <si>
@@ -2531,40 +2466,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_02.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>東浦町立緒川小学校</t>
   </si>
   <si>
@@ -2577,40 +2478,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_03.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>宮代町立笠原小学校</t>
   </si>
   <si>
@@ -2623,40 +2490,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_04.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>浪合村立浪合学校</t>
   </si>
   <si>
@@ -2669,40 +2502,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_05.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>千葉市立瀬小学校</t>
   </si>
   <si>
@@ -2715,40 +2514,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_06.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>目黒区立宮前小学校</t>
   </si>
   <si>
@@ -2758,40 +2523,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_07.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>棚倉町立社川小学校</t>
   </si>
   <si>
@@ -2804,40 +2535,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_08.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>加藤学園暁秀初等学校</t>
   </si>
   <si>
@@ -2850,40 +2547,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_09.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>福岡市立博多小学校</t>
   </si>
   <si>
@@ -2896,40 +2559,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_10.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>迫桜高等学校</t>
   </si>
   <si>
@@ -2942,40 +2571,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_11.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>福島県立郡山養護学校</t>
   </si>
   <si>
@@ -2988,40 +2583,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_12.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>三春町立岩江幼稚園</t>
   </si>
   <si>
@@ -3034,40 +2595,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_13.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>東金市立嶺南幼稚園</t>
   </si>
   <si>
@@ -3077,40 +2604,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_14.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>豊川保育園</t>
   </si>
   <si>
@@ -3120,40 +2613,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_15.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>学校・幼稚園・保育園</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [16</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ふじようちえん</t>
   </si>
   <si>
@@ -3166,38 +2625,7 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//09_16.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
+    <t>10_図書館 [15問]</t>
   </si>
   <si>
     <t>日野市立中央図書館</t>
@@ -3212,40 +2640,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_01.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>金沢市立玉川図書館</t>
   </si>
   <si>
@@ -3258,40 +2652,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_02.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>朝霞市立図書館本館</t>
   </si>
   <si>
@@ -3304,40 +2664,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_03.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>苅田町立図書館本館</t>
   </si>
   <si>
@@ -3350,40 +2676,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_04.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>国立国会図書館関西館</t>
   </si>
   <si>
@@ -3396,40 +2688,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_05.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ぎふメディアコスモス</t>
   </si>
   <si>
@@ -3442,40 +2700,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_06.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>国際子ども図書館</t>
   </si>
   <si>
@@ -3488,40 +2712,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_07.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>まちとしょテラソ</t>
   </si>
   <si>
@@ -3534,40 +2724,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_08.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>フランス国立図書館</t>
   </si>
   <si>
@@ -3577,40 +2733,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_09.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>英国図書館セントパンクラス館</t>
   </si>
   <si>
@@ -3620,40 +2742,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_10.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ベルリン自由大学図書館</t>
   </si>
   <si>
@@ -3663,40 +2751,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_11.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>新アレクサンドリア図書館</t>
   </si>
   <si>
@@ -3709,40 +2763,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_12.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>シアトル中央図書館</t>
   </si>
   <si>
@@ -3755,40 +2775,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_13.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ストックホルム市立図書館</t>
   </si>
   <si>
@@ -3801,40 +2787,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_14.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>図書館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [15</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>デンマーク王立図書館</t>
   </si>
   <si>
@@ -3847,38 +2799,7 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//10_15.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
+    <t>11_美術館・博物館 [22問]</t>
   </si>
   <si>
     <t>潟博物館（水の駅　ビュー福島潟）</t>
@@ -3893,40 +2814,6 @@
     <t>11</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>世田谷美術館</t>
   </si>
   <si>
@@ -3936,40 +2823,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_02.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>海の博物館</t>
   </si>
   <si>
@@ -3979,40 +2832,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_03.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>東京国立博物本館</t>
   </si>
   <si>
@@ -4022,40 +2841,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_04.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>金沢21世紀美術館</t>
   </si>
   <si>
@@ -4065,40 +2850,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_05.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>丸亀市猪熊弦一郎現代美術館</t>
   </si>
   <si>
@@ -4108,40 +2859,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_06.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>八千代市立博物館（未来の森ミュージアム）</t>
   </si>
   <si>
@@ -4151,40 +2868,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_07.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>広島市現代美術館</t>
   </si>
   <si>
@@ -4194,40 +2877,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_08.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>大阪府立近つ飛鳥博物館</t>
   </si>
   <si>
@@ -4237,40 +2886,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_09.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>太田市美術館・図書館</t>
   </si>
   <si>
@@ -4280,40 +2895,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_10.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ふくしま海洋科学館　アクアマリンふくしま</t>
   </si>
   <si>
@@ -4323,40 +2904,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_11.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>富弘美術館</t>
   </si>
   <si>
@@ -4366,40 +2913,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_12.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ポーラ美術館</t>
   </si>
   <si>
@@ -4409,40 +2922,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_13.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>京都市京セラ美術館</t>
   </si>
   <si>
@@ -4452,40 +2931,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_14.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>豊島美術館</t>
   </si>
   <si>
@@ -4495,40 +2940,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_15.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ビルバオ・グッゲンハイム美術館</t>
   </si>
   <si>
@@ -4538,40 +2949,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_16.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ニューヨーク近代美術館</t>
   </si>
   <si>
@@ -4581,40 +2958,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_17.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ロサンゼルス近代美術館</t>
   </si>
   <si>
@@ -4624,40 +2967,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_18.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>フォートワース現代美術館</t>
   </si>
   <si>
@@ -4667,40 +2976,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_19.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>アスペン美術館</t>
   </si>
   <si>
@@ -4710,40 +2985,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_20.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>グッゲンハイム美術館</t>
   </si>
   <si>
@@ -4753,40 +2994,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_21.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>美術館・博物館</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [22</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>キンベル美術館</t>
   </si>
   <si>
@@ -4796,38 +3003,7 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_22.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>医療施設</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [5</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
+    <t>12_医療施設 [5問]</t>
   </si>
   <si>
     <t>旧神戸市立中央市民病院</t>
@@ -4842,40 +3018,6 @@
     <t>12</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>医療施設</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [5</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>聖路加国際病院</t>
   </si>
   <si>
@@ -4885,40 +3027,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//12_02.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>医療施設</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [5</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>大牟田市立総合病院</t>
   </si>
   <si>
@@ -4928,40 +3036,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//12_03.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>医療施設</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [5</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>西神戸医療センター</t>
   </si>
   <si>
@@ -4971,40 +3045,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//12_04.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>医療施設</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [5</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>国立がんセンター中央病院・通院治療センター</t>
   </si>
   <si>
@@ -5014,38 +3054,7 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//12_05.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>高齢者施設等</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [4</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
+    <t>13_高齢者施設等 [4問]</t>
   </si>
   <si>
     <t>カリタス21</t>
@@ -5060,40 +3069,6 @@
     <t>13</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>高齢者施設等</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [4</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>こもれびの家</t>
   </si>
   <si>
@@ -5103,40 +3078,6 @@
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//13_02.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>高齢者施設等</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [4</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ケアハウスほっとほっと</t>
   </si>
   <si>
@@ -5144,40 +3085,6 @@
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//13_03.png</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>高齢者施設等</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> [4</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="ＭＳ ゴシック"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>問</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>]</t>
-    </r>
   </si>
   <si>
     <t>ケアタウンたかのす</t>
@@ -9670,7 +7577,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -9694,6 +7601,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -16632,7 +14542,7 @@
       <c r="O223" s="3"/>
     </row>
     <row r="224" ht="18.0" customHeight="1">
-      <c r="A224" s="4" t="s">
+      <c r="A224" s="8" t="s">
         <v>790</v>
       </c>
       <c r="B224" s="4" t="s">
@@ -16666,20 +14576,20 @@
       <c r="O224" s="3"/>
     </row>
     <row r="225" ht="18.0" customHeight="1">
-      <c r="A225" s="4" t="s">
+      <c r="A225" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="B225" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="E225" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="E225" s="1" t="s">
+      <c r="G225" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="G225" s="7" t="s">
+      <c r="I225" s="1" t="s">
         <v>799</v>
-      </c>
-      <c r="I225" s="1" t="s">
-        <v>800</v>
       </c>
       <c r="J225" s="6" t="s">
         <v>671</v>
@@ -16697,20 +14607,20 @@
       <c r="O225" s="3"/>
     </row>
     <row r="226" ht="18.0" customHeight="1">
-      <c r="A226" s="4" t="s">
+      <c r="A226" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="G226" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="E226" s="1" t="s">
+      <c r="I226" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="G226" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="I226" s="1" t="s">
-        <v>805</v>
       </c>
       <c r="J226" s="6" t="s">
         <v>671</v>
@@ -16728,20 +14638,20 @@
       <c r="O226" s="3"/>
     </row>
     <row r="227" ht="18.0" customHeight="1">
-      <c r="A227" s="4" t="s">
+      <c r="A227" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="G227" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="I227" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="E227" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="G227" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="I227" s="1" t="s">
-        <v>810</v>
       </c>
       <c r="J227" s="6" t="s">
         <v>671</v>
@@ -16759,20 +14669,20 @@
       <c r="O227" s="3"/>
     </row>
     <row r="228" ht="18.0" customHeight="1">
-      <c r="A228" s="4" t="s">
+      <c r="A228" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="G228" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="I228" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="G228" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="I228" s="1" t="s">
-        <v>815</v>
       </c>
       <c r="J228" s="6" t="s">
         <v>671</v>
@@ -16790,20 +14700,20 @@
       <c r="O228" s="3"/>
     </row>
     <row r="229" ht="18.0" customHeight="1">
-      <c r="A229" s="4" t="s">
-        <v>816</v>
+      <c r="A229" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="G229" s="7" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="J229" s="6" t="s">
         <v>671</v>
@@ -16821,20 +14731,20 @@
       <c r="O229" s="3"/>
     </row>
     <row r="230" ht="18.0" customHeight="1">
-      <c r="A230" s="4" t="s">
-        <v>821</v>
+      <c r="A230" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>559</v>
       </c>
       <c r="G230" s="7" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="J230" s="6" t="s">
         <v>671</v>
@@ -16852,20 +14762,20 @@
       <c r="O230" s="3"/>
     </row>
     <row r="231" ht="18.0" customHeight="1">
-      <c r="A231" s="4" t="s">
-        <v>825</v>
+      <c r="A231" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="J231" s="6" t="s">
         <v>671</v>
@@ -16883,20 +14793,20 @@
       <c r="O231" s="3"/>
     </row>
     <row r="232" ht="18.0" customHeight="1">
-      <c r="A232" s="4" t="s">
-        <v>830</v>
+      <c r="A232" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="G232" s="7" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="J232" s="6" t="s">
         <v>671</v>
@@ -16914,20 +14824,20 @@
       <c r="O232" s="3"/>
     </row>
     <row r="233" ht="18.0" customHeight="1">
-      <c r="A233" s="4" t="s">
-        <v>835</v>
+      <c r="A233" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="G233" s="7" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="J233" s="6" t="s">
         <v>671</v>
@@ -16945,20 +14855,20 @@
       <c r="O233" s="3"/>
     </row>
     <row r="234" ht="18.0" customHeight="1">
-      <c r="A234" s="4" t="s">
-        <v>840</v>
+      <c r="A234" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="G234" s="7" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="J234" s="6" t="s">
         <v>671</v>
@@ -16976,20 +14886,20 @@
       <c r="O234" s="3"/>
     </row>
     <row r="235" ht="18.0" customHeight="1">
-      <c r="A235" s="4" t="s">
-        <v>845</v>
+      <c r="A235" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>846</v>
+        <v>835</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="G235" s="7" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="J235" s="6" t="s">
         <v>671</v>
@@ -17007,20 +14917,20 @@
       <c r="O235" s="3"/>
     </row>
     <row r="236" ht="18.0" customHeight="1">
-      <c r="A236" s="4" t="s">
-        <v>850</v>
+      <c r="A236" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="G236" s="7" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="J236" s="6" t="s">
         <v>671</v>
@@ -17038,20 +14948,20 @@
       <c r="O236" s="3"/>
     </row>
     <row r="237" ht="18.0" customHeight="1">
-      <c r="A237" s="4" t="s">
-        <v>855</v>
+      <c r="A237" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="G237" s="7" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="J237" s="6" t="s">
         <v>671</v>
@@ -17069,20 +14979,20 @@
       <c r="O237" s="3"/>
     </row>
     <row r="238" ht="18.0" customHeight="1">
-      <c r="A238" s="4" t="s">
-        <v>859</v>
+      <c r="A238" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>559</v>
       </c>
       <c r="G238" s="7" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="J238" s="6" t="s">
         <v>671</v>
@@ -17100,20 +15010,20 @@
       <c r="O238" s="3"/>
     </row>
     <row r="239" ht="18.0" customHeight="1">
-      <c r="A239" s="4" t="s">
-        <v>863</v>
+      <c r="A239" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="G239" s="7" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="J239" s="6" t="s">
         <v>671</v>
@@ -17131,20 +15041,20 @@
       <c r="O239" s="3"/>
     </row>
     <row r="240" ht="18.0" customHeight="1">
-      <c r="A240" s="4" t="s">
-        <v>868</v>
+      <c r="A240" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="G240" s="7" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="J240" s="6" t="s">
         <v>671</v>
@@ -17162,20 +15072,20 @@
       <c r="O240" s="3"/>
     </row>
     <row r="241" ht="18.0" customHeight="1">
-      <c r="A241" s="4" t="s">
-        <v>873</v>
+      <c r="A241" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>874</v>
+        <v>858</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="G241" s="7" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="J241" s="6" t="s">
         <v>671</v>
@@ -17193,20 +15103,20 @@
       <c r="O241" s="3"/>
     </row>
     <row r="242" ht="18.0" customHeight="1">
-      <c r="A242" s="4" t="s">
-        <v>878</v>
+      <c r="A242" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>880</v>
+        <v>863</v>
       </c>
       <c r="G242" s="7" t="s">
-        <v>881</v>
+        <v>864</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="J242" s="6" t="s">
         <v>671</v>
@@ -17224,20 +15134,20 @@
       <c r="O242" s="3"/>
     </row>
     <row r="243" ht="18.0" customHeight="1">
-      <c r="A243" s="4" t="s">
-        <v>883</v>
+      <c r="A243" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>885</v>
+        <v>867</v>
       </c>
       <c r="G243" s="7" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>887</v>
+        <v>869</v>
       </c>
       <c r="J243" s="6" t="s">
         <v>671</v>
@@ -17255,20 +15165,20 @@
       <c r="O243" s="3"/>
     </row>
     <row r="244" ht="18.0" customHeight="1">
-      <c r="A244" s="4" t="s">
-        <v>888</v>
+      <c r="A244" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="G244" s="7" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="J244" s="6" t="s">
         <v>671</v>
@@ -17286,20 +15196,20 @@
       <c r="O244" s="3"/>
     </row>
     <row r="245" ht="18.0" customHeight="1">
-      <c r="A245" s="4" t="s">
-        <v>893</v>
+      <c r="A245" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="G245" s="7" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="J245" s="6" t="s">
         <v>671</v>
@@ -17317,20 +15227,20 @@
       <c r="O245" s="3"/>
     </row>
     <row r="246" ht="18.0" customHeight="1">
-      <c r="A246" s="4" t="s">
-        <v>898</v>
+      <c r="A246" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>900</v>
+        <v>879</v>
       </c>
       <c r="G246" s="7" t="s">
-        <v>901</v>
+        <v>880</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>902</v>
+        <v>881</v>
       </c>
       <c r="J246" s="6" t="s">
         <v>671</v>
@@ -17348,20 +15258,20 @@
       <c r="O246" s="3"/>
     </row>
     <row r="247" ht="18.0" customHeight="1">
-      <c r="A247" s="4" t="s">
-        <v>903</v>
+      <c r="A247" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>904</v>
+        <v>882</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>905</v>
+        <v>883</v>
       </c>
       <c r="G247" s="7" t="s">
-        <v>906</v>
+        <v>884</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>907</v>
+        <v>885</v>
       </c>
       <c r="J247" s="6" t="s">
         <v>671</v>
@@ -17379,20 +15289,20 @@
       <c r="O247" s="3"/>
     </row>
     <row r="248" ht="18.0" customHeight="1">
-      <c r="A248" s="4" t="s">
-        <v>908</v>
+      <c r="A248" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>399</v>
       </c>
       <c r="G248" s="7" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="J248" s="6" t="s">
         <v>671</v>
@@ -17410,20 +15320,20 @@
       <c r="O248" s="3"/>
     </row>
     <row r="249" ht="18.0" customHeight="1">
-      <c r="A249" s="4" t="s">
-        <v>912</v>
+      <c r="A249" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>423</v>
       </c>
       <c r="G249" s="7" t="s">
-        <v>914</v>
+        <v>890</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>915</v>
+        <v>891</v>
       </c>
       <c r="J249" s="6" t="s">
         <v>671</v>
@@ -17441,20 +15351,20 @@
       <c r="O249" s="3"/>
     </row>
     <row r="250" ht="18.0" customHeight="1">
-      <c r="A250" s="4" t="s">
-        <v>916</v>
+      <c r="A250" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>917</v>
+        <v>892</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>299</v>
       </c>
       <c r="G250" s="7" t="s">
-        <v>918</v>
+        <v>893</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>919</v>
+        <v>894</v>
       </c>
       <c r="J250" s="6" t="s">
         <v>671</v>
@@ -17472,20 +15382,20 @@
       <c r="O250" s="3"/>
     </row>
     <row r="251" ht="18.0" customHeight="1">
-      <c r="A251" s="4" t="s">
-        <v>920</v>
+      <c r="A251" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>921</v>
+        <v>895</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>922</v>
+        <v>896</v>
       </c>
       <c r="G251" s="7" t="s">
-        <v>923</v>
+        <v>897</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>924</v>
+        <v>898</v>
       </c>
       <c r="J251" s="6" t="s">
         <v>671</v>
@@ -17503,20 +15413,20 @@
       <c r="O251" s="3"/>
     </row>
     <row r="252" ht="18.0" customHeight="1">
-      <c r="A252" s="4" t="s">
-        <v>925</v>
+      <c r="A252" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>926</v>
+        <v>899</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>927</v>
+        <v>900</v>
       </c>
       <c r="G252" s="7" t="s">
-        <v>928</v>
+        <v>901</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>929</v>
+        <v>902</v>
       </c>
       <c r="J252" s="6" t="s">
         <v>671</v>
@@ -17534,20 +15444,20 @@
       <c r="O252" s="3"/>
     </row>
     <row r="253" ht="18.0" customHeight="1">
-      <c r="A253" s="4" t="s">
-        <v>930</v>
+      <c r="A253" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>931</v>
+        <v>903</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>932</v>
+        <v>904</v>
       </c>
       <c r="G253" s="7" t="s">
-        <v>933</v>
+        <v>905</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>934</v>
+        <v>906</v>
       </c>
       <c r="J253" s="6" t="s">
         <v>671</v>
@@ -17565,20 +15475,20 @@
       <c r="O253" s="3"/>
     </row>
     <row r="254" ht="18.0" customHeight="1">
-      <c r="A254" s="4" t="s">
-        <v>935</v>
+      <c r="A254" s="8" t="s">
+        <v>853</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>936</v>
+        <v>907</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>937</v>
+        <v>908</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>938</v>
+        <v>909</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>939</v>
+        <v>910</v>
       </c>
       <c r="J254" s="6" t="s">
         <v>671</v>
@@ -17596,18 +15506,18 @@
       <c r="O254" s="3"/>
     </row>
     <row r="255" ht="18.0" customHeight="1">
-      <c r="A255" s="4" t="s">
-        <v>940</v>
+      <c r="A255" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>941</v>
+        <v>912</v>
       </c>
       <c r="E255" s="1"/>
       <c r="G255" s="7" t="s">
-        <v>942</v>
+        <v>913</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>943</v>
+        <v>914</v>
       </c>
       <c r="J255" s="6" t="s">
         <v>671</v>
@@ -17617,7 +15527,7 @@
         <v>/11_01.png</v>
       </c>
       <c r="L255" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M255" s="3" t="s">
         <v>21</v>
@@ -17625,17 +15535,17 @@
       <c r="O255" s="3"/>
     </row>
     <row r="256" ht="18.0" customHeight="1">
-      <c r="A256" s="4" t="s">
-        <v>945</v>
+      <c r="A256" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>946</v>
+        <v>916</v>
       </c>
       <c r="G256" s="7" t="s">
-        <v>947</v>
+        <v>917</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>948</v>
+        <v>918</v>
       </c>
       <c r="J256" s="6" t="s">
         <v>671</v>
@@ -17645,7 +15555,7 @@
         <v>/11_02.png</v>
       </c>
       <c r="L256" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M256" s="3" t="s">
         <v>22</v>
@@ -17653,17 +15563,17 @@
       <c r="O256" s="3"/>
     </row>
     <row r="257" ht="18.0" customHeight="1">
-      <c r="A257" s="4" t="s">
-        <v>949</v>
+      <c r="A257" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>950</v>
+        <v>919</v>
       </c>
       <c r="G257" s="7" t="s">
-        <v>951</v>
+        <v>920</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>952</v>
+        <v>921</v>
       </c>
       <c r="J257" s="6" t="s">
         <v>671</v>
@@ -17673,7 +15583,7 @@
         <v>/11_03.png</v>
       </c>
       <c r="L257" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M257" s="3" t="s">
         <v>30</v>
@@ -17681,17 +15591,17 @@
       <c r="O257" s="3"/>
     </row>
     <row r="258" ht="18.0" customHeight="1">
-      <c r="A258" s="4" t="s">
-        <v>953</v>
+      <c r="A258" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>954</v>
+        <v>922</v>
       </c>
       <c r="G258" s="7" t="s">
-        <v>955</v>
+        <v>923</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>956</v>
+        <v>924</v>
       </c>
       <c r="J258" s="6" t="s">
         <v>671</v>
@@ -17701,7 +15611,7 @@
         <v>/11_04.png</v>
       </c>
       <c r="L258" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M258" s="3" t="s">
         <v>38</v>
@@ -17709,17 +15619,17 @@
       <c r="O258" s="3"/>
     </row>
     <row r="259" ht="18.0" customHeight="1">
-      <c r="A259" s="4" t="s">
-        <v>957</v>
+      <c r="A259" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>958</v>
+        <v>925</v>
       </c>
       <c r="G259" s="7" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>960</v>
+        <v>927</v>
       </c>
       <c r="J259" s="6" t="s">
         <v>671</v>
@@ -17729,7 +15639,7 @@
         <v>/11_05.png</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M259" s="3" t="s">
         <v>47</v>
@@ -17737,17 +15647,17 @@
       <c r="O259" s="3"/>
     </row>
     <row r="260" ht="18.0" customHeight="1">
-      <c r="A260" s="4" t="s">
-        <v>961</v>
+      <c r="A260" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>962</v>
+        <v>928</v>
       </c>
       <c r="G260" s="7" t="s">
-        <v>963</v>
+        <v>929</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>964</v>
+        <v>930</v>
       </c>
       <c r="J260" s="6" t="s">
         <v>671</v>
@@ -17757,7 +15667,7 @@
         <v>/11_06.png</v>
       </c>
       <c r="L260" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M260" s="3" t="s">
         <v>55</v>
@@ -17765,17 +15675,17 @@
       <c r="O260" s="3"/>
     </row>
     <row r="261" ht="18.0" customHeight="1">
-      <c r="A261" s="4" t="s">
-        <v>965</v>
+      <c r="A261" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>966</v>
+        <v>931</v>
       </c>
       <c r="G261" s="7" t="s">
-        <v>967</v>
+        <v>932</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>968</v>
+        <v>933</v>
       </c>
       <c r="J261" s="6" t="s">
         <v>671</v>
@@ -17785,7 +15695,7 @@
         <v>/11_07.png</v>
       </c>
       <c r="L261" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M261" s="3" t="s">
         <v>63</v>
@@ -17793,17 +15703,17 @@
       <c r="O261" s="3"/>
     </row>
     <row r="262" ht="18.0" customHeight="1">
-      <c r="A262" s="4" t="s">
-        <v>969</v>
+      <c r="A262" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="G262" s="7" t="s">
-        <v>971</v>
+        <v>935</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>972</v>
+        <v>936</v>
       </c>
       <c r="J262" s="6" t="s">
         <v>671</v>
@@ -17813,7 +15723,7 @@
         <v>/11_08.png</v>
       </c>
       <c r="L262" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M262" s="3" t="s">
         <v>70</v>
@@ -17821,17 +15731,17 @@
       <c r="O262" s="3"/>
     </row>
     <row r="263" ht="18.0" customHeight="1">
-      <c r="A263" s="4" t="s">
-        <v>973</v>
+      <c r="A263" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>974</v>
+        <v>937</v>
       </c>
       <c r="G263" s="7" t="s">
-        <v>975</v>
+        <v>938</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>976</v>
+        <v>939</v>
       </c>
       <c r="J263" s="6" t="s">
         <v>671</v>
@@ -17841,7 +15751,7 @@
         <v>/11_09.png</v>
       </c>
       <c r="L263" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M263" s="3" t="s">
         <v>77</v>
@@ -17849,17 +15759,17 @@
       <c r="O263" s="3"/>
     </row>
     <row r="264" ht="18.0" customHeight="1">
-      <c r="A264" s="4" t="s">
-        <v>977</v>
+      <c r="A264" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>978</v>
+        <v>940</v>
       </c>
       <c r="G264" s="7" t="s">
-        <v>979</v>
+        <v>941</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>980</v>
+        <v>942</v>
       </c>
       <c r="J264" s="6" t="s">
         <v>671</v>
@@ -17869,7 +15779,7 @@
         <v>/11_10.png</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M264" s="3" t="s">
         <v>85</v>
@@ -17877,17 +15787,17 @@
       <c r="O264" s="3"/>
     </row>
     <row r="265" ht="18.0" customHeight="1">
-      <c r="A265" s="4" t="s">
-        <v>981</v>
+      <c r="A265" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>982</v>
+        <v>943</v>
       </c>
       <c r="G265" s="7" t="s">
-        <v>983</v>
+        <v>944</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>984</v>
+        <v>945</v>
       </c>
       <c r="J265" s="6" t="s">
         <v>671</v>
@@ -17897,7 +15807,7 @@
         <v>/11_11.png</v>
       </c>
       <c r="L265" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M265" s="3">
         <v>11.0</v>
@@ -17905,17 +15815,17 @@
       <c r="O265" s="3"/>
     </row>
     <row r="266" ht="18.0" customHeight="1">
-      <c r="A266" s="4" t="s">
-        <v>985</v>
+      <c r="A266" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>986</v>
+        <v>946</v>
       </c>
       <c r="G266" s="7" t="s">
-        <v>987</v>
+        <v>947</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>988</v>
+        <v>948</v>
       </c>
       <c r="J266" s="6" t="s">
         <v>671</v>
@@ -17925,7 +15835,7 @@
         <v>/11_12.png</v>
       </c>
       <c r="L266" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M266" s="3">
         <v>12.0</v>
@@ -17933,17 +15843,17 @@
       <c r="O266" s="3"/>
     </row>
     <row r="267" ht="18.0" customHeight="1">
-      <c r="A267" s="4" t="s">
-        <v>989</v>
+      <c r="A267" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>990</v>
+        <v>949</v>
       </c>
       <c r="G267" s="7" t="s">
-        <v>991</v>
+        <v>950</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>992</v>
+        <v>951</v>
       </c>
       <c r="J267" s="6" t="s">
         <v>671</v>
@@ -17953,7 +15863,7 @@
         <v>/11_13.png</v>
       </c>
       <c r="L267" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M267" s="3">
         <v>13.0</v>
@@ -17961,17 +15871,17 @@
       <c r="O267" s="3"/>
     </row>
     <row r="268" ht="18.0" customHeight="1">
-      <c r="A268" s="4" t="s">
-        <v>993</v>
+      <c r="A268" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>994</v>
+        <v>952</v>
       </c>
       <c r="G268" s="7" t="s">
-        <v>995</v>
+        <v>953</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>996</v>
+        <v>954</v>
       </c>
       <c r="J268" s="6" t="s">
         <v>671</v>
@@ -17981,7 +15891,7 @@
         <v>/11_14.png</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M268" s="3">
         <v>14.0</v>
@@ -17989,17 +15899,17 @@
       <c r="O268" s="3"/>
     </row>
     <row r="269" ht="18.0" customHeight="1">
-      <c r="A269" s="4" t="s">
-        <v>997</v>
+      <c r="A269" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>998</v>
+        <v>955</v>
       </c>
       <c r="G269" s="7" t="s">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>1000</v>
+        <v>957</v>
       </c>
       <c r="J269" s="6" t="s">
         <v>671</v>
@@ -18009,7 +15919,7 @@
         <v>/11_15.png</v>
       </c>
       <c r="L269" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M269" s="3">
         <v>15.0</v>
@@ -18017,17 +15927,17 @@
       <c r="O269" s="3"/>
     </row>
     <row r="270" ht="18.0" customHeight="1">
-      <c r="A270" s="4" t="s">
-        <v>1001</v>
+      <c r="A270" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1002</v>
+        <v>958</v>
       </c>
       <c r="G270" s="7" t="s">
-        <v>1003</v>
+        <v>959</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>1004</v>
+        <v>960</v>
       </c>
       <c r="J270" s="6" t="s">
         <v>671</v>
@@ -18037,7 +15947,7 @@
         <v>/11_16.png</v>
       </c>
       <c r="L270" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M270" s="3">
         <v>16.0</v>
@@ -18045,17 +15955,17 @@
       <c r="O270" s="3"/>
     </row>
     <row r="271" ht="18.0" customHeight="1">
-      <c r="A271" s="4" t="s">
-        <v>1005</v>
+      <c r="A271" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1006</v>
+        <v>961</v>
       </c>
       <c r="G271" s="7" t="s">
-        <v>1007</v>
+        <v>962</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>1008</v>
+        <v>963</v>
       </c>
       <c r="J271" s="6" t="s">
         <v>671</v>
@@ -18065,7 +15975,7 @@
         <v>/11_17.png</v>
       </c>
       <c r="L271" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M271" s="3">
         <f t="shared" ref="M271:M276" si="4">M270+1</f>
@@ -18074,17 +15984,17 @@
       <c r="O271" s="3"/>
     </row>
     <row r="272" ht="18.0" customHeight="1">
-      <c r="A272" s="4" t="s">
-        <v>1009</v>
+      <c r="A272" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1010</v>
+        <v>964</v>
       </c>
       <c r="G272" s="7" t="s">
-        <v>1011</v>
+        <v>965</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>1012</v>
+        <v>966</v>
       </c>
       <c r="J272" s="6" t="s">
         <v>671</v>
@@ -18094,7 +16004,7 @@
         <v>/11_18.png</v>
       </c>
       <c r="L272" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M272" s="3">
         <f t="shared" si="4"/>
@@ -18103,17 +16013,17 @@
       <c r="O272" s="3"/>
     </row>
     <row r="273" ht="18.0" customHeight="1">
-      <c r="A273" s="4" t="s">
-        <v>1013</v>
+      <c r="A273" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1014</v>
+        <v>967</v>
       </c>
       <c r="G273" s="7" t="s">
-        <v>1015</v>
+        <v>968</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>1016</v>
+        <v>969</v>
       </c>
       <c r="J273" s="6" t="s">
         <v>671</v>
@@ -18123,7 +16033,7 @@
         <v>/11_19.png</v>
       </c>
       <c r="L273" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M273" s="3">
         <f t="shared" si="4"/>
@@ -18132,17 +16042,17 @@
       <c r="O273" s="3"/>
     </row>
     <row r="274" ht="18.0" customHeight="1">
-      <c r="A274" s="4" t="s">
-        <v>1017</v>
+      <c r="A274" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1018</v>
+        <v>970</v>
       </c>
       <c r="G274" s="7" t="s">
-        <v>1019</v>
+        <v>971</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>1020</v>
+        <v>972</v>
       </c>
       <c r="J274" s="6" t="s">
         <v>671</v>
@@ -18152,7 +16062,7 @@
         <v>/11_20.png</v>
       </c>
       <c r="L274" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M274" s="3">
         <f t="shared" si="4"/>
@@ -18161,17 +16071,17 @@
       <c r="O274" s="3"/>
     </row>
     <row r="275" ht="18.0" customHeight="1">
-      <c r="A275" s="4" t="s">
-        <v>1021</v>
+      <c r="A275" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1022</v>
+        <v>973</v>
       </c>
       <c r="G275" s="7" t="s">
-        <v>1023</v>
+        <v>974</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>1024</v>
+        <v>975</v>
       </c>
       <c r="J275" s="6" t="s">
         <v>671</v>
@@ -18181,7 +16091,7 @@
         <v>/11_21.png</v>
       </c>
       <c r="L275" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M275" s="3">
         <f t="shared" si="4"/>
@@ -18190,17 +16100,17 @@
       <c r="O275" s="3"/>
     </row>
     <row r="276" ht="18.0" customHeight="1">
-      <c r="A276" s="4" t="s">
-        <v>1025</v>
+      <c r="A276" s="8" t="s">
+        <v>911</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1026</v>
+        <v>976</v>
       </c>
       <c r="G276" s="7" t="s">
-        <v>1027</v>
+        <v>977</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1028</v>
+        <v>978</v>
       </c>
       <c r="J276" s="6" t="s">
         <v>671</v>
@@ -18210,7 +16120,7 @@
         <v>/11_22.png</v>
       </c>
       <c r="L276" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="M276" s="3">
         <f t="shared" si="4"/>
@@ -18219,17 +16129,17 @@
       <c r="O276" s="3"/>
     </row>
     <row r="277" ht="18.0" customHeight="1">
-      <c r="A277" s="4" t="s">
-        <v>1029</v>
+      <c r="A277" s="8" t="s">
+        <v>979</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>1030</v>
+        <v>980</v>
       </c>
       <c r="G277" s="7" t="s">
-        <v>1031</v>
+        <v>981</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>1032</v>
+        <v>982</v>
       </c>
       <c r="J277" s="6" t="s">
         <v>671</v>
@@ -18239,7 +16149,7 @@
         <v>/12_01.png</v>
       </c>
       <c r="L277" s="2" t="s">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="M277" s="3" t="s">
         <v>21</v>
@@ -18247,17 +16157,17 @@
       <c r="O277" s="3"/>
     </row>
     <row r="278" ht="18.0" customHeight="1">
-      <c r="A278" s="4" t="s">
-        <v>1034</v>
+      <c r="A278" s="8" t="s">
+        <v>979</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1035</v>
+        <v>984</v>
       </c>
       <c r="G278" s="7" t="s">
-        <v>1036</v>
+        <v>985</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1037</v>
+        <v>986</v>
       </c>
       <c r="J278" s="6" t="s">
         <v>671</v>
@@ -18267,7 +16177,7 @@
         <v>/12_02.png</v>
       </c>
       <c r="L278" s="2" t="s">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="M278" s="3" t="s">
         <v>22</v>
@@ -18275,17 +16185,17 @@
       <c r="O278" s="3"/>
     </row>
     <row r="279" ht="18.0" customHeight="1">
-      <c r="A279" s="4" t="s">
-        <v>1038</v>
+      <c r="A279" s="8" t="s">
+        <v>979</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1039</v>
+        <v>987</v>
       </c>
       <c r="G279" s="7" t="s">
-        <v>1040</v>
+        <v>988</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1041</v>
+        <v>989</v>
       </c>
       <c r="J279" s="6" t="s">
         <v>671</v>
@@ -18295,7 +16205,7 @@
         <v>/12_03.png</v>
       </c>
       <c r="L279" s="2" t="s">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="M279" s="3" t="s">
         <v>30</v>
@@ -18303,17 +16213,17 @@
       <c r="O279" s="3"/>
     </row>
     <row r="280" ht="18.0" customHeight="1">
-      <c r="A280" s="4" t="s">
-        <v>1042</v>
+      <c r="A280" s="8" t="s">
+        <v>979</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1043</v>
+        <v>990</v>
       </c>
       <c r="G280" s="7" t="s">
-        <v>1044</v>
+        <v>991</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>1045</v>
+        <v>992</v>
       </c>
       <c r="J280" s="6" t="s">
         <v>671</v>
@@ -18323,7 +16233,7 @@
         <v>/12_04.png</v>
       </c>
       <c r="L280" s="2" t="s">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="M280" s="3" t="s">
         <v>38</v>
@@ -18331,17 +16241,17 @@
       <c r="O280" s="3"/>
     </row>
     <row r="281" ht="18.0" customHeight="1">
-      <c r="A281" s="4" t="s">
-        <v>1046</v>
+      <c r="A281" s="8" t="s">
+        <v>979</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1047</v>
+        <v>993</v>
       </c>
       <c r="G281" s="7" t="s">
-        <v>1048</v>
+        <v>994</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>1049</v>
+        <v>995</v>
       </c>
       <c r="J281" s="6" t="s">
         <v>671</v>
@@ -18351,7 +16261,7 @@
         <v>/12_05.png</v>
       </c>
       <c r="L281" s="2" t="s">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="M281" s="3" t="s">
         <v>47</v>
@@ -18359,17 +16269,17 @@
       <c r="O281" s="3"/>
     </row>
     <row r="282" ht="18.0" customHeight="1">
-      <c r="A282" s="4" t="s">
-        <v>1050</v>
+      <c r="A282" s="8" t="s">
+        <v>996</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1051</v>
+        <v>997</v>
       </c>
       <c r="G282" s="7" t="s">
-        <v>1052</v>
+        <v>998</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>1053</v>
+        <v>999</v>
       </c>
       <c r="J282" s="6" t="s">
         <v>671</v>
@@ -18379,7 +16289,7 @@
         <v>/13_01.png</v>
       </c>
       <c r="L282" s="2" t="s">
-        <v>1054</v>
+        <v>1000</v>
       </c>
       <c r="M282" s="3" t="s">
         <v>21</v>
@@ -18387,17 +16297,17 @@
       <c r="O282" s="3"/>
     </row>
     <row r="283" ht="18.0" customHeight="1">
-      <c r="A283" s="4" t="s">
-        <v>1055</v>
+      <c r="A283" s="8" t="s">
+        <v>996</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1056</v>
+        <v>1001</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>1057</v>
+        <v>1002</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>1058</v>
+        <v>1003</v>
       </c>
       <c r="J283" s="6" t="s">
         <v>671</v>
@@ -18407,7 +16317,7 @@
         <v>/13_02.png</v>
       </c>
       <c r="L283" s="2" t="s">
-        <v>1054</v>
+        <v>1000</v>
       </c>
       <c r="M283" s="3" t="s">
         <v>22</v>
@@ -18415,17 +16325,17 @@
       <c r="O283" s="3"/>
     </row>
     <row r="284" ht="18.0" customHeight="1">
-      <c r="A284" s="4" t="s">
-        <v>1059</v>
+      <c r="A284" s="8" t="s">
+        <v>996</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1060</v>
+        <v>1004</v>
       </c>
       <c r="G284" s="7" t="s">
-        <v>1061</v>
+        <v>1005</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>1062</v>
+        <v>1006</v>
       </c>
       <c r="J284" s="6" t="s">
         <v>671</v>
@@ -18435,7 +16345,7 @@
         <v>/13_03.png</v>
       </c>
       <c r="L284" s="2" t="s">
-        <v>1054</v>
+        <v>1000</v>
       </c>
       <c r="M284" s="3" t="s">
         <v>30</v>
@@ -18443,17 +16353,17 @@
       <c r="O284" s="3"/>
     </row>
     <row r="285" ht="18.0" customHeight="1">
-      <c r="A285" s="4" t="s">
-        <v>1063</v>
+      <c r="A285" s="8" t="s">
+        <v>996</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1064</v>
+        <v>1007</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>1065</v>
+        <v>1008</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>1066</v>
+        <v>1009</v>
       </c>
       <c r="J285" s="6" t="s">
         <v>671</v>
@@ -18463,7 +16373,7 @@
         <v>/13_04.png</v>
       </c>
       <c r="L285" s="2" t="s">
-        <v>1054</v>
+        <v>1000</v>
       </c>
       <c r="M285" s="3" t="s">
         <v>38</v>
@@ -18472,16 +16382,16 @@
     </row>
     <row r="286" ht="18.0" customHeight="1">
       <c r="A286" s="4" t="s">
-        <v>1067</v>
+        <v>1010</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1068</v>
+        <v>1011</v>
       </c>
       <c r="G286" s="7" t="s">
-        <v>1069</v>
+        <v>1012</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>1070</v>
+        <v>1013</v>
       </c>
       <c r="J286" s="6" t="s">
         <v>671</v>
@@ -18491,7 +16401,7 @@
         <v>/14_01.png</v>
       </c>
       <c r="L286" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M286" s="3" t="s">
         <v>21</v>
@@ -18500,16 +16410,16 @@
     </row>
     <row r="287" ht="18.0" customHeight="1">
       <c r="A287" s="4" t="s">
-        <v>1072</v>
+        <v>1015</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1073</v>
+        <v>1016</v>
       </c>
       <c r="G287" s="7" t="s">
-        <v>1074</v>
+        <v>1017</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="J287" s="6" t="s">
         <v>671</v>
@@ -18519,7 +16429,7 @@
         <v>/14_02.png</v>
       </c>
       <c r="L287" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M287" s="3" t="s">
         <v>22</v>
@@ -18528,16 +16438,16 @@
     </row>
     <row r="288" ht="18.0" customHeight="1">
       <c r="A288" s="4" t="s">
-        <v>1076</v>
+        <v>1019</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1077</v>
+        <v>1020</v>
       </c>
       <c r="G288" s="7" t="s">
-        <v>1078</v>
+        <v>1021</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1079</v>
+        <v>1022</v>
       </c>
       <c r="J288" s="6" t="s">
         <v>671</v>
@@ -18547,7 +16457,7 @@
         <v>/14_03.png</v>
       </c>
       <c r="L288" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M288" s="3" t="s">
         <v>30</v>
@@ -18556,16 +16466,16 @@
     </row>
     <row r="289" ht="18.0" customHeight="1">
       <c r="A289" s="4" t="s">
-        <v>1080</v>
+        <v>1023</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1081</v>
+        <v>1024</v>
       </c>
       <c r="G289" s="7" t="s">
-        <v>1082</v>
+        <v>1025</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>1083</v>
+        <v>1026</v>
       </c>
       <c r="J289" s="6" t="s">
         <v>671</v>
@@ -18575,7 +16485,7 @@
         <v>/14_04.png</v>
       </c>
       <c r="L289" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M289" s="3" t="s">
         <v>38</v>
@@ -18584,16 +16494,16 @@
     </row>
     <row r="290" ht="18.0" customHeight="1">
       <c r="A290" s="4" t="s">
-        <v>1084</v>
+        <v>1027</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1085</v>
+        <v>1028</v>
       </c>
       <c r="G290" s="7" t="s">
-        <v>1086</v>
+        <v>1029</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1087</v>
+        <v>1030</v>
       </c>
       <c r="J290" s="6" t="s">
         <v>671</v>
@@ -18603,7 +16513,7 @@
         <v>/14_05.png</v>
       </c>
       <c r="L290" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M290" s="3" t="s">
         <v>47</v>
@@ -18612,16 +16522,16 @@
     </row>
     <row r="291" ht="18.0" customHeight="1">
       <c r="A291" s="4" t="s">
-        <v>1088</v>
+        <v>1031</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1089</v>
+        <v>1032</v>
       </c>
       <c r="G291" s="7" t="s">
-        <v>1090</v>
+        <v>1033</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>1091</v>
+        <v>1034</v>
       </c>
       <c r="J291" s="6" t="s">
         <v>671</v>
@@ -18631,7 +16541,7 @@
         <v>/14_06.png</v>
       </c>
       <c r="L291" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M291" s="3" t="s">
         <v>55</v>
@@ -18640,16 +16550,16 @@
     </row>
     <row r="292" ht="18.0" customHeight="1">
       <c r="A292" s="4" t="s">
-        <v>1092</v>
+        <v>1035</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1093</v>
+        <v>1036</v>
       </c>
       <c r="G292" s="7" t="s">
-        <v>1094</v>
+        <v>1037</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>1095</v>
+        <v>1038</v>
       </c>
       <c r="J292" s="6" t="s">
         <v>671</v>
@@ -18659,7 +16569,7 @@
         <v>/14_07.png</v>
       </c>
       <c r="L292" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M292" s="3" t="s">
         <v>63</v>
@@ -18668,16 +16578,16 @@
     </row>
     <row r="293" ht="18.0" customHeight="1">
       <c r="A293" s="4" t="s">
-        <v>1096</v>
+        <v>1039</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1097</v>
+        <v>1040</v>
       </c>
       <c r="G293" s="7" t="s">
-        <v>1098</v>
+        <v>1041</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>1099</v>
+        <v>1042</v>
       </c>
       <c r="J293" s="6" t="s">
         <v>671</v>
@@ -18687,7 +16597,7 @@
         <v>/14_08.png</v>
       </c>
       <c r="L293" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M293" s="3" t="s">
         <v>70</v>
@@ -18696,19 +16606,19 @@
     </row>
     <row r="294" ht="18.0" customHeight="1">
       <c r="A294" s="4" t="s">
-        <v>1100</v>
+        <v>1043</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1101</v>
+        <v>1044</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>1102</v>
+        <v>1045</v>
       </c>
       <c r="G294" s="7" t="s">
-        <v>1103</v>
+        <v>1046</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>1104</v>
+        <v>1047</v>
       </c>
       <c r="J294" s="6" t="s">
         <v>671</v>
@@ -18718,7 +16628,7 @@
         <v>/14_09.png</v>
       </c>
       <c r="L294" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M294" s="3" t="s">
         <v>77</v>
@@ -18727,19 +16637,19 @@
     </row>
     <row r="295" ht="18.0" customHeight="1">
       <c r="A295" s="4" t="s">
-        <v>1105</v>
+        <v>1048</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>1107</v>
+        <v>1050</v>
       </c>
       <c r="G295" s="7" t="s">
-        <v>1108</v>
+        <v>1051</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>1109</v>
+        <v>1052</v>
       </c>
       <c r="J295" s="6" t="s">
         <v>671</v>
@@ -18749,7 +16659,7 @@
         <v>/14_10.png</v>
       </c>
       <c r="L295" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M295" s="3" t="s">
         <v>85</v>
@@ -18758,16 +16668,16 @@
     </row>
     <row r="296" ht="18.0" customHeight="1">
       <c r="A296" s="4" t="s">
-        <v>1110</v>
+        <v>1053</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1111</v>
+        <v>1054</v>
       </c>
       <c r="G296" s="7" t="s">
-        <v>1112</v>
+        <v>1055</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>1113</v>
+        <v>1056</v>
       </c>
       <c r="J296" s="6" t="s">
         <v>671</v>
@@ -18777,7 +16687,7 @@
         <v>/14_11.png</v>
       </c>
       <c r="L296" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M296" s="3">
         <v>11.0</v>
@@ -18786,16 +16696,16 @@
     </row>
     <row r="297" ht="18.0" customHeight="1">
       <c r="A297" s="4" t="s">
-        <v>1114</v>
+        <v>1057</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1115</v>
+        <v>1058</v>
       </c>
       <c r="G297" s="7" t="s">
-        <v>1116</v>
+        <v>1059</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>1117</v>
+        <v>1060</v>
       </c>
       <c r="J297" s="6" t="s">
         <v>671</v>
@@ -18805,7 +16715,7 @@
         <v>/14_12.png</v>
       </c>
       <c r="L297" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M297" s="3">
         <v>12.0</v>
@@ -18814,16 +16724,16 @@
     </row>
     <row r="298" ht="18.0" customHeight="1">
       <c r="A298" s="4" t="s">
-        <v>1118</v>
+        <v>1061</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1119</v>
+        <v>1062</v>
       </c>
       <c r="G298" s="7" t="s">
-        <v>1120</v>
+        <v>1063</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>1121</v>
+        <v>1064</v>
       </c>
       <c r="J298" s="6" t="s">
         <v>671</v>
@@ -18833,7 +16743,7 @@
         <v>/14_13.png</v>
       </c>
       <c r="L298" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M298" s="3">
         <v>13.0</v>
@@ -18842,16 +16752,16 @@
     </row>
     <row r="299" ht="18.0" customHeight="1">
       <c r="A299" s="4" t="s">
-        <v>1122</v>
+        <v>1065</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1123</v>
+        <v>1066</v>
       </c>
       <c r="G299" s="7" t="s">
-        <v>1124</v>
+        <v>1067</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="J299" s="6" t="s">
         <v>671</v>
@@ -18861,7 +16771,7 @@
         <v>/14_14.png</v>
       </c>
       <c r="L299" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M299" s="3">
         <v>14.0</v>
@@ -18870,16 +16780,16 @@
     </row>
     <row r="300" ht="18.0" customHeight="1">
       <c r="A300" s="4" t="s">
-        <v>1126</v>
+        <v>1069</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1127</v>
+        <v>1070</v>
       </c>
       <c r="G300" s="7" t="s">
-        <v>1128</v>
+        <v>1071</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>1129</v>
+        <v>1072</v>
       </c>
       <c r="J300" s="6" t="s">
         <v>671</v>
@@ -18889,7 +16799,7 @@
         <v>/14_15.png</v>
       </c>
       <c r="L300" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M300" s="3">
         <v>15.0</v>
@@ -18898,16 +16808,16 @@
     </row>
     <row r="301" ht="18.0" customHeight="1">
       <c r="A301" s="4" t="s">
-        <v>1130</v>
+        <v>1073</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1131</v>
+        <v>1074</v>
       </c>
       <c r="G301" s="7" t="s">
-        <v>1132</v>
+        <v>1075</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>1133</v>
+        <v>1076</v>
       </c>
       <c r="J301" s="6" t="s">
         <v>671</v>
@@ -18917,7 +16827,7 @@
         <v>/14_16.png</v>
       </c>
       <c r="L301" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M301" s="3">
         <f t="shared" ref="M301:M304" si="5">M300+1</f>
@@ -18927,16 +16837,16 @@
     </row>
     <row r="302" ht="18.0" customHeight="1">
       <c r="A302" s="4" t="s">
-        <v>1134</v>
+        <v>1077</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1135</v>
+        <v>1078</v>
       </c>
       <c r="G302" s="7" t="s">
-        <v>1136</v>
+        <v>1079</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>1137</v>
+        <v>1080</v>
       </c>
       <c r="J302" s="6" t="s">
         <v>671</v>
@@ -18946,7 +16856,7 @@
         <v>/14_17.png</v>
       </c>
       <c r="L302" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M302" s="3">
         <f t="shared" si="5"/>
@@ -18956,16 +16866,16 @@
     </row>
     <row r="303" ht="18.0" customHeight="1">
       <c r="A303" s="4" t="s">
-        <v>1138</v>
+        <v>1081</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1139</v>
+        <v>1082</v>
       </c>
       <c r="G303" s="7" t="s">
-        <v>1140</v>
+        <v>1083</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>1141</v>
+        <v>1084</v>
       </c>
       <c r="J303" s="6" t="s">
         <v>671</v>
@@ -18975,7 +16885,7 @@
         <v>/14_18.png</v>
       </c>
       <c r="L303" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M303" s="3">
         <f t="shared" si="5"/>
@@ -18985,16 +16895,16 @@
     </row>
     <row r="304" ht="18.0" customHeight="1">
       <c r="A304" s="4" t="s">
-        <v>1142</v>
+        <v>1085</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1143</v>
+        <v>1086</v>
       </c>
       <c r="G304" s="7" t="s">
-        <v>1144</v>
+        <v>1087</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>1145</v>
+        <v>1088</v>
       </c>
       <c r="J304" s="6" t="s">
         <v>671</v>
@@ -19004,7 +16914,7 @@
         <v>/14_19.png</v>
       </c>
       <c r="L304" s="2" t="s">
-        <v>1071</v>
+        <v>1014</v>
       </c>
       <c r="M304" s="3">
         <f t="shared" si="5"/>
@@ -19014,16 +16924,16 @@
     </row>
     <row r="305" ht="18.0" customHeight="1">
       <c r="A305" s="4" t="s">
-        <v>1146</v>
+        <v>1089</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>1147</v>
+        <v>1090</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1148</v>
+        <v>1091</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>1149</v>
+        <v>1092</v>
       </c>
       <c r="J305" s="6" t="s">
         <v>671</v>
@@ -19033,7 +16943,7 @@
         <v>/15_01.png</v>
       </c>
       <c r="L305" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M305" s="3" t="s">
         <v>21</v>
@@ -19042,16 +16952,16 @@
     </row>
     <row r="306" ht="18.0" customHeight="1">
       <c r="A306" s="4" t="s">
-        <v>1151</v>
+        <v>1094</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>1152</v>
+        <v>1095</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1153</v>
+        <v>1096</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>1154</v>
+        <v>1097</v>
       </c>
       <c r="J306" s="6" t="s">
         <v>671</v>
@@ -19061,7 +16971,7 @@
         <v>/15_02.png</v>
       </c>
       <c r="L306" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M306" s="3" t="s">
         <v>22</v>
@@ -19070,16 +16980,16 @@
     </row>
     <row r="307" ht="18.0" customHeight="1">
       <c r="A307" s="4" t="s">
-        <v>1155</v>
+        <v>1098</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>1156</v>
+        <v>1099</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1157</v>
+        <v>1100</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>1158</v>
+        <v>1101</v>
       </c>
       <c r="J307" s="6" t="s">
         <v>671</v>
@@ -19089,7 +16999,7 @@
         <v>/15_03.png</v>
       </c>
       <c r="L307" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M307" s="3" t="s">
         <v>30</v>
@@ -19098,16 +17008,16 @@
     </row>
     <row r="308" ht="18.0" customHeight="1">
       <c r="A308" s="4" t="s">
-        <v>1159</v>
+        <v>1102</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>1160</v>
+        <v>1103</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1161</v>
+        <v>1104</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>1162</v>
+        <v>1105</v>
       </c>
       <c r="J308" s="6" t="s">
         <v>671</v>
@@ -19117,7 +17027,7 @@
         <v>/15_04.png</v>
       </c>
       <c r="L308" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M308" s="3" t="s">
         <v>38</v>
@@ -19126,16 +17036,16 @@
     </row>
     <row r="309" ht="18.0" customHeight="1">
       <c r="A309" s="4" t="s">
-        <v>1163</v>
+        <v>1106</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>1164</v>
+        <v>1107</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1165</v>
+        <v>1108</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>1166</v>
+        <v>1109</v>
       </c>
       <c r="J309" s="6" t="s">
         <v>671</v>
@@ -19145,7 +17055,7 @@
         <v>/15_05.png</v>
       </c>
       <c r="L309" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M309" s="3" t="s">
         <v>47</v>
@@ -19154,16 +17064,16 @@
     </row>
     <row r="310" ht="18.0" customHeight="1">
       <c r="A310" s="4" t="s">
-        <v>1167</v>
+        <v>1110</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>1168</v>
+        <v>1111</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1169</v>
+        <v>1112</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>1170</v>
+        <v>1113</v>
       </c>
       <c r="J310" s="6" t="s">
         <v>671</v>
@@ -19173,7 +17083,7 @@
         <v>/15_06.png</v>
       </c>
       <c r="L310" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M310" s="3" t="s">
         <v>55</v>
@@ -19182,16 +17092,16 @@
     </row>
     <row r="311" ht="18.0" customHeight="1">
       <c r="A311" s="4" t="s">
-        <v>1171</v>
+        <v>1114</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>1172</v>
+        <v>1115</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1173</v>
+        <v>1116</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>1174</v>
+        <v>1117</v>
       </c>
       <c r="J311" s="6" t="s">
         <v>671</v>
@@ -19201,7 +17111,7 @@
         <v>/15_07.png</v>
       </c>
       <c r="L311" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M311" s="3" t="s">
         <v>63</v>
@@ -19210,16 +17120,16 @@
     </row>
     <row r="312" ht="18.0" customHeight="1">
       <c r="A312" s="4" t="s">
-        <v>1175</v>
+        <v>1118</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>1176</v>
+        <v>1119</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>1177</v>
+        <v>1120</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>1178</v>
+        <v>1121</v>
       </c>
       <c r="J312" s="6" t="s">
         <v>671</v>
@@ -19229,7 +17139,7 @@
         <v>/15_08.png</v>
       </c>
       <c r="L312" s="2" t="s">
-        <v>1150</v>
+        <v>1093</v>
       </c>
       <c r="M312" s="3" t="s">
         <v>70</v>
@@ -19238,16 +17148,16 @@
     </row>
     <row r="313" ht="18.0" customHeight="1">
       <c r="A313" s="4" t="s">
-        <v>1179</v>
+        <v>1122</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>1180</v>
+        <v>1123</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1181</v>
+        <v>1124</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>1182</v>
+        <v>1125</v>
       </c>
       <c r="J313" s="6" t="s">
         <v>671</v>
@@ -19257,7 +17167,7 @@
         <v>/16_01.png</v>
       </c>
       <c r="L313" s="2" t="s">
-        <v>1183</v>
+        <v>1126</v>
       </c>
       <c r="M313" s="3" t="s">
         <v>21</v>
@@ -19266,16 +17176,16 @@
     </row>
     <row r="314" ht="18.0" customHeight="1">
       <c r="A314" s="4" t="s">
-        <v>1184</v>
+        <v>1127</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>1185</v>
+        <v>1128</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>1186</v>
+        <v>1129</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>1187</v>
+        <v>1130</v>
       </c>
       <c r="J314" s="6" t="s">
         <v>671</v>
@@ -19285,7 +17195,7 @@
         <v>/16_02.png</v>
       </c>
       <c r="L314" s="2" t="s">
-        <v>1183</v>
+        <v>1126</v>
       </c>
       <c r="M314" s="3" t="s">
         <v>22</v>
@@ -19294,16 +17204,16 @@
     </row>
     <row r="315" ht="18.0" customHeight="1">
       <c r="A315" s="4" t="s">
-        <v>1188</v>
+        <v>1131</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>1189</v>
+        <v>1132</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="I315" s="8" t="s">
-        <v>1191</v>
+        <v>1133</v>
+      </c>
+      <c r="I315" s="9" t="s">
+        <v>1134</v>
       </c>
       <c r="J315" s="6" t="s">
         <v>671</v>
@@ -19313,7 +17223,7 @@
         <v>/16_03.png</v>
       </c>
       <c r="L315" s="2" t="s">
-        <v>1183</v>
+        <v>1126</v>
       </c>
       <c r="M315" s="3" t="s">
         <v>30</v>
@@ -19322,16 +17232,16 @@
     </row>
     <row r="316" ht="18.0" customHeight="1">
       <c r="A316" s="4" t="s">
-        <v>1192</v>
+        <v>1135</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1193</v>
+        <v>1136</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1194</v>
+        <v>1137</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>1195</v>
+        <v>1138</v>
       </c>
       <c r="J316" s="6" t="s">
         <v>671</v>
@@ -19341,7 +17251,7 @@
         <v>/16_04.png</v>
       </c>
       <c r="L316" s="2" t="s">
-        <v>1183</v>
+        <v>1126</v>
       </c>
       <c r="M316" s="3" t="s">
         <v>38</v>
@@ -19350,19 +17260,19 @@
     </row>
     <row r="317" ht="18.0" customHeight="1">
       <c r="A317" s="4" t="s">
-        <v>1196</v>
+        <v>1139</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>1197</v>
+        <v>1140</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>1198</v>
+        <v>1141</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1199</v>
+        <v>1142</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>1200</v>
+        <v>1143</v>
       </c>
       <c r="J317" s="6" t="s">
         <v>671</v>
@@ -19372,7 +17282,7 @@
         <v>/17_01.png</v>
       </c>
       <c r="L317" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M317" s="3" t="s">
         <v>21</v>
@@ -19381,19 +17291,19 @@
     </row>
     <row r="318" ht="18.0" customHeight="1">
       <c r="A318" s="4" t="s">
-        <v>1202</v>
+        <v>1145</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>1203</v>
+        <v>1146</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>1198</v>
+        <v>1141</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1204</v>
+        <v>1147</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>1205</v>
+        <v>1148</v>
       </c>
       <c r="J318" s="6" t="s">
         <v>671</v>
@@ -19403,7 +17313,7 @@
         <v>/17_02.png</v>
       </c>
       <c r="L318" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M318" s="3" t="s">
         <v>22</v>
@@ -19412,19 +17322,19 @@
     </row>
     <row r="319" ht="18.0" customHeight="1">
       <c r="A319" s="4" t="s">
-        <v>1206</v>
+        <v>1149</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>1207</v>
+        <v>1150</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>1208</v>
+        <v>1151</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1209</v>
+        <v>1152</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>1210</v>
+        <v>1153</v>
       </c>
       <c r="J319" s="6" t="s">
         <v>671</v>
@@ -19434,7 +17344,7 @@
         <v>/17_03.png</v>
       </c>
       <c r="L319" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M319" s="3" t="s">
         <v>30</v>
@@ -19443,19 +17353,19 @@
     </row>
     <row r="320" ht="18.0" customHeight="1">
       <c r="A320" s="4" t="s">
-        <v>1211</v>
+        <v>1154</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>1212</v>
+        <v>1155</v>
       </c>
       <c r="C320" s="7" t="s">
-        <v>1213</v>
+        <v>1156</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1214</v>
+        <v>1157</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>1215</v>
+        <v>1158</v>
       </c>
       <c r="J320" s="6" t="s">
         <v>671</v>
@@ -19465,7 +17375,7 @@
         <v>/17_04.png</v>
       </c>
       <c r="L320" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M320" s="3" t="s">
         <v>38</v>
@@ -19474,19 +17384,19 @@
     </row>
     <row r="321" ht="18.0" customHeight="1">
       <c r="A321" s="4" t="s">
-        <v>1216</v>
+        <v>1159</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>1217</v>
+        <v>1160</v>
       </c>
       <c r="C321" s="7" t="s">
-        <v>1218</v>
+        <v>1161</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1219</v>
+        <v>1162</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>1220</v>
+        <v>1163</v>
       </c>
       <c r="J321" s="6" t="s">
         <v>671</v>
@@ -19496,7 +17406,7 @@
         <v>/17_05.png</v>
       </c>
       <c r="L321" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M321" s="3" t="s">
         <v>47</v>
@@ -19505,19 +17415,19 @@
     </row>
     <row r="322" ht="18.0" customHeight="1">
       <c r="A322" s="4" t="s">
-        <v>1221</v>
+        <v>1164</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>1222</v>
+        <v>1165</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>1223</v>
+        <v>1166</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1224</v>
+        <v>1167</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>1225</v>
+        <v>1168</v>
       </c>
       <c r="J322" s="6" t="s">
         <v>671</v>
@@ -19527,7 +17437,7 @@
         <v>/17_06.png</v>
       </c>
       <c r="L322" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M322" s="3" t="s">
         <v>55</v>
@@ -19536,16 +17446,16 @@
     </row>
     <row r="323" ht="18.0" customHeight="1">
       <c r="A323" s="4" t="s">
-        <v>1226</v>
+        <v>1169</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1227</v>
+        <v>1170</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1228</v>
+        <v>1171</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>1229</v>
+        <v>1172</v>
       </c>
       <c r="J323" s="6" t="s">
         <v>671</v>
@@ -19555,7 +17465,7 @@
         <v>/17_07.png</v>
       </c>
       <c r="L323" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M323" s="3" t="s">
         <v>63</v>
@@ -19564,16 +17474,16 @@
     </row>
     <row r="324" ht="18.0" customHeight="1">
       <c r="A324" s="4" t="s">
-        <v>1230</v>
+        <v>1173</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1231</v>
+        <v>1174</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1232</v>
+        <v>1175</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>1233</v>
+        <v>1176</v>
       </c>
       <c r="J324" s="6" t="s">
         <v>671</v>
@@ -19583,7 +17493,7 @@
         <v>/17_08.png</v>
       </c>
       <c r="L324" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M324" s="3" t="s">
         <v>70</v>
@@ -19592,16 +17502,16 @@
     </row>
     <row r="325" ht="18.0" customHeight="1">
       <c r="A325" s="4" t="s">
-        <v>1234</v>
+        <v>1177</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1235</v>
+        <v>1178</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>1236</v>
+        <v>1179</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>1237</v>
+        <v>1180</v>
       </c>
       <c r="J325" s="6" t="s">
         <v>671</v>
@@ -19611,7 +17521,7 @@
         <v>/17_09.png</v>
       </c>
       <c r="L325" s="2" t="s">
-        <v>1201</v>
+        <v>1144</v>
       </c>
       <c r="M325" s="3" t="s">
         <v>77</v>
@@ -19620,16 +17530,16 @@
     </row>
     <row r="326" ht="18.0" customHeight="1">
       <c r="A326" s="4" t="s">
-        <v>1238</v>
+        <v>1181</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1239</v>
+        <v>1182</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1240</v>
+        <v>1183</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>1241</v>
+        <v>1184</v>
       </c>
       <c r="J326" s="6" t="s">
         <v>671</v>
@@ -19648,16 +17558,16 @@
     </row>
     <row r="327" ht="18.0" customHeight="1">
       <c r="A327" s="4" t="s">
-        <v>1242</v>
+        <v>1185</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1243</v>
+        <v>1186</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1244</v>
+        <v>1187</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>1245</v>
+        <v>1188</v>
       </c>
       <c r="J327" s="6" t="s">
         <v>671</v>
@@ -19676,16 +17586,16 @@
     </row>
     <row r="328" ht="18.0" customHeight="1">
       <c r="A328" s="4" t="s">
-        <v>1246</v>
+        <v>1189</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1247</v>
+        <v>1190</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>1248</v>
+        <v>1191</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>1249</v>
+        <v>1192</v>
       </c>
       <c r="J328" s="6" t="s">
         <v>671</v>
@@ -19704,16 +17614,16 @@
     </row>
     <row r="329" ht="18.0" customHeight="1">
       <c r="A329" s="4" t="s">
-        <v>1250</v>
+        <v>1193</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1251</v>
+        <v>1194</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1252</v>
+        <v>1195</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>1253</v>
+        <v>1196</v>
       </c>
       <c r="J329" s="6" t="s">
         <v>671</v>
@@ -19732,16 +17642,16 @@
     </row>
     <row r="330" ht="18.0" customHeight="1">
       <c r="A330" s="4" t="s">
-        <v>1254</v>
+        <v>1197</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1255</v>
+        <v>1198</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1256</v>
+        <v>1199</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>1257</v>
+        <v>1200</v>
       </c>
       <c r="J330" s="6" t="s">
         <v>671</v>
@@ -19760,16 +17670,16 @@
     </row>
     <row r="331" ht="18.0" customHeight="1">
       <c r="A331" s="4" t="s">
-        <v>1258</v>
+        <v>1201</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1259</v>
+        <v>1202</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>1260</v>
+        <v>1203</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>1261</v>
+        <v>1204</v>
       </c>
       <c r="J331" s="6" t="s">
         <v>671</v>
@@ -19788,16 +17698,16 @@
     </row>
     <row r="332" ht="18.0" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1262</v>
+        <v>1205</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1263</v>
+        <v>1206</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1264</v>
+        <v>1207</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>1265</v>
+        <v>1208</v>
       </c>
       <c r="J332" s="6" t="s">
         <v>671</v>
@@ -19816,16 +17726,16 @@
     </row>
     <row r="333" ht="18.0" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1266</v>
+        <v>1209</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1267</v>
+        <v>1210</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>1268</v>
+        <v>1211</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>1269</v>
+        <v>1212</v>
       </c>
       <c r="J333" s="6" t="s">
         <v>671</v>
@@ -19844,16 +17754,16 @@
     </row>
     <row r="334" ht="18.0" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1270</v>
+        <v>1213</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1271</v>
+        <v>1214</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>1272</v>
+        <v>1215</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>1273</v>
+        <v>1216</v>
       </c>
       <c r="J334" s="6" t="s">
         <v>671</v>
@@ -19872,16 +17782,16 @@
     </row>
     <row r="335" ht="18.0" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1274</v>
+        <v>1217</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1275</v>
+        <v>1218</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>1276</v>
+        <v>1219</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>1277</v>
+        <v>1220</v>
       </c>
       <c r="J335" s="6" t="s">
         <v>671</v>
@@ -19900,16 +17810,16 @@
     </row>
     <row r="336" ht="18.0" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1278</v>
+        <v>1221</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1279</v>
+        <v>1222</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>1280</v>
+        <v>1223</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>1281</v>
+        <v>1224</v>
       </c>
       <c r="J336" s="6" t="s">
         <v>671</v>
@@ -19928,16 +17838,16 @@
     </row>
     <row r="337" ht="18.0" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1282</v>
+        <v>1225</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1283</v>
+        <v>1226</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>1284</v>
+        <v>1227</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>1285</v>
+        <v>1228</v>
       </c>
       <c r="J337" s="6" t="s">
         <v>671</v>
@@ -19956,16 +17866,16 @@
     </row>
     <row r="338" ht="18.0" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1286</v>
+        <v>1229</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1287</v>
+        <v>1230</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1288</v>
+        <v>1231</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>1289</v>
+        <v>1232</v>
       </c>
       <c r="J338" s="6" t="s">
         <v>671</v>
@@ -19984,16 +17894,16 @@
     </row>
     <row r="339" ht="18.0" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1290</v>
+        <v>1233</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1291</v>
+        <v>1234</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>1292</v>
+        <v>1235</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>1293</v>
+        <v>1236</v>
       </c>
       <c r="J339" s="6" t="s">
         <v>671</v>
@@ -20012,16 +17922,16 @@
     </row>
     <row r="340" ht="18.0" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1294</v>
+        <v>1237</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1295</v>
+        <v>1238</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>1296</v>
+        <v>1239</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>1297</v>
+        <v>1240</v>
       </c>
       <c r="J340" s="6" t="s">
         <v>671</v>
@@ -20040,16 +17950,16 @@
     </row>
     <row r="341" ht="18.0" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1298</v>
+        <v>1241</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1299</v>
+        <v>1242</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1300</v>
+        <v>1243</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>1301</v>
+        <v>1244</v>
       </c>
       <c r="J341" s="6" t="s">
         <v>671</v>
@@ -20068,16 +17978,16 @@
     </row>
     <row r="342" ht="18.0" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1302</v>
+        <v>1245</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1303</v>
+        <v>1246</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1304</v>
+        <v>1247</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>1305</v>
+        <v>1248</v>
       </c>
       <c r="J342" s="6" t="s">
         <v>671</v>
@@ -20096,16 +18006,16 @@
     </row>
     <row r="343" ht="18.0" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1306</v>
+        <v>1249</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1307</v>
+        <v>1250</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>1308</v>
+        <v>1251</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>1309</v>
+        <v>1252</v>
       </c>
       <c r="J343" s="6" t="s">
         <v>671</v>
@@ -20124,16 +18034,16 @@
     </row>
     <row r="344" ht="18.0" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1310</v>
+        <v>1253</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1311</v>
+        <v>1254</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1312</v>
+        <v>1255</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>1313</v>
+        <v>1256</v>
       </c>
       <c r="J344" s="6" t="s">
         <v>671</v>
@@ -20152,16 +18062,16 @@
     </row>
     <row r="345" ht="18.0" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1314</v>
+        <v>1257</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1315</v>
+        <v>1258</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1316</v>
+        <v>1259</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>1317</v>
+        <v>1260</v>
       </c>
       <c r="J345" s="6" t="s">
         <v>671</v>
@@ -20180,16 +18090,16 @@
     </row>
     <row r="346" ht="18.0" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1318</v>
+        <v>1261</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1319</v>
+        <v>1262</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>1320</v>
+        <v>1263</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>1321</v>
+        <v>1264</v>
       </c>
       <c r="J346" s="6" t="s">
         <v>671</v>
@@ -20208,16 +18118,16 @@
     </row>
     <row r="347" ht="18.0" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1322</v>
+        <v>1265</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1323</v>
+        <v>1266</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>1324</v>
+        <v>1267</v>
       </c>
       <c r="I347" s="1" t="s">
-        <v>1325</v>
+        <v>1268</v>
       </c>
       <c r="J347" s="6" t="s">
         <v>671</v>
@@ -20236,16 +18146,16 @@
     </row>
     <row r="348" ht="18.0" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1326</v>
+        <v>1269</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1327</v>
+        <v>1270</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>1328</v>
+        <v>1271</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>1329</v>
+        <v>1272</v>
       </c>
       <c r="J348" s="6" t="s">
         <v>671</v>
@@ -20264,16 +18174,16 @@
     </row>
     <row r="349" ht="18.0" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1330</v>
+        <v>1273</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1331</v>
+        <v>1274</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>1332</v>
+        <v>1275</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>1333</v>
+        <v>1276</v>
       </c>
       <c r="J349" s="6" t="s">
         <v>671</v>
@@ -20292,16 +18202,16 @@
     </row>
     <row r="350" ht="18.0" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1334</v>
+        <v>1277</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1335</v>
+        <v>1278</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1336</v>
+        <v>1279</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>1337</v>
+        <v>1280</v>
       </c>
       <c r="J350" s="6" t="s">
         <v>671</v>
@@ -20321,16 +18231,16 @@
     </row>
     <row r="351" ht="18.0" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1338</v>
+        <v>1281</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1339</v>
+        <v>1282</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1340</v>
+        <v>1283</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>1341</v>
+        <v>1284</v>
       </c>
       <c r="J351" s="6" t="s">
         <v>671</v>
@@ -20350,16 +18260,16 @@
     </row>
     <row r="352" ht="18.0" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1342</v>
+        <v>1285</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1343</v>
+        <v>1286</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1344</v>
+        <v>1287</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>1345</v>
+        <v>1288</v>
       </c>
       <c r="J352" s="6" t="s">
         <v>671</v>
@@ -20379,16 +18289,16 @@
     </row>
     <row r="353" ht="18.0" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1346</v>
+        <v>1289</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1347</v>
+        <v>1290</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1348</v>
+        <v>1291</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>1349</v>
+        <v>1292</v>
       </c>
       <c r="J353" s="6" t="s">
         <v>671</v>
@@ -20408,16 +18318,16 @@
     </row>
     <row r="354" ht="18.0" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1350</v>
+        <v>1293</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1351</v>
+        <v>1294</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>1352</v>
+        <v>1295</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>1353</v>
+        <v>1296</v>
       </c>
       <c r="J354" s="6" t="s">
         <v>671</v>
@@ -20437,16 +18347,16 @@
     </row>
     <row r="355" ht="18.0" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1354</v>
+        <v>1297</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1355</v>
+        <v>1298</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>1356</v>
+        <v>1299</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>1357</v>
+        <v>1300</v>
       </c>
       <c r="J355" s="6" t="s">
         <v>671</v>
@@ -20466,16 +18376,16 @@
     </row>
     <row r="356" ht="18.0" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1358</v>
+        <v>1301</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1359</v>
+        <v>1302</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>1360</v>
+        <v>1303</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>1361</v>
+        <v>1304</v>
       </c>
       <c r="J356" s="6" t="s">
         <v>671</v>
@@ -20495,16 +18405,16 @@
     </row>
     <row r="357" ht="18.0" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1362</v>
+        <v>1305</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1363</v>
+        <v>1306</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>1364</v>
+        <v>1307</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>1365</v>
+        <v>1308</v>
       </c>
       <c r="J357" s="6" t="s">
         <v>671</v>
@@ -20524,16 +18434,16 @@
     </row>
     <row r="358" ht="18.0" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1366</v>
+        <v>1309</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1367</v>
+        <v>1310</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>1368</v>
+        <v>1311</v>
       </c>
       <c r="I358" s="1" t="s">
-        <v>1369</v>
+        <v>1312</v>
       </c>
       <c r="J358" s="6" t="s">
         <v>671</v>
@@ -20553,16 +18463,16 @@
     </row>
     <row r="359" ht="18.0" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1370</v>
+        <v>1313</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1371</v>
+        <v>1314</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>1372</v>
+        <v>1315</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>1373</v>
+        <v>1316</v>
       </c>
       <c r="J359" s="6" t="s">
         <v>671</v>
@@ -20582,16 +18492,16 @@
     </row>
     <row r="360" ht="18.0" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1374</v>
+        <v>1317</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1375</v>
+        <v>1318</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>1376</v>
+        <v>1319</v>
       </c>
       <c r="I360" s="1" t="s">
-        <v>1377</v>
+        <v>1320</v>
       </c>
       <c r="J360" s="6" t="s">
         <v>671</v>
@@ -20611,16 +18521,16 @@
     </row>
     <row r="361" ht="18.0" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1378</v>
+        <v>1321</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1379</v>
+        <v>1322</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>1380</v>
+        <v>1323</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>1381</v>
+        <v>1324</v>
       </c>
       <c r="J361" s="6" t="s">
         <v>671</v>
@@ -20639,16 +18549,16 @@
     </row>
     <row r="362" ht="18.0" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1382</v>
+        <v>1325</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1383</v>
+        <v>1326</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>1384</v>
+        <v>1327</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>1385</v>
+        <v>1328</v>
       </c>
       <c r="J362" s="6" t="s">
         <v>671</v>
@@ -20667,16 +18577,16 @@
     </row>
     <row r="363" ht="18.0" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1386</v>
+        <v>1329</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1387</v>
+        <v>1330</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>1388</v>
+        <v>1331</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>1389</v>
+        <v>1332</v>
       </c>
       <c r="J363" s="6" t="s">
         <v>671</v>
@@ -20695,16 +18605,16 @@
     </row>
     <row r="364" ht="18.0" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1390</v>
+        <v>1333</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1391</v>
+        <v>1334</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>1392</v>
+        <v>1335</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>1393</v>
+        <v>1336</v>
       </c>
       <c r="J364" s="6" t="s">
         <v>671</v>
@@ -20723,16 +18633,16 @@
     </row>
     <row r="365" ht="18.0" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1394</v>
+        <v>1337</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1395</v>
+        <v>1338</v>
       </c>
       <c r="G365" s="7" t="s">
-        <v>1396</v>
+        <v>1339</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>1397</v>
+        <v>1340</v>
       </c>
       <c r="J365" s="6" t="s">
         <v>671</v>
@@ -20751,16 +18661,16 @@
     </row>
     <row r="366" ht="18.0" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1399</v>
+        <v>1342</v>
       </c>
       <c r="G366" s="7" t="s">
-        <v>1400</v>
+        <v>1343</v>
       </c>
       <c r="I366" s="1" t="s">
-        <v>1401</v>
+        <v>1344</v>
       </c>
       <c r="J366" s="6" t="s">
         <v>671</v>
@@ -20779,16 +18689,16 @@
     </row>
     <row r="367" ht="18.0" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1402</v>
+        <v>1345</v>
       </c>
       <c r="G367" s="7" t="s">
-        <v>1403</v>
+        <v>1346</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>1404</v>
+        <v>1347</v>
       </c>
       <c r="J367" s="6" t="s">
         <v>671</v>
@@ -20807,16 +18717,16 @@
     </row>
     <row r="368" ht="18.0" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1405</v>
+        <v>1348</v>
       </c>
       <c r="G368" s="7" t="s">
-        <v>1406</v>
+        <v>1349</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>1407</v>
+        <v>1350</v>
       </c>
       <c r="J368" s="6" t="s">
         <v>671</v>
@@ -20835,16 +18745,16 @@
     </row>
     <row r="369" ht="18.0" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1408</v>
+        <v>1351</v>
       </c>
       <c r="G369" s="7" t="s">
-        <v>1409</v>
+        <v>1352</v>
       </c>
       <c r="I369" s="1" t="s">
-        <v>1410</v>
+        <v>1353</v>
       </c>
       <c r="J369" s="6" t="s">
         <v>671</v>
@@ -20863,16 +18773,16 @@
     </row>
     <row r="370" ht="18.0" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1411</v>
+        <v>1354</v>
       </c>
       <c r="G370" s="7" t="s">
-        <v>1412</v>
+        <v>1355</v>
       </c>
       <c r="I370" s="1" t="s">
-        <v>1413</v>
+        <v>1356</v>
       </c>
       <c r="J370" s="6" t="s">
         <v>671</v>
@@ -20891,16 +18801,16 @@
     </row>
     <row r="371" ht="18.0" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1414</v>
+        <v>1357</v>
       </c>
       <c r="G371" s="7" t="s">
-        <v>1415</v>
+        <v>1358</v>
       </c>
       <c r="I371" s="1" t="s">
-        <v>1416</v>
+        <v>1359</v>
       </c>
       <c r="J371" s="6" t="s">
         <v>671</v>
@@ -20919,16 +18829,16 @@
     </row>
     <row r="372" ht="18.0" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1417</v>
+        <v>1360</v>
       </c>
       <c r="G372" s="7" t="s">
-        <v>1418</v>
+        <v>1361</v>
       </c>
       <c r="I372" s="1" t="s">
-        <v>1419</v>
+        <v>1362</v>
       </c>
       <c r="J372" s="6" t="s">
         <v>671</v>
@@ -20947,16 +18857,16 @@
     </row>
     <row r="373" ht="18.0" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1420</v>
+        <v>1363</v>
       </c>
       <c r="G373" s="7" t="s">
-        <v>1421</v>
+        <v>1364</v>
       </c>
       <c r="I373" s="1" t="s">
-        <v>1422</v>
+        <v>1365</v>
       </c>
       <c r="J373" s="6" t="s">
         <v>671</v>
@@ -20975,16 +18885,16 @@
     </row>
     <row r="374" ht="18.0" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1423</v>
+        <v>1366</v>
       </c>
       <c r="G374" s="7" t="s">
-        <v>1424</v>
+        <v>1367</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>1425</v>
+        <v>1368</v>
       </c>
       <c r="J374" s="6" t="s">
         <v>671</v>
@@ -21003,16 +18913,16 @@
     </row>
     <row r="375" ht="18.0" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1426</v>
+        <v>1369</v>
       </c>
       <c r="G375" s="7" t="s">
-        <v>1427</v>
+        <v>1370</v>
       </c>
       <c r="I375" s="1" t="s">
-        <v>1428</v>
+        <v>1371</v>
       </c>
       <c r="J375" s="6" t="s">
         <v>671</v>
@@ -21031,16 +18941,16 @@
     </row>
     <row r="376" ht="18.0" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1429</v>
+        <v>1372</v>
       </c>
       <c r="G376" s="7" t="s">
-        <v>1430</v>
+        <v>1373</v>
       </c>
       <c r="I376" s="1" t="s">
-        <v>1431</v>
+        <v>1374</v>
       </c>
       <c r="J376" s="6" t="s">
         <v>671</v>
@@ -21059,16 +18969,16 @@
     </row>
     <row r="377" ht="18.0" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1432</v>
+        <v>1375</v>
       </c>
       <c r="G377" s="7" t="s">
-        <v>1433</v>
+        <v>1376</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>1434</v>
+        <v>1377</v>
       </c>
       <c r="J377" s="6" t="s">
         <v>671</v>
@@ -21087,16 +18997,16 @@
     </row>
     <row r="378" ht="18.0" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1435</v>
+        <v>1378</v>
       </c>
       <c r="G378" s="7" t="s">
-        <v>1436</v>
+        <v>1379</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>1437</v>
+        <v>1380</v>
       </c>
       <c r="J378" s="6" t="s">
         <v>671</v>
@@ -21115,16 +19025,16 @@
     </row>
     <row r="379" ht="18.0" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1438</v>
+        <v>1381</v>
       </c>
       <c r="G379" s="7" t="s">
-        <v>1439</v>
+        <v>1382</v>
       </c>
       <c r="I379" s="1" t="s">
-        <v>1440</v>
+        <v>1383</v>
       </c>
       <c r="J379" s="6" t="s">
         <v>671</v>
@@ -21143,16 +19053,16 @@
     </row>
     <row r="380" ht="18.0" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1441</v>
+        <v>1384</v>
       </c>
       <c r="G380" s="7" t="s">
-        <v>1442</v>
+        <v>1385</v>
       </c>
       <c r="I380" s="1" t="s">
-        <v>1443</v>
+        <v>1386</v>
       </c>
       <c r="J380" s="6" t="s">
         <v>671</v>
@@ -21171,16 +19081,16 @@
     </row>
     <row r="381" ht="18.0" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1444</v>
+        <v>1387</v>
       </c>
       <c r="G381" s="7" t="s">
-        <v>1445</v>
+        <v>1388</v>
       </c>
       <c r="I381" s="1" t="s">
-        <v>1446</v>
+        <v>1389</v>
       </c>
       <c r="J381" s="6" t="s">
         <v>671</v>
@@ -21199,16 +19109,16 @@
     </row>
     <row r="382" ht="18.0" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1447</v>
+        <v>1390</v>
       </c>
       <c r="G382" s="7" t="s">
-        <v>1448</v>
+        <v>1391</v>
       </c>
       <c r="I382" s="1" t="s">
-        <v>1449</v>
+        <v>1392</v>
       </c>
       <c r="J382" s="6" t="s">
         <v>671</v>
@@ -21227,16 +19137,16 @@
     </row>
     <row r="383" ht="18.0" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1398</v>
+        <v>1341</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1450</v>
+        <v>1393</v>
       </c>
       <c r="G383" s="7" t="s">
-        <v>1451</v>
+        <v>1394</v>
       </c>
       <c r="I383" s="1" t="s">
-        <v>1452</v>
+        <v>1395</v>
       </c>
       <c r="J383" s="6" t="s">
         <v>671</v>
@@ -21256,13 +19166,13 @@
     </row>
     <row r="384" ht="18.0" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1454</v>
+        <v>1397</v>
       </c>
       <c r="I384" s="1" t="s">
-        <v>1455</v>
+        <v>1398</v>
       </c>
       <c r="J384" s="6" t="s">
         <v>671</v>
@@ -21272,7 +19182,7 @@
         <v>/22_01.png</v>
       </c>
       <c r="L384" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M384" s="3" t="s">
         <v>21</v>
@@ -21281,13 +19191,13 @@
     </row>
     <row r="385" ht="18.0" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1457</v>
+        <v>1400</v>
       </c>
       <c r="I385" s="1" t="s">
-        <v>1458</v>
+        <v>1401</v>
       </c>
       <c r="J385" s="6" t="s">
         <v>671</v>
@@ -21297,7 +19207,7 @@
         <v>/22_02.png</v>
       </c>
       <c r="L385" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M385" s="3" t="s">
         <v>22</v>
@@ -21306,13 +19216,13 @@
     </row>
     <row r="386" ht="18.0" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1459</v>
+        <v>1402</v>
       </c>
       <c r="I386" s="1" t="s">
-        <v>1460</v>
+        <v>1403</v>
       </c>
       <c r="J386" s="6" t="s">
         <v>671</v>
@@ -21322,7 +19232,7 @@
         <v>/22_03.png</v>
       </c>
       <c r="L386" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M386" s="3" t="s">
         <v>30</v>
@@ -21331,13 +19241,13 @@
     </row>
     <row r="387" ht="18.0" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1461</v>
+        <v>1404</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>1462</v>
+        <v>1405</v>
       </c>
       <c r="J387" s="6" t="s">
         <v>671</v>
@@ -21347,7 +19257,7 @@
         <v>/22_04.png</v>
       </c>
       <c r="L387" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M387" s="3" t="s">
         <v>38</v>
@@ -21356,13 +19266,13 @@
     </row>
     <row r="388" ht="18.0" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1463</v>
+        <v>1406</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>1464</v>
+        <v>1407</v>
       </c>
       <c r="J388" s="6" t="s">
         <v>671</v>
@@ -21372,7 +19282,7 @@
         <v>/22_05.png</v>
       </c>
       <c r="L388" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M388" s="3" t="s">
         <v>47</v>
@@ -21381,13 +19291,13 @@
     </row>
     <row r="389" ht="18.0" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1465</v>
+        <v>1408</v>
       </c>
       <c r="I389" s="1" t="s">
-        <v>1466</v>
+        <v>1409</v>
       </c>
       <c r="J389" s="6" t="s">
         <v>671</v>
@@ -21397,7 +19307,7 @@
         <v>/22_06.png</v>
       </c>
       <c r="L389" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M389" s="3" t="s">
         <v>55</v>
@@ -21406,13 +19316,13 @@
     </row>
     <row r="390" ht="18.0" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1467</v>
+        <v>1410</v>
       </c>
       <c r="I390" s="1" t="s">
-        <v>1468</v>
+        <v>1411</v>
       </c>
       <c r="J390" s="6" t="s">
         <v>671</v>
@@ -21422,7 +19332,7 @@
         <v>/22_07.png</v>
       </c>
       <c r="L390" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M390" s="3" t="s">
         <v>63</v>
@@ -21431,13 +19341,13 @@
     </row>
     <row r="391" ht="18.0" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1453</v>
+        <v>1396</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1469</v>
+        <v>1412</v>
       </c>
       <c r="I391" s="1" t="s">
-        <v>1470</v>
+        <v>1413</v>
       </c>
       <c r="J391" s="6" t="s">
         <v>671</v>
@@ -21447,7 +19357,7 @@
         <v>/22_08.png</v>
       </c>
       <c r="L391" s="2" t="s">
-        <v>1456</v>
+        <v>1399</v>
       </c>
       <c r="M391" s="3" t="s">
         <v>70</v>
@@ -21456,13 +19366,13 @@
     </row>
     <row r="392" ht="18.0" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1471</v>
+        <v>1414</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1472</v>
+        <v>1415</v>
       </c>
       <c r="I392" s="1" t="s">
-        <v>1473</v>
+        <v>1416</v>
       </c>
       <c r="J392" s="6" t="s">
         <v>671</v>
@@ -21472,7 +19382,7 @@
         <v>/23_01.png</v>
       </c>
       <c r="L392" s="2" t="s">
-        <v>1474</v>
+        <v>1417</v>
       </c>
       <c r="M392" s="3" t="s">
         <v>21</v>
@@ -21481,13 +19391,13 @@
     </row>
     <row r="393" ht="18.0" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1471</v>
+        <v>1414</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1475</v>
+        <v>1418</v>
       </c>
       <c r="I393" s="1" t="s">
-        <v>1476</v>
+        <v>1419</v>
       </c>
       <c r="J393" s="6" t="s">
         <v>671</v>
@@ -21497,7 +19407,7 @@
         <v>/23_02.png</v>
       </c>
       <c r="L393" s="2" t="s">
-        <v>1474</v>
+        <v>1417</v>
       </c>
       <c r="M393" s="3" t="s">
         <v>22</v>
@@ -21506,13 +19416,13 @@
     </row>
     <row r="394" ht="18.0" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1471</v>
+        <v>1414</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1477</v>
+        <v>1420</v>
       </c>
       <c r="I394" s="1" t="s">
-        <v>1478</v>
+        <v>1421</v>
       </c>
       <c r="J394" s="6" t="s">
         <v>671</v>
@@ -21522,7 +19432,7 @@
         <v>/23_03.png</v>
       </c>
       <c r="L394" s="2" t="s">
-        <v>1474</v>
+        <v>1417</v>
       </c>
       <c r="M394" s="3" t="s">
         <v>30</v>
@@ -21531,13 +19441,13 @@
     </row>
     <row r="395" ht="18.0" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1471</v>
+        <v>1414</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1479</v>
+        <v>1422</v>
       </c>
       <c r="I395" s="1" t="s">
-        <v>1480</v>
+        <v>1423</v>
       </c>
       <c r="J395" s="6" t="s">
         <v>671</v>
@@ -21547,7 +19457,7 @@
         <v>/23_04.png</v>
       </c>
       <c r="L395" s="2" t="s">
-        <v>1474</v>
+        <v>1417</v>
       </c>
       <c r="M395" s="3" t="s">
         <v>38</v>
@@ -21556,13 +19466,13 @@
     </row>
     <row r="396" ht="18.0" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1471</v>
+        <v>1414</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1481</v>
+        <v>1424</v>
       </c>
       <c r="I396" s="1" t="s">
-        <v>1482</v>
+        <v>1425</v>
       </c>
       <c r="J396" s="6" t="s">
         <v>671</v>
@@ -21572,7 +19482,7 @@
         <v>/23_05.png</v>
       </c>
       <c r="L396" s="2" t="s">
-        <v>1474</v>
+        <v>1417</v>
       </c>
       <c r="M396" s="3" t="s">
         <v>47</v>
@@ -21581,13 +19491,13 @@
     </row>
     <row r="397" ht="18.0" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1471</v>
+        <v>1414</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1483</v>
+        <v>1426</v>
       </c>
       <c r="I397" s="1" t="s">
-        <v>1484</v>
+        <v>1427</v>
       </c>
       <c r="J397" s="6" t="s">
         <v>671</v>
@@ -21597,7 +19507,7 @@
         <v>/23_06.png</v>
       </c>
       <c r="L397" s="2" t="s">
-        <v>1474</v>
+        <v>1417</v>
       </c>
       <c r="M397" s="3" t="s">
         <v>55</v>
@@ -21606,13 +19516,13 @@
     </row>
     <row r="398" ht="18.0" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1486</v>
+        <v>1429</v>
       </c>
       <c r="I398" s="1" t="s">
-        <v>1487</v>
+        <v>1430</v>
       </c>
       <c r="J398" s="6" t="s">
         <v>671</v>
@@ -21622,7 +19532,7 @@
         <v>/24_01.png</v>
       </c>
       <c r="L398" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M398" s="3" t="s">
         <v>21</v>
@@ -21631,13 +19541,13 @@
     </row>
     <row r="399" ht="18.0" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1489</v>
+        <v>1432</v>
       </c>
       <c r="I399" s="1" t="s">
-        <v>1490</v>
+        <v>1433</v>
       </c>
       <c r="J399" s="6" t="s">
         <v>671</v>
@@ -21647,7 +19557,7 @@
         <v>/24_02.png</v>
       </c>
       <c r="L399" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M399" s="3" t="s">
         <v>22</v>
@@ -21656,13 +19566,13 @@
     </row>
     <row r="400" ht="18.0" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1491</v>
+        <v>1434</v>
       </c>
       <c r="I400" s="1" t="s">
-        <v>1492</v>
+        <v>1435</v>
       </c>
       <c r="J400" s="6" t="s">
         <v>671</v>
@@ -21672,7 +19582,7 @@
         <v>/24_03.png</v>
       </c>
       <c r="L400" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M400" s="3" t="s">
         <v>30</v>
@@ -21681,13 +19591,13 @@
     </row>
     <row r="401" ht="18.0" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1493</v>
+        <v>1436</v>
       </c>
       <c r="I401" s="1" t="s">
-        <v>1494</v>
+        <v>1437</v>
       </c>
       <c r="J401" s="6" t="s">
         <v>671</v>
@@ -21697,7 +19607,7 @@
         <v>/24_04.png</v>
       </c>
       <c r="L401" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M401" s="3" t="s">
         <v>38</v>
@@ -21706,13 +19616,13 @@
     </row>
     <row r="402" ht="18.0" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1495</v>
+        <v>1438</v>
       </c>
       <c r="I402" s="1" t="s">
-        <v>1496</v>
+        <v>1439</v>
       </c>
       <c r="J402" s="6" t="s">
         <v>671</v>
@@ -21722,7 +19632,7 @@
         <v>/24_05.png</v>
       </c>
       <c r="L402" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M402" s="3" t="s">
         <v>47</v>
@@ -21731,13 +19641,13 @@
     </row>
     <row r="403" ht="18.0" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1497</v>
+        <v>1440</v>
       </c>
       <c r="I403" s="1" t="s">
-        <v>1498</v>
+        <v>1441</v>
       </c>
       <c r="J403" s="6" t="s">
         <v>671</v>
@@ -21747,7 +19657,7 @@
         <v>/24_06.png</v>
       </c>
       <c r="L403" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M403" s="3" t="s">
         <v>55</v>
@@ -21756,13 +19666,13 @@
     </row>
     <row r="404" ht="18.0" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1499</v>
+        <v>1442</v>
       </c>
       <c r="I404" s="1" t="s">
-        <v>1500</v>
+        <v>1443</v>
       </c>
       <c r="J404" s="6" t="s">
         <v>671</v>
@@ -21772,7 +19682,7 @@
         <v>/24_07.png</v>
       </c>
       <c r="L404" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M404" s="3" t="s">
         <v>63</v>
@@ -21781,13 +19691,13 @@
     </row>
     <row r="405" ht="18.0" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1501</v>
+        <v>1444</v>
       </c>
       <c r="I405" s="1" t="s">
-        <v>1502</v>
+        <v>1445</v>
       </c>
       <c r="J405" s="6" t="s">
         <v>671</v>
@@ -21797,7 +19707,7 @@
         <v>/24_08.png</v>
       </c>
       <c r="L405" s="2" t="s">
-        <v>1488</v>
+        <v>1431</v>
       </c>
       <c r="M405" s="3" t="s">
         <v>70</v>

--- a/計画-事例集.xlsx
+++ b/計画-事例集.xlsx
@@ -3,20 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="全体" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="全体" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="tSdSv6b7iSHDclVir7nint1XN3z5Zs1PcvKlr/bhZXg="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1445">
   <si>
     <t>ジャンル</t>
   </si>
@@ -5568,10 +5563,10 @@
     </r>
   </si>
   <si>
-    <t>ヒッポダモス（ミトレス）</t>
-  </si>
-  <si>
-    <t>イオニア地方(現在のトルコ西部)に建設された植民都市であベルシャの侵攻で焼失した後、紀元前 5 世紀中頃にヒッポダモスの計画に基づいて再建された。城壁内全体に直交格子状の道路網を敷設し、中央部に行政・宗教・商業施設を、その南北に住宅地を配置している。</t>
+    <t>ヒッポダモス</t>
+  </si>
+  <si>
+    <t>ミトレス</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_01.png</t>
@@ -5619,10 +5614,10 @@
     </r>
   </si>
   <si>
-    <t>ミケランジェロ（カンポドリオ広場）</t>
-  </si>
-  <si>
-    <t>ロ ー マのカンピドリオ広場は、 16 世紀中頃にミケランジェロの計画により、カンピドリオの丘の頂上に造られた台形状の広場である。中央に騎馬像を置いた広場を中心に、そのアプロ ー チとなる大階段、 3 つのパラツツオ(宮殿)を対照的に配置することで軸線を強調しており、後のバロック期の広場計画に多大な影響を与えた。</t>
+    <t>ミケランジェロ</t>
+  </si>
+  <si>
+    <t>カンポドリオ広場</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_02.png</t>
@@ -5670,10 +5665,10 @@
     </r>
   </si>
   <si>
-    <t>E.ハワード（明日の田園都市）</t>
-  </si>
-  <si>
-    <t>ユ ー トビア(理想郷)の思想に影響を受け、その実現に向けての経営・行政の方法を論し、都市の利点と農村の魅力を融合させた自給自足の小都市構想。レッチワ ー ス(イギリス)をはじめ、その後のニュ ー タウンの建設に大きな影響を与えた。</t>
+    <t>E.ハワード</t>
+  </si>
+  <si>
+    <t>明日の田園都市</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_03.png</t>
@@ -5721,10 +5716,10 @@
     </r>
   </si>
   <si>
-    <t>T.ガルニエ（工業都市）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 20 世紀初頭のフランスの建築家。近代都市を支える「工業都市」構想は、工業を計画の主題とし、都市を構成する機能を地域ごとに分けた明確な構造を示している。住居地域を緑地帯によって工業地域から分離することにより各 々 を独自に拡張可能なものとし、生活と労働の両面に対応した近代性を備える都市を提案している。</t>
+    <t>T.ガルニエ</t>
+  </si>
+  <si>
+    <t>工業都市</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_04.png</t>
@@ -5979,7 +5974,7 @@
     <t>L.コルビュジエ（輝く都市）</t>
   </si>
   <si>
-    <t>人口過密で環境の悪化する近代都市を批判し、地表面を開放してオ ー プンスペ ー スを確保し、空中に持ち上げた高層建築と道路の機能区分の明瞭さが特徴的な都市の再開発計画の提案であり、マルセイユの「住居単位」でその理論の一部を具体化し</t>
+    <t>人口過密で環境の悪化する近代都市を批判し、地表面を開放してオ ー プンスペ ー スを確保し、空中に持ち上げた高層建築と道路の機能区分の明瞭さが特徴的な都市の再開発計画の提案であり、マルセイユの「住居単位」でその理論の一部を具体化した</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_09.png</t>
@@ -6027,10 +6022,10 @@
     </r>
   </si>
   <si>
-    <t>C.ブキャナン（ブキャナンレポート）</t>
-  </si>
-  <si>
-    <t>著書の「都市の自動車交通」で、都市内交通に関する総合交通体系を研究したもの。都心部への自動車交通の集中や住宅地内道路での通過交通の増大を避けるため、道路網を構成する各道路の役割分担を明確にした段階構成の重要性を指摘し、日本をはじめとする諸外国の道路交通政策に大きな影響を与えた。</t>
+    <t>C.ブキャナン</t>
+  </si>
+  <si>
+    <t>ブキャナンレポート</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_10.png</t>
@@ -6078,10 +6073,10 @@
     </r>
   </si>
   <si>
-    <t>P.ゲデス（進化する都市）</t>
-  </si>
-  <si>
-    <t>生物学の基礎の上に社会学を展開し、その実践の場を都市計画に見出した。都市人口、雇用、生活等を数量的に分析し、科学的な都市計画の研究「進化する都市」を発表した。後年はインドに赴いて、保存的外科手術(Conservative Surgery) という概念のもと、都市の歴史性を保存しながら再開発を実施した。</t>
+    <t>P.ゲデス</t>
+  </si>
+  <si>
+    <t>進化する都市</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_11.png</t>
@@ -6129,10 +6124,10 @@
     </r>
   </si>
   <si>
-    <t>C. A. ドクシァディス（エキュメノポリス）</t>
-  </si>
-  <si>
-    <t>都市を人間定住社会対象として考え、エキスティック=人間定住社会理論を展開した。雑誌『エキスティック』で、メカロポリス、工ペロポリス、エキュメノボリス等の分類を提唱。メガロホリスの例としては、アメリカ東海岸のポストンからニュ ー ヨ ー ク、ワシントンにかけての都市化地域、また、我が国では、首都圏中京圏・近畿圏とつながる東海道メガロポリスもこれに近い例といえる。</t>
+    <t>C. A. ドクシァディス</t>
+  </si>
+  <si>
+    <t>エキュメノポリス</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_12.png</t>
@@ -6180,10 +6175,10 @@
     </r>
   </si>
   <si>
-    <t>C. A. ペリー（近隣住区）</t>
-  </si>
-  <si>
-    <t>新しいコミュニティ計画を目指して、近隣住区を構成単位とする住区計画の理論を提唱。ハワ ー ドの構想とともに以後のニュー タウン計画の基礎となっている。</t>
+    <t>C. A. ペリー</t>
+  </si>
+  <si>
+    <t>近隣住区</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_13.png</t>
@@ -6231,10 +6226,10 @@
     </r>
   </si>
   <si>
-    <t>C. スタイン,　H. ライト（ラドバーン方式）</t>
-  </si>
-  <si>
-    <t>多数のコミュニティ計画を手がけたが、歩車道分離、ス ー パ ー プロック制をとったラドバ ー ン地区の計画が有名。人と車との分離(歩車分離)を図ったラドバ ー ン方式として、その後の団地計画の基本的な考え方のひとっとなった。</t>
+    <t>C. スタイン,　H. ライト</t>
+  </si>
+  <si>
+    <t>ラドバーン方式</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_14.png</t>
@@ -6282,10 +6277,10 @@
     </r>
   </si>
   <si>
-    <t>L. ハルブリン（ストリートファニチュア）</t>
-  </si>
-  <si>
-    <t>街灯、べンチ、フラワ ー ポット、電話ポックス、ノ ヾ ス停など各種ストリ ー トファニチュアを総合的に計画した「ニコレットモ ー 丿レ(アメリカ・ミネアポリス)」の設計者、都市計画家。</t>
+    <t>L. ハルブリン</t>
+  </si>
+  <si>
+    <t>ストリートファニチュア</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_15.png</t>
@@ -6333,10 +6328,10 @@
     </r>
   </si>
   <si>
-    <t>J.ジェイコブズ（アメリカの大都市の生と死）</t>
-  </si>
-  <si>
-    <t>その著書の自動車中心になり、人間不在の状況になっていることを批判し、都市の街路や地区に多様性を生み出すための 4 つの条件を提示している。①多くの場所に、主要な機能が 2 つ以上ある。②街区が短く、街路が多く、街角を曲る機会が頻繁にある。③年代や状態の異なる様 々 な建物が混じり合う。④人 々 が十分に密集している。都市の防犯計画について,頻繁に使われている街路は安全な路となる傾向にあり,犯罪抑制のためには,街路には常に住民,通行人,店員などの多数の目を置いて監視する必要があると述べている。「アメリカ大都市の死と生」( 1961 年)で、アメリカの大都市が</t>
+    <t>J.ジェイコブズ</t>
+  </si>
+  <si>
+    <t>アメリカの大都市の生と死</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_16.png</t>
@@ -6384,10 +6379,10 @@
     </r>
   </si>
   <si>
-    <t>L. マンフォード（都市の文化）</t>
-  </si>
-  <si>
-    <t>中世以降の都市を技術・文明の発達という視点から分析し、過大成長して過密化した現代都市の再生への方策を提案している。他の主な著書に「歴史の都市明日の都市」「芸術と技術」等がある。</t>
+    <t>L. マンフォード</t>
+  </si>
+  <si>
+    <t>都市の文化</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_17.png</t>
@@ -6435,10 +6430,7 @@
     </r>
   </si>
   <si>
-    <t>丹下健三（東京計画1960）</t>
-  </si>
-  <si>
-    <t>戦後の急激な拡大膨張により、 1960 年当時にはすでに人口1 , 000 万人を超える巨大都市となっていた東京の将来的な混乱や麻痺を危惧し、東京湾上に道路や人口地盤を建設するという構想による「東京計画 1960 」を発表した。この計画案では、それまでの都心を中心とした求心・放射型の都市構造の閉鎖性を否定し、都市軸の概念を導人することによって開放的な線形発展を可能にするという都市構造を提案している。</t>
+    <t>東京計画1960</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_18.png</t>
@@ -6486,10 +6478,10 @@
     </r>
   </si>
   <si>
-    <t>R. B. フラー（ユートピア都市構想）</t>
-  </si>
-  <si>
-    <t>巨大な空気膜のド ー ムによってニュ ー ヨ ー ク市街の一部を覆い、その地区全体を理想的な気候状態に保っというュ ー トビア都市構想を提示した。</t>
+    <t>R. B. フラー</t>
+  </si>
+  <si>
+    <t>ユートピア都市構想</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_19.png</t>
@@ -6537,10 +6529,10 @@
     </r>
   </si>
   <si>
-    <t>K. リンク（都市のイメージ）</t>
-  </si>
-  <si>
-    <t>都市空間から抽出されるイメ ー ジを構成する要素として、以下の 5 つを提示した。①移動路 (path)2 境界 (edge)③地区 (district)④結節点( node )⑤目印 (landmark)この 5 つの要素が、住民や来訪者にとって都市を明瞭で分かりやすいものにし、安心感や愛着を感じるための手がかりになると主張した。</t>
+    <t>K. リンク</t>
+  </si>
+  <si>
+    <t>都市のイメージ</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_20.png</t>
@@ -6588,10 +6580,10 @@
     </r>
   </si>
   <si>
-    <t>G. カレン（都市の景観）</t>
-  </si>
-  <si>
-    <t>歩行者によって体験されるシ ー クエンス(連続する光景)の多様さにより、都市景観の価値が形成されることを示した。</t>
+    <t>G. カレン</t>
+  </si>
+  <si>
+    <t>都市の景観</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_21.png</t>
@@ -6639,10 +6631,10 @@
     </r>
   </si>
   <si>
-    <t>R. ヴェンチューリ（ラスベガス,建築の多様性と対立性）</t>
-  </si>
-  <si>
-    <t>ラスベガスの街路景観の調査をもとに,建築物や看板に見られる大衆文化(ポップカルチャ ー )の中の象徴性について,記号論的な視点から分析した。「建築の多様性と対立性」では,歴史上の建築を例に,曖味さや複雑さのある建築の魅力を伝え,不整合性をもっ多様な建築表現の有効性を示し,単純化・抽象化されすぎた近代建築が建築の唯一の解でないことを主張した。</t>
+    <t>R. ヴェンチューリ</t>
+  </si>
+  <si>
+    <t>ラスベガス,建築の多様性と対立性</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_22.png</t>
@@ -6690,10 +6682,10 @@
     </r>
   </si>
   <si>
-    <t>A.ロッシ（都市の建築）</t>
-  </si>
-  <si>
-    <t>人 々 が建築を造り始めるとき,それは同時に都市の初源的輪郭をも形づくる行為であり,文明の形成と同質のもので,永続的,普遍的,かっ必需物であるとし,特殊と普遍,個と集団との対照を浮かびあがらせる都市という視点で考察した。</t>
+    <t>A.ロッシ</t>
+  </si>
+  <si>
+    <t>都市の建築</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_23.png</t>
@@ -6744,7 +6736,7 @@
     <t>C.アレグザンダー（都市はツリーではない）</t>
   </si>
   <si>
-    <t>建築家や都市計画家によって設計された人工都市は単純なツリ ー 構造であり、長い年月をかけて形成された自然都市の複雑な構造とは全く異なることを指摘し、近代の都市計画の方法を批判した。</t>
+    <t>都市はツリーではない</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_24.png</t>
@@ -6795,7 +6787,7 @@
     <t>C.アレグザンダー（パタン・ランゲージ）</t>
   </si>
   <si>
-    <t>世界各地の都市や建築物の事例から、人 々 が心地よいと感じるパタ ー ンを抽出し、言葉を組み合わせて文章をつくるように、それを構成することで美しい街並みや住まいを創造する設計手法。パタ ー ンを見出すのは住民自身であり、住民参加のまちづくりや建築を目指し、その手助けをすることが建築家の役割であると主張している。実例として、「盈進学園東野高等学校」「川越一番街」がある。</t>
+    <t>パタン・ランゲージ</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_25.png</t>
@@ -6846,7 +6838,7 @@
     <t>C.アレグザンダー（形の合成に関するノート）</t>
   </si>
   <si>
-    <t>「建築はすべて数学的に説明できる」という主張に基づき、図形を使って、デザインという問題を、合理的、かっ、数学的な理論を用いて、定式化して解くことを提案した。</t>
+    <t>形の合成に関するノート</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_26.png</t>
@@ -6894,10 +6886,10 @@
     </r>
   </si>
   <si>
-    <t>槇文彦（見えがくれする都市）</t>
-  </si>
-  <si>
-    <t>古地図に示された江戸の街路パタ ー ンや都市景観の特徴などを分析し、日本の建築空間や都市空間の美しさをつくる潜在的な秩序を、美学的及び幾何学的な観点から考察した。</t>
+    <t>槇文彦</t>
+  </si>
+  <si>
+    <t>見えがくれする都市</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_27.png</t>
@@ -6945,10 +6937,10 @@
     </r>
   </si>
   <si>
-    <t>R. コールハース（錯乱のニューヨーク）</t>
-  </si>
-  <si>
-    <t>近代アメリカの超高層建築物着目することにより、マンハッタンの街が空間の最大効率化をめざす「過密の文化」にもとづいていることを指摘し、そこに見出せる理論構造を「マンハッタニズム」と定義した。</t>
+    <t>R. コールハース</t>
+  </si>
+  <si>
+    <t>錯乱のニューヨーク</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//19_28.png</t>
@@ -7577,7 +7569,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -7608,6 +7600,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -7618,6 +7613,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17728,10 +17727,10 @@
       <c r="A333" s="4" t="s">
         <v>1209</v>
       </c>
-      <c r="B333" s="4" t="s">
+      <c r="B333" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="G333" s="1" t="s">
+      <c r="G333" s="10" t="s">
         <v>1211</v>
       </c>
       <c r="I333" s="1" t="s">
@@ -17756,10 +17755,10 @@
       <c r="A334" s="4" t="s">
         <v>1213</v>
       </c>
-      <c r="B334" s="4" t="s">
+      <c r="B334" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="G334" s="1" t="s">
+      <c r="G334" s="10" t="s">
         <v>1215</v>
       </c>
       <c r="I334" s="1" t="s">
@@ -17784,10 +17783,10 @@
       <c r="A335" s="4" t="s">
         <v>1217</v>
       </c>
-      <c r="B335" s="4" t="s">
+      <c r="B335" s="8" t="s">
         <v>1218</v>
       </c>
-      <c r="G335" s="1" t="s">
+      <c r="G335" s="10" t="s">
         <v>1219</v>
       </c>
       <c r="I335" s="1" t="s">
@@ -17812,10 +17811,10 @@
       <c r="A336" s="4" t="s">
         <v>1221</v>
       </c>
-      <c r="B336" s="4" t="s">
+      <c r="B336" s="8" t="s">
         <v>1222</v>
       </c>
-      <c r="G336" s="1" t="s">
+      <c r="G336" s="10" t="s">
         <v>1223</v>
       </c>
       <c r="I336" s="1" t="s">
@@ -17955,7 +17954,7 @@
       <c r="B341" s="4" t="s">
         <v>1242</v>
       </c>
-      <c r="G341" s="1" t="s">
+      <c r="G341" s="10" t="s">
         <v>1243</v>
       </c>
       <c r="I341" s="1" t="s">
@@ -17980,10 +17979,10 @@
       <c r="A342" s="4" t="s">
         <v>1245</v>
       </c>
-      <c r="B342" s="4" t="s">
+      <c r="B342" s="8" t="s">
         <v>1246</v>
       </c>
-      <c r="G342" s="1" t="s">
+      <c r="G342" s="10" t="s">
         <v>1247</v>
       </c>
       <c r="I342" s="1" t="s">
@@ -18008,10 +18007,10 @@
       <c r="A343" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="B343" s="4" t="s">
+      <c r="B343" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="G343" s="1" t="s">
+      <c r="G343" s="10" t="s">
         <v>1251</v>
       </c>
       <c r="I343" s="1" t="s">
@@ -18036,10 +18035,10 @@
       <c r="A344" s="4" t="s">
         <v>1253</v>
       </c>
-      <c r="B344" s="4" t="s">
+      <c r="B344" s="8" t="s">
         <v>1254</v>
       </c>
-      <c r="G344" s="1" t="s">
+      <c r="G344" s="10" t="s">
         <v>1255</v>
       </c>
       <c r="I344" s="1" t="s">
@@ -18064,10 +18063,10 @@
       <c r="A345" s="4" t="s">
         <v>1257</v>
       </c>
-      <c r="B345" s="4" t="s">
+      <c r="B345" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="G345" s="1" t="s">
+      <c r="G345" s="10" t="s">
         <v>1259</v>
       </c>
       <c r="I345" s="1" t="s">
@@ -18092,10 +18091,10 @@
       <c r="A346" s="4" t="s">
         <v>1261</v>
       </c>
-      <c r="B346" s="4" t="s">
+      <c r="B346" s="8" t="s">
         <v>1262</v>
       </c>
-      <c r="G346" s="1" t="s">
+      <c r="G346" s="10" t="s">
         <v>1263</v>
       </c>
       <c r="I346" s="1" t="s">
@@ -18120,10 +18119,10 @@
       <c r="A347" s="4" t="s">
         <v>1265</v>
       </c>
-      <c r="B347" s="4" t="s">
+      <c r="B347" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="G347" s="1" t="s">
+      <c r="G347" s="10" t="s">
         <v>1267</v>
       </c>
       <c r="I347" s="1" t="s">
@@ -18148,10 +18147,10 @@
       <c r="A348" s="4" t="s">
         <v>1269</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B348" s="8" t="s">
         <v>1270</v>
       </c>
-      <c r="G348" s="1" t="s">
+      <c r="G348" s="10" t="s">
         <v>1271</v>
       </c>
       <c r="I348" s="1" t="s">
@@ -18176,10 +18175,10 @@
       <c r="A349" s="4" t="s">
         <v>1273</v>
       </c>
-      <c r="B349" s="4" t="s">
+      <c r="B349" s="8" t="s">
         <v>1274</v>
       </c>
-      <c r="G349" s="1" t="s">
+      <c r="G349" s="10" t="s">
         <v>1275</v>
       </c>
       <c r="I349" s="1" t="s">
@@ -18204,14 +18203,14 @@
       <c r="A350" s="4" t="s">
         <v>1277</v>
       </c>
-      <c r="B350" s="4" t="s">
+      <c r="B350" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="G350" s="10" t="s">
         <v>1278</v>
       </c>
-      <c r="G350" s="1" t="s">
+      <c r="I350" s="1" t="s">
         <v>1279</v>
-      </c>
-      <c r="I350" s="1" t="s">
-        <v>1280</v>
       </c>
       <c r="J350" s="6" t="s">
         <v>671</v>
@@ -18231,16 +18230,16 @@
     </row>
     <row r="351" ht="18.0" customHeight="1">
       <c r="A351" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B351" s="8" t="s">
         <v>1281</v>
       </c>
-      <c r="B351" s="4" t="s">
+      <c r="G351" s="10" t="s">
         <v>1282</v>
       </c>
-      <c r="G351" s="1" t="s">
+      <c r="I351" s="1" t="s">
         <v>1283</v>
-      </c>
-      <c r="I351" s="1" t="s">
-        <v>1284</v>
       </c>
       <c r="J351" s="6" t="s">
         <v>671</v>
@@ -18260,16 +18259,16 @@
     </row>
     <row r="352" ht="18.0" customHeight="1">
       <c r="A352" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B352" s="8" t="s">
         <v>1285</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="G352" s="10" t="s">
         <v>1286</v>
       </c>
-      <c r="G352" s="1" t="s">
+      <c r="I352" s="1" t="s">
         <v>1287</v>
-      </c>
-      <c r="I352" s="1" t="s">
-        <v>1288</v>
       </c>
       <c r="J352" s="6" t="s">
         <v>671</v>
@@ -18289,16 +18288,16 @@
     </row>
     <row r="353" ht="18.0" customHeight="1">
       <c r="A353" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B353" s="8" t="s">
         <v>1289</v>
       </c>
-      <c r="B353" s="4" t="s">
+      <c r="G353" s="10" t="s">
         <v>1290</v>
       </c>
-      <c r="G353" s="1" t="s">
+      <c r="I353" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="I353" s="1" t="s">
-        <v>1292</v>
       </c>
       <c r="J353" s="6" t="s">
         <v>671</v>
@@ -18318,16 +18317,16 @@
     </row>
     <row r="354" ht="18.0" customHeight="1">
       <c r="A354" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B354" s="8" t="s">
         <v>1293</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="G354" s="10" t="s">
         <v>1294</v>
       </c>
-      <c r="G354" s="1" t="s">
+      <c r="I354" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="I354" s="1" t="s">
-        <v>1296</v>
       </c>
       <c r="J354" s="6" t="s">
         <v>671</v>
@@ -18347,16 +18346,16 @@
     </row>
     <row r="355" ht="18.0" customHeight="1">
       <c r="A355" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B355" s="8" t="s">
         <v>1297</v>
       </c>
-      <c r="B355" s="4" t="s">
+      <c r="G355" s="10" t="s">
         <v>1298</v>
       </c>
-      <c r="G355" s="1" t="s">
+      <c r="I355" s="1" t="s">
         <v>1299</v>
-      </c>
-      <c r="I355" s="1" t="s">
-        <v>1300</v>
       </c>
       <c r="J355" s="6" t="s">
         <v>671</v>
@@ -18376,16 +18375,16 @@
     </row>
     <row r="356" ht="18.0" customHeight="1">
       <c r="A356" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B356" s="4" t="s">
         <v>1301</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="G356" s="10" t="s">
         <v>1302</v>
       </c>
-      <c r="G356" s="1" t="s">
+      <c r="I356" s="1" t="s">
         <v>1303</v>
-      </c>
-      <c r="I356" s="1" t="s">
-        <v>1304</v>
       </c>
       <c r="J356" s="6" t="s">
         <v>671</v>
@@ -18405,16 +18404,16 @@
     </row>
     <row r="357" ht="18.0" customHeight="1">
       <c r="A357" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B357" s="4" t="s">
         <v>1305</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="G357" s="10" t="s">
         <v>1306</v>
       </c>
-      <c r="G357" s="1" t="s">
+      <c r="I357" s="1" t="s">
         <v>1307</v>
-      </c>
-      <c r="I357" s="1" t="s">
-        <v>1308</v>
       </c>
       <c r="J357" s="6" t="s">
         <v>671</v>
@@ -18434,16 +18433,16 @@
     </row>
     <row r="358" ht="18.0" customHeight="1">
       <c r="A358" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B358" s="4" t="s">
         <v>1309</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="G358" s="10" t="s">
         <v>1310</v>
       </c>
-      <c r="G358" s="1" t="s">
+      <c r="I358" s="1" t="s">
         <v>1311</v>
-      </c>
-      <c r="I358" s="1" t="s">
-        <v>1312</v>
       </c>
       <c r="J358" s="6" t="s">
         <v>671</v>
@@ -18463,16 +18462,16 @@
     </row>
     <row r="359" ht="18.0" customHeight="1">
       <c r="A359" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B359" s="8" t="s">
         <v>1313</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="G359" s="10" t="s">
         <v>1314</v>
       </c>
-      <c r="G359" s="1" t="s">
+      <c r="I359" s="1" t="s">
         <v>1315</v>
-      </c>
-      <c r="I359" s="1" t="s">
-        <v>1316</v>
       </c>
       <c r="J359" s="6" t="s">
         <v>671</v>
@@ -18492,16 +18491,16 @@
     </row>
     <row r="360" ht="18.0" customHeight="1">
       <c r="A360" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B360" s="8" t="s">
         <v>1317</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="G360" s="10" t="s">
         <v>1318</v>
       </c>
-      <c r="G360" s="1" t="s">
+      <c r="I360" s="1" t="s">
         <v>1319</v>
-      </c>
-      <c r="I360" s="1" t="s">
-        <v>1320</v>
       </c>
       <c r="J360" s="6" t="s">
         <v>671</v>
@@ -18521,16 +18520,16 @@
     </row>
     <row r="361" ht="18.0" customHeight="1">
       <c r="A361" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B361" s="4" t="s">
         <v>1321</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="G361" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="G361" s="1" t="s">
+      <c r="I361" s="1" t="s">
         <v>1323</v>
-      </c>
-      <c r="I361" s="1" t="s">
-        <v>1324</v>
       </c>
       <c r="J361" s="6" t="s">
         <v>671</v>
@@ -18549,16 +18548,16 @@
     </row>
     <row r="362" ht="18.0" customHeight="1">
       <c r="A362" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B362" s="4" t="s">
         <v>1325</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="G362" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="G362" s="1" t="s">
+      <c r="I362" s="1" t="s">
         <v>1327</v>
-      </c>
-      <c r="I362" s="1" t="s">
-        <v>1328</v>
       </c>
       <c r="J362" s="6" t="s">
         <v>671</v>
@@ -18577,16 +18576,16 @@
     </row>
     <row r="363" ht="18.0" customHeight="1">
       <c r="A363" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B363" s="4" t="s">
         <v>1329</v>
       </c>
-      <c r="B363" s="4" t="s">
+      <c r="G363" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="G363" s="1" t="s">
+      <c r="I363" s="1" t="s">
         <v>1331</v>
-      </c>
-      <c r="I363" s="1" t="s">
-        <v>1332</v>
       </c>
       <c r="J363" s="6" t="s">
         <v>671</v>
@@ -18605,16 +18604,16 @@
     </row>
     <row r="364" ht="18.0" customHeight="1">
       <c r="A364" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B364" s="4" t="s">
         <v>1333</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="G364" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="G364" s="1" t="s">
+      <c r="I364" s="1" t="s">
         <v>1335</v>
-      </c>
-      <c r="I364" s="1" t="s">
-        <v>1336</v>
       </c>
       <c r="J364" s="6" t="s">
         <v>671</v>
@@ -18633,16 +18632,16 @@
     </row>
     <row r="365" ht="18.0" customHeight="1">
       <c r="A365" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B365" s="4" t="s">
         <v>1337</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="G365" s="7" t="s">
         <v>1338</v>
       </c>
-      <c r="G365" s="7" t="s">
+      <c r="I365" s="1" t="s">
         <v>1339</v>
-      </c>
-      <c r="I365" s="1" t="s">
-        <v>1340</v>
       </c>
       <c r="J365" s="6" t="s">
         <v>671</v>
@@ -18661,16 +18660,16 @@
     </row>
     <row r="366" ht="18.0" customHeight="1">
       <c r="A366" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B366" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="G366" s="7" t="s">
         <v>1342</v>
       </c>
-      <c r="G366" s="7" t="s">
+      <c r="I366" s="1" t="s">
         <v>1343</v>
-      </c>
-      <c r="I366" s="1" t="s">
-        <v>1344</v>
       </c>
       <c r="J366" s="6" t="s">
         <v>671</v>
@@ -18689,16 +18688,16 @@
     </row>
     <row r="367" ht="18.0" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B367" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G367" s="7" t="s">
         <v>1345</v>
       </c>
-      <c r="G367" s="7" t="s">
+      <c r="I367" s="1" t="s">
         <v>1346</v>
-      </c>
-      <c r="I367" s="1" t="s">
-        <v>1347</v>
       </c>
       <c r="J367" s="6" t="s">
         <v>671</v>
@@ -18717,16 +18716,16 @@
     </row>
     <row r="368" ht="18.0" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B368" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G368" s="7" t="s">
         <v>1348</v>
       </c>
-      <c r="G368" s="7" t="s">
+      <c r="I368" s="1" t="s">
         <v>1349</v>
-      </c>
-      <c r="I368" s="1" t="s">
-        <v>1350</v>
       </c>
       <c r="J368" s="6" t="s">
         <v>671</v>
@@ -18745,16 +18744,16 @@
     </row>
     <row r="369" ht="18.0" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B369" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G369" s="7" t="s">
         <v>1351</v>
       </c>
-      <c r="G369" s="7" t="s">
+      <c r="I369" s="1" t="s">
         <v>1352</v>
-      </c>
-      <c r="I369" s="1" t="s">
-        <v>1353</v>
       </c>
       <c r="J369" s="6" t="s">
         <v>671</v>
@@ -18773,16 +18772,16 @@
     </row>
     <row r="370" ht="18.0" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B370" s="4" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G370" s="7" t="s">
         <v>1354</v>
       </c>
-      <c r="G370" s="7" t="s">
+      <c r="I370" s="1" t="s">
         <v>1355</v>
-      </c>
-      <c r="I370" s="1" t="s">
-        <v>1356</v>
       </c>
       <c r="J370" s="6" t="s">
         <v>671</v>
@@ -18801,16 +18800,16 @@
     </row>
     <row r="371" ht="18.0" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B371" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G371" s="7" t="s">
         <v>1357</v>
       </c>
-      <c r="G371" s="7" t="s">
+      <c r="I371" s="1" t="s">
         <v>1358</v>
-      </c>
-      <c r="I371" s="1" t="s">
-        <v>1359</v>
       </c>
       <c r="J371" s="6" t="s">
         <v>671</v>
@@ -18829,16 +18828,16 @@
     </row>
     <row r="372" ht="18.0" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B372" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="G372" s="7" t="s">
         <v>1360</v>
       </c>
-      <c r="G372" s="7" t="s">
+      <c r="I372" s="1" t="s">
         <v>1361</v>
-      </c>
-      <c r="I372" s="1" t="s">
-        <v>1362</v>
       </c>
       <c r="J372" s="6" t="s">
         <v>671</v>
@@ -18857,16 +18856,16 @@
     </row>
     <row r="373" ht="18.0" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B373" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G373" s="7" t="s">
         <v>1363</v>
       </c>
-      <c r="G373" s="7" t="s">
+      <c r="I373" s="1" t="s">
         <v>1364</v>
-      </c>
-      <c r="I373" s="1" t="s">
-        <v>1365</v>
       </c>
       <c r="J373" s="6" t="s">
         <v>671</v>
@@ -18885,16 +18884,16 @@
     </row>
     <row r="374" ht="18.0" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B374" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G374" s="7" t="s">
         <v>1366</v>
       </c>
-      <c r="G374" s="7" t="s">
+      <c r="I374" s="1" t="s">
         <v>1367</v>
-      </c>
-      <c r="I374" s="1" t="s">
-        <v>1368</v>
       </c>
       <c r="J374" s="6" t="s">
         <v>671</v>
@@ -18913,16 +18912,16 @@
     </row>
     <row r="375" ht="18.0" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B375" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G375" s="7" t="s">
         <v>1369</v>
       </c>
-      <c r="G375" s="7" t="s">
+      <c r="I375" s="1" t="s">
         <v>1370</v>
-      </c>
-      <c r="I375" s="1" t="s">
-        <v>1371</v>
       </c>
       <c r="J375" s="6" t="s">
         <v>671</v>
@@ -18941,16 +18940,16 @@
     </row>
     <row r="376" ht="18.0" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B376" s="4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G376" s="7" t="s">
         <v>1372</v>
       </c>
-      <c r="G376" s="7" t="s">
+      <c r="I376" s="1" t="s">
         <v>1373</v>
-      </c>
-      <c r="I376" s="1" t="s">
-        <v>1374</v>
       </c>
       <c r="J376" s="6" t="s">
         <v>671</v>
@@ -18969,16 +18968,16 @@
     </row>
     <row r="377" ht="18.0" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B377" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G377" s="7" t="s">
         <v>1375</v>
       </c>
-      <c r="G377" s="7" t="s">
+      <c r="I377" s="1" t="s">
         <v>1376</v>
-      </c>
-      <c r="I377" s="1" t="s">
-        <v>1377</v>
       </c>
       <c r="J377" s="6" t="s">
         <v>671</v>
@@ -18997,16 +18996,16 @@
     </row>
     <row r="378" ht="18.0" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B378" s="4" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G378" s="7" t="s">
         <v>1378</v>
       </c>
-      <c r="G378" s="7" t="s">
+      <c r="I378" s="1" t="s">
         <v>1379</v>
-      </c>
-      <c r="I378" s="1" t="s">
-        <v>1380</v>
       </c>
       <c r="J378" s="6" t="s">
         <v>671</v>
@@ -19025,16 +19024,16 @@
     </row>
     <row r="379" ht="18.0" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B379" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G379" s="7" t="s">
         <v>1381</v>
       </c>
-      <c r="G379" s="7" t="s">
+      <c r="I379" s="1" t="s">
         <v>1382</v>
-      </c>
-      <c r="I379" s="1" t="s">
-        <v>1383</v>
       </c>
       <c r="J379" s="6" t="s">
         <v>671</v>
@@ -19053,16 +19052,16 @@
     </row>
     <row r="380" ht="18.0" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B380" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G380" s="7" t="s">
         <v>1384</v>
       </c>
-      <c r="G380" s="7" t="s">
+      <c r="I380" s="1" t="s">
         <v>1385</v>
-      </c>
-      <c r="I380" s="1" t="s">
-        <v>1386</v>
       </c>
       <c r="J380" s="6" t="s">
         <v>671</v>
@@ -19081,16 +19080,16 @@
     </row>
     <row r="381" ht="18.0" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B381" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G381" s="7" t="s">
         <v>1387</v>
       </c>
-      <c r="G381" s="7" t="s">
+      <c r="I381" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="I381" s="1" t="s">
-        <v>1389</v>
       </c>
       <c r="J381" s="6" t="s">
         <v>671</v>
@@ -19109,16 +19108,16 @@
     </row>
     <row r="382" ht="18.0" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B382" s="4" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G382" s="7" t="s">
         <v>1390</v>
       </c>
-      <c r="G382" s="7" t="s">
+      <c r="I382" s="1" t="s">
         <v>1391</v>
-      </c>
-      <c r="I382" s="1" t="s">
-        <v>1392</v>
       </c>
       <c r="J382" s="6" t="s">
         <v>671</v>
@@ -19137,16 +19136,16 @@
     </row>
     <row r="383" ht="18.0" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B383" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G383" s="7" t="s">
         <v>1393</v>
       </c>
-      <c r="G383" s="7" t="s">
+      <c r="I383" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="I383" s="1" t="s">
-        <v>1395</v>
       </c>
       <c r="J383" s="6" t="s">
         <v>671</v>
@@ -19166,23 +19165,23 @@
     </row>
     <row r="384" ht="18.0" customHeight="1">
       <c r="A384" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B384" s="4" t="s">
         <v>1396</v>
       </c>
-      <c r="B384" s="4" t="s">
+      <c r="I384" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="I384" s="1" t="s">
+      <c r="J384" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="K384" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/22_01.png</v>
+      </c>
+      <c r="L384" s="2" t="s">
         <v>1398</v>
-      </c>
-      <c r="J384" s="6" t="s">
-        <v>671</v>
-      </c>
-      <c r="K384" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/22_01.png</v>
-      </c>
-      <c r="L384" s="2" t="s">
-        <v>1399</v>
       </c>
       <c r="M384" s="3" t="s">
         <v>21</v>
@@ -19191,14 +19190,14 @@
     </row>
     <row r="385" ht="18.0" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B385" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="I385" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="I385" s="1" t="s">
-        <v>1401</v>
-      </c>
       <c r="J385" s="6" t="s">
         <v>671</v>
       </c>
@@ -19207,7 +19206,7 @@
         <v>/22_02.png</v>
       </c>
       <c r="L385" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M385" s="3" t="s">
         <v>22</v>
@@ -19216,14 +19215,14 @@
     </row>
     <row r="386" ht="18.0" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B386" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="I386" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="I386" s="1" t="s">
-        <v>1403</v>
-      </c>
       <c r="J386" s="6" t="s">
         <v>671</v>
       </c>
@@ -19232,7 +19231,7 @@
         <v>/22_03.png</v>
       </c>
       <c r="L386" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M386" s="3" t="s">
         <v>30</v>
@@ -19241,14 +19240,14 @@
     </row>
     <row r="387" ht="18.0" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B387" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I387" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="I387" s="1" t="s">
-        <v>1405</v>
-      </c>
       <c r="J387" s="6" t="s">
         <v>671</v>
       </c>
@@ -19257,7 +19256,7 @@
         <v>/22_04.png</v>
       </c>
       <c r="L387" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M387" s="3" t="s">
         <v>38</v>
@@ -19266,14 +19265,14 @@
     </row>
     <row r="388" ht="18.0" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B388" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I388" s="1" t="s">
         <v>1406</v>
       </c>
-      <c r="I388" s="1" t="s">
-        <v>1407</v>
-      </c>
       <c r="J388" s="6" t="s">
         <v>671</v>
       </c>
@@ -19282,7 +19281,7 @@
         <v>/22_05.png</v>
       </c>
       <c r="L388" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M388" s="3" t="s">
         <v>47</v>
@@ -19291,14 +19290,14 @@
     </row>
     <row r="389" ht="18.0" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B389" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="I389" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="I389" s="1" t="s">
-        <v>1409</v>
-      </c>
       <c r="J389" s="6" t="s">
         <v>671</v>
       </c>
@@ -19307,7 +19306,7 @@
         <v>/22_06.png</v>
       </c>
       <c r="L389" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M389" s="3" t="s">
         <v>55</v>
@@ -19316,14 +19315,14 @@
     </row>
     <row r="390" ht="18.0" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B390" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="I390" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="I390" s="1" t="s">
-        <v>1411</v>
-      </c>
       <c r="J390" s="6" t="s">
         <v>671</v>
       </c>
@@ -19332,7 +19331,7 @@
         <v>/22_07.png</v>
       </c>
       <c r="L390" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M390" s="3" t="s">
         <v>63</v>
@@ -19341,14 +19340,14 @@
     </row>
     <row r="391" ht="18.0" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B391" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="I391" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="I391" s="1" t="s">
-        <v>1413</v>
-      </c>
       <c r="J391" s="6" t="s">
         <v>671</v>
       </c>
@@ -19357,7 +19356,7 @@
         <v>/22_08.png</v>
       </c>
       <c r="L391" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="M391" s="3" t="s">
         <v>70</v>
@@ -19366,23 +19365,23 @@
     </row>
     <row r="392" ht="18.0" customHeight="1">
       <c r="A392" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B392" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="B392" s="4" t="s">
+      <c r="I392" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="I392" s="1" t="s">
+      <c r="J392" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="K392" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/23_01.png</v>
+      </c>
+      <c r="L392" s="2" t="s">
         <v>1416</v>
-      </c>
-      <c r="J392" s="6" t="s">
-        <v>671</v>
-      </c>
-      <c r="K392" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/23_01.png</v>
-      </c>
-      <c r="L392" s="2" t="s">
-        <v>1417</v>
       </c>
       <c r="M392" s="3" t="s">
         <v>21</v>
@@ -19391,14 +19390,14 @@
     </row>
     <row r="393" ht="18.0" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B393" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="I393" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="I393" s="1" t="s">
-        <v>1419</v>
-      </c>
       <c r="J393" s="6" t="s">
         <v>671</v>
       </c>
@@ -19407,7 +19406,7 @@
         <v>/23_02.png</v>
       </c>
       <c r="L393" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="M393" s="3" t="s">
         <v>22</v>
@@ -19416,14 +19415,14 @@
     </row>
     <row r="394" ht="18.0" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B394" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I394" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="I394" s="1" t="s">
-        <v>1421</v>
-      </c>
       <c r="J394" s="6" t="s">
         <v>671</v>
       </c>
@@ -19432,7 +19431,7 @@
         <v>/23_03.png</v>
       </c>
       <c r="L394" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="M394" s="3" t="s">
         <v>30</v>
@@ -19441,14 +19440,14 @@
     </row>
     <row r="395" ht="18.0" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B395" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I395" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="I395" s="1" t="s">
-        <v>1423</v>
-      </c>
       <c r="J395" s="6" t="s">
         <v>671</v>
       </c>
@@ -19457,7 +19456,7 @@
         <v>/23_04.png</v>
       </c>
       <c r="L395" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="M395" s="3" t="s">
         <v>38</v>
@@ -19466,14 +19465,14 @@
     </row>
     <row r="396" ht="18.0" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B396" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I396" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="I396" s="1" t="s">
-        <v>1425</v>
-      </c>
       <c r="J396" s="6" t="s">
         <v>671</v>
       </c>
@@ -19482,7 +19481,7 @@
         <v>/23_05.png</v>
       </c>
       <c r="L396" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="M396" s="3" t="s">
         <v>47</v>
@@ -19491,14 +19490,14 @@
     </row>
     <row r="397" ht="18.0" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B397" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="I397" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="I397" s="1" t="s">
-        <v>1427</v>
-      </c>
       <c r="J397" s="6" t="s">
         <v>671</v>
       </c>
@@ -19507,7 +19506,7 @@
         <v>/23_06.png</v>
       </c>
       <c r="L397" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="M397" s="3" t="s">
         <v>55</v>
@@ -19516,23 +19515,23 @@
     </row>
     <row r="398" ht="18.0" customHeight="1">
       <c r="A398" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B398" s="4" t="s">
         <v>1428</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="I398" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="I398" s="1" t="s">
+      <c r="J398" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="K398" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>/24_01.png</v>
+      </c>
+      <c r="L398" s="2" t="s">
         <v>1430</v>
-      </c>
-      <c r="J398" s="6" t="s">
-        <v>671</v>
-      </c>
-      <c r="K398" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>/24_01.png</v>
-      </c>
-      <c r="L398" s="2" t="s">
-        <v>1431</v>
       </c>
       <c r="M398" s="3" t="s">
         <v>21</v>
@@ -19541,14 +19540,14 @@
     </row>
     <row r="399" ht="18.0" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B399" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I399" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="I399" s="1" t="s">
-        <v>1433</v>
-      </c>
       <c r="J399" s="6" t="s">
         <v>671</v>
       </c>
@@ -19557,7 +19556,7 @@
         <v>/24_02.png</v>
       </c>
       <c r="L399" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M399" s="3" t="s">
         <v>22</v>
@@ -19566,14 +19565,14 @@
     </row>
     <row r="400" ht="18.0" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B400" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="I400" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="I400" s="1" t="s">
-        <v>1435</v>
-      </c>
       <c r="J400" s="6" t="s">
         <v>671</v>
       </c>
@@ -19582,7 +19581,7 @@
         <v>/24_03.png</v>
       </c>
       <c r="L400" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M400" s="3" t="s">
         <v>30</v>
@@ -19591,14 +19590,14 @@
     </row>
     <row r="401" ht="18.0" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B401" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="I401" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="I401" s="1" t="s">
-        <v>1437</v>
-      </c>
       <c r="J401" s="6" t="s">
         <v>671</v>
       </c>
@@ -19607,7 +19606,7 @@
         <v>/24_04.png</v>
       </c>
       <c r="L401" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M401" s="3" t="s">
         <v>38</v>
@@ -19616,14 +19615,14 @@
     </row>
     <row r="402" ht="18.0" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B402" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="I402" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="I402" s="1" t="s">
-        <v>1439</v>
-      </c>
       <c r="J402" s="6" t="s">
         <v>671</v>
       </c>
@@ -19632,7 +19631,7 @@
         <v>/24_05.png</v>
       </c>
       <c r="L402" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M402" s="3" t="s">
         <v>47</v>
@@ -19641,14 +19640,14 @@
     </row>
     <row r="403" ht="18.0" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B403" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="I403" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="I403" s="1" t="s">
-        <v>1441</v>
-      </c>
       <c r="J403" s="6" t="s">
         <v>671</v>
       </c>
@@ -19657,7 +19656,7 @@
         <v>/24_06.png</v>
       </c>
       <c r="L403" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M403" s="3" t="s">
         <v>55</v>
@@ -19666,14 +19665,14 @@
     </row>
     <row r="404" ht="18.0" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B404" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="I404" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="I404" s="1" t="s">
-        <v>1443</v>
-      </c>
       <c r="J404" s="6" t="s">
         <v>671</v>
       </c>
@@ -19682,7 +19681,7 @@
         <v>/24_07.png</v>
       </c>
       <c r="L404" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M404" s="3" t="s">
         <v>63</v>
@@ -19691,14 +19690,14 @@
     </row>
     <row r="405" ht="18.0" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B405" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I405" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="I405" s="1" t="s">
-        <v>1445</v>
-      </c>
       <c r="J405" s="6" t="s">
         <v>671</v>
       </c>
@@ -19707,7 +19706,7 @@
         <v>/24_08.png</v>
       </c>
       <c r="L405" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M405" s="3" t="s">
         <v>70</v>

--- a/計画-事例集.xlsx
+++ b/計画-事例集.xlsx
@@ -1141,7 +1141,7 @@
     <t>A.パラディオ</t>
   </si>
   <si>
-    <t>ルネサンス後期にA.パラディオの設計された裁判所。視聴者に古典的なファサードを付加、1階を開放的なアーケード都市、アーチの間にドリス式オダーをおいている。</t>
+    <t>ルネサンス後期にA.パラディオの設計された裁判所。視聴者に古典的なファサードを付加、1階を開放的なアーケード都市、アーチの間にドリス式オーダーをおいている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images/02_21.png</t>
@@ -4036,7 +4036,7 @@
     </r>
   </si>
   <si>
-    <t>ンルバーハット</t>
+    <t>シルバーハット</t>
   </si>
   <si>
     <t>伊東豊雄、鉄骨フレ ー ム・アルミ板・テント</t>
@@ -6433,7 +6433,7 @@
     <t>プロムナード多摩中央</t>
   </si>
   <si>
-    <t>多摩ニュ ー タウンに建つ集合住宅。街路に面して開かれたフリー スペ ー ス(ル ー ム)と呼ばれる 1 室を持つ。この室で趣味活動などを通しての暮らしの充実と,通りのにぎわいの創出を狙ったという。</t>
+    <t>街区のほぼ中央にある歩行者専用道に面した設置階の住戸に居住者が趣味や創作活動のアトリエ、教室等に利用することを想定した「フリースペース」と称する一室を設けることによって、沿道の賑わいや親しみのある景観形成を意図している。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//07_17.png</t>
@@ -6892,7 +6892,7 @@
     <t>世田谷区深沢環境共生住宅</t>
   </si>
   <si>
-    <t>木造平家建ての公営住宅の建替えに当たり,高木の保存,井戸の活用,優良土壌の再利用,古材の使用等,既存環境を継承し,屋上緑化,ソ ー ラ ー 暖房,風力発電など環境共生技術を盛込み,高齢者在宅サ ー ビスセンタ ー を併設したシルバ ー ハウジング・プロジェクトを含んでおり,人と人との共生についても配慮した設計がなされている。</t>
+    <t>木造平屋建の住宅団地の建て替え計画により建設され、高木の保存、井戸の活用、優良土壌の再利用、古材の使用等、既存環境の継承を意図している。高齢者在宅サ ー ビスセンタ ー を併設したシルバ ー ハウジング・プロジェクトを含んでおり,人と人との共生についても配慮した設計がなされている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//07_26.png</t>
@@ -10409,7 +10409,7 @@
     <t>ロサンゼルス近代美術館</t>
   </si>
   <si>
-    <t>1979 年に創設され, 1988 年にフランク・ゲ ー リ ー の設計による分館が完成し,さらに 1998 年に磯崎新の設計による新館が開館した。新館は,地下に展示スペ ー スを埋設した低層の建築物で,中央には自由に行き来できる通路兼広場があり,赤砂岩の外壁を持っ基壇部の上にビラミッド型のトップライトなどが配置されている。</t>
+    <t>磯崎新、赤砂岩の外壁をもつ基壇部があり、その基壇部の上にピラミッド型のトップライトが配置されている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_18.png</t>
@@ -10455,7 +10455,7 @@
     <t>フォートワース現代美術館</t>
   </si>
   <si>
-    <t>1892 年に創設され,現代の建物は,安藤忠雄の設計により 2002年に完成したものである。周囲に池を配し平行に並べられた長方形の室によって展示室が構成され,日差しへの配慮から深い庇が掛けられ,それをコンクリ ー ト打放しの Y 字型の柱で支えている。なお,隣接した敷地には,ルイス・カ ー ンの設計により 1972 年に開館したキンベル美術館が建っている。</t>
+    <t>安藤忠雄、平行に並べられた長方形の室によって展示室が構成されその展示室には日差しへの配慮から深い庇がかけられている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_19.png</t>
@@ -10593,7 +10593,7 @@
     <t>キンベル美術館</t>
   </si>
   <si>
-    <t>基壇状の地上階を覆う屋根には, 1 体が 6.5m&gt;&lt;30m の RC 造ヴォ ー ルトを用い前庭を囲んで合計 16 体を 6 &gt;&lt; 3 列に並へており,正面の妻壁には 6 つの連続したサイクロイド曲線のスカイラインが現れている。ヴォ ー ルトの頂部には,線状のトップライトが設けられ,点在する中庭に面した開口部とともに室内に昼光を採り人れている。</t>
+    <t>基壇状の地上階を覆う屋根には, 1 体が 6.5m×30m の RC 造ヴォ ー ルトを用い前庭を囲んで合計 16 体を 6×3 列に並へており,正面の妻壁には 6 つの連続したサイクロイド曲線のスカイラインが現れている。ヴォ ー ルトの頂部には,線状のトップライトが設けられ,点在する中庭に面した開口部とともに室内に昼光を採り人れている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_22.png</t>
@@ -10688,7 +10688,7 @@
     <t>聖路加国際病院</t>
   </si>
   <si>
-    <t>三角形平面の 11 階建ての病棟 2 棟と外来・中央診療部門などを有する 5 階建ての診療棟からなる。フライノ ヾ シ ー 確保のため, 520 床のほぼ全病室が,シングルケアユニットと呼ばれるトイレ・シャワ ー 付きの個室であり,陽が射すように配置されている。老朽化した旧病院周辺の再開発に当たって,複数の街区にわたる特定街区制度を採用し,医職・住・学・悠を融合させた新たな都市環境の形成を図った。第 1 街区は A ・レ ー モンド設計の礼拝堂の保存と看護大学,第2 街区は新病院,第 3 街区は聖路加タワ ー (ホテルを含むオフイス棟)と聖路加レジデンス(高齢者向けケア付きマンション)。</t>
+    <t>520床のほぼ全病室が、シングルユニットと呼ばれるトイレ、シャワー付きの個室で構成されている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//12_02.png</t>
@@ -11169,7 +11169,7 @@
     <t>水戸芸術館</t>
   </si>
   <si>
-    <t>コンサ ー トホ ー ル,劇場,現代美術ギャラリ ー ,会議場等の文化施設が,それぞれ独自に活動できる独立性の高い空間を保ちつつ,共通のエントランスホ ー ルによって相互の融合を図った総合芸術文化センタ ー 。水戸市の中心部に近く,市民の広場としても機能している。</t>
+    <t>コンサートホール,劇場,現代美術ギャラリー ,会議場等の文化施設が,それぞれ独自に活動できる独立性の高い空間を保ちつつ,共通のエントランスホ ー ルによって相互の融合を図った総合芸術文化センター。市の中心部に近く,市民の広場としても機能している。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//14_03.png</t>
@@ -11583,7 +11583,7 @@
     <t>最高裁判所庁舎</t>
   </si>
   <si>
-    <t>各棟は,複数の軸に沿って配置されており,「スへ ー ス・ウォ ー ル」と呼ば、れる 4 ~ 6 m の厚さをもつ 2 重壁によって結びつけられている。この 2 重壁は,廊下・階段・便所等の機能をもつ空間となっている。建物高さは,最頂部で国会議事堂の高さと同等になるように計画されている。</t>
+    <t>各棟は,複数の軸に沿って配置されており,「スペース・ウォール」と呼ばれる 4 ~ 6 m の厚さをもつ 2 重壁によって結びつけられている。この 2 重壁は,廊下・階段・便所等の機能をもつ空間となっている。建物高さは,最頂部で国会議事堂の高さと同等になるように計画されている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//14_11.png</t>
@@ -17185,7 +17185,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -17219,6 +17219,10 @@
       <color theme="10"/>
       <name val="游ゴシック"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -17234,7 +17238,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -17253,6 +17257,9 @@
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -17262,13 +17269,19 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -19807,7 +19820,7 @@
       <c r="F57" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="6" t="s">
         <v>358</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -20839,7 +20852,7 @@
       <c r="G86" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="I86" s="6" t="s">
+      <c r="I86" s="7" t="s">
         <v>520</v>
       </c>
       <c r="J86" s="2" t="s">
@@ -20872,7 +20885,7 @@
       <c r="G87" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="I87" s="6" t="s">
+      <c r="I87" s="7" t="s">
         <v>527</v>
       </c>
       <c r="J87" s="2" t="s">
@@ -20905,7 +20918,7 @@
       <c r="G88" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="I88" s="6" t="s">
+      <c r="I88" s="7" t="s">
         <v>534</v>
       </c>
       <c r="J88" s="2" t="s">
@@ -20938,7 +20951,7 @@
       <c r="G89" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="I89" s="6" t="s">
+      <c r="I89" s="7" t="s">
         <v>541</v>
       </c>
       <c r="J89" s="2" t="s">
@@ -20974,7 +20987,7 @@
       <c r="G90" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="I90" s="6" t="s">
+      <c r="I90" s="7" t="s">
         <v>549</v>
       </c>
       <c r="J90" s="2" t="s">
@@ -21010,7 +21023,7 @@
       <c r="G91" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="I91" s="6" t="s">
+      <c r="I91" s="7" t="s">
         <v>555</v>
       </c>
       <c r="J91" s="2" t="s">
@@ -21049,7 +21062,7 @@
       <c r="G92" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="I92" s="6" t="s">
+      <c r="I92" s="7" t="s">
         <v>562</v>
       </c>
       <c r="J92" s="2" t="s">
@@ -21085,7 +21098,7 @@
       <c r="G93" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="I93" s="6" t="s">
+      <c r="I93" s="7" t="s">
         <v>569</v>
       </c>
       <c r="J93" s="2" t="s">
@@ -21121,7 +21134,7 @@
       <c r="G94" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="I94" s="6" t="s">
+      <c r="I94" s="7" t="s">
         <v>574</v>
       </c>
       <c r="J94" s="2" t="s">
@@ -21883,7 +21896,7 @@
       <c r="B122" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C122" s="8" t="s">
         <v>715</v>
       </c>
       <c r="G122" s="1" t="s">
@@ -21913,7 +21926,7 @@
       <c r="B123" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="C123" s="8" t="s">
         <v>721</v>
       </c>
       <c r="G123" s="1" t="s">
@@ -21943,28 +21956,28 @@
       <c r="B124" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="C124" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D124" s="8">
         <v>1935.0</v>
       </c>
-      <c r="E124" s="7" t="s">
+      <c r="E124" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="7" t="s">
+      <c r="G124" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="H124" s="7" t="s">
+      <c r="H124" s="8" t="s">
         <v>729</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="J124" s="6" t="s">
+      <c r="J124" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K124" s="1" t="str">
@@ -21986,28 +21999,28 @@
       <c r="B125" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C125" s="8" t="s">
         <v>734</v>
       </c>
       <c r="D125" s="1">
         <v>1927.0</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="E125" s="8" t="s">
         <v>108</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="7" t="s">
+      <c r="G125" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="H125" s="7" t="s">
+      <c r="H125" s="8" t="s">
         <v>736</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="J125" s="6" t="s">
+      <c r="J125" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K125" s="1" t="str">
@@ -22029,28 +22042,28 @@
       <c r="B126" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C126" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="8">
         <v>1941.0</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="H126" s="8" t="s">
         <v>742</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="J126" s="6" t="s">
+      <c r="J126" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K126" s="1" t="str">
@@ -22072,28 +22085,28 @@
       <c r="B127" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C127" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="D127" s="7">
+      <c r="D127" s="8">
         <v>1958.0</v>
       </c>
-      <c r="E127" s="7" t="s">
+      <c r="E127" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="G127" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="H127" s="7" t="s">
+      <c r="H127" s="8" t="s">
         <v>748</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="J127" s="6" t="s">
+      <c r="J127" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K127" s="1" t="str">
@@ -22115,28 +22128,28 @@
       <c r="B128" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="D128" s="7">
+      <c r="D128" s="8">
         <v>1961.0</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E128" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="7" t="s">
+      <c r="G128" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="H128" s="7" t="s">
+      <c r="H128" s="8" t="s">
         <v>754</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="J128" s="6" t="s">
+      <c r="J128" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K128" s="1" t="str">
@@ -22155,16 +22168,16 @@
       <c r="A129" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="B129" s="8" t="s">
+      <c r="B129" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="G129" s="7" t="s">
+      <c r="G129" s="8" t="s">
         <v>758</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="J129" s="6" t="s">
+      <c r="J129" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K129" s="1" t="str">
@@ -22183,16 +22196,16 @@
       <c r="A130" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B130" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="G130" s="7" t="s">
+      <c r="G130" s="8" t="s">
         <v>762</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="J130" s="6" t="s">
+      <c r="J130" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K130" s="1" t="str">
@@ -22211,16 +22224,16 @@
       <c r="A131" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="B131" s="8" t="s">
+      <c r="B131" s="9" t="s">
         <v>765</v>
       </c>
-      <c r="G131" s="7" t="s">
+      <c r="G131" s="8" t="s">
         <v>766</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="J131" s="6" t="s">
+      <c r="J131" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K131" s="1" t="str">
@@ -22239,16 +22252,16 @@
       <c r="A132" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B132" s="9" t="s">
         <v>769</v>
       </c>
-      <c r="G132" s="7" t="s">
+      <c r="G132" s="8" t="s">
         <v>770</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="J132" s="6" t="s">
+      <c r="J132" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K132" s="1" t="str">
@@ -22267,16 +22280,16 @@
       <c r="A133" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="B133" s="8" t="s">
+      <c r="B133" s="9" t="s">
         <v>773</v>
       </c>
-      <c r="G133" s="7" t="s">
+      <c r="G133" s="8" t="s">
         <v>774</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="J133" s="6" t="s">
+      <c r="J133" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K133" s="1" t="str">
@@ -22295,16 +22308,16 @@
       <c r="A134" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="G134" s="7" t="s">
+      <c r="G134" s="8" t="s">
         <v>778</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="J134" s="6" t="s">
+      <c r="J134" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K134" s="1" t="str">
@@ -22323,16 +22336,16 @@
       <c r="A135" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="9" t="s">
         <v>781</v>
       </c>
-      <c r="G135" s="7" t="s">
+      <c r="G135" s="8" t="s">
         <v>782</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="J135" s="6" t="s">
+      <c r="J135" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K135" s="1" t="str">
@@ -22351,16 +22364,16 @@
       <c r="A136" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B136" s="8" t="s">
+      <c r="B136" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="G136" s="7" t="s">
+      <c r="G136" s="8" t="s">
         <v>786</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="J136" s="6" t="s">
+      <c r="J136" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K136" s="1" t="str">
@@ -22379,16 +22392,16 @@
       <c r="A137" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="B137" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="G137" s="8" t="s">
         <v>790</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="J137" s="6" t="s">
+      <c r="J137" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K137" s="1" t="str">
@@ -22407,16 +22420,16 @@
       <c r="A138" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B138" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="G138" s="7" t="s">
+      <c r="G138" s="8" t="s">
         <v>794</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="J138" s="6" t="s">
+      <c r="J138" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K138" s="1" t="str">
@@ -22435,16 +22448,16 @@
       <c r="A139" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="B139" s="8" t="s">
+      <c r="B139" s="9" t="s">
         <v>797</v>
       </c>
-      <c r="G139" s="7" t="s">
+      <c r="G139" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="I139" s="9" t="s">
+      <c r="I139" s="11" t="s">
         <v>799</v>
       </c>
-      <c r="J139" s="6" t="s">
+      <c r="J139" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K139" s="1" t="str">
@@ -22463,16 +22476,16 @@
       <c r="A140" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="B140" s="8" t="s">
+      <c r="B140" s="9" t="s">
         <v>801</v>
       </c>
-      <c r="G140" s="7" t="s">
+      <c r="G140" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="I140" s="9" t="s">
+      <c r="I140" s="11" t="s">
         <v>802</v>
       </c>
-      <c r="J140" s="6" t="s">
+      <c r="J140" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K140" s="1" t="str">
@@ -22491,16 +22504,16 @@
       <c r="A141" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="B141" s="8" t="s">
+      <c r="B141" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="G141" s="7" t="s">
+      <c r="G141" s="8" t="s">
         <v>805</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="J141" s="6" t="s">
+      <c r="J141" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K141" s="1" t="str">
@@ -22520,16 +22533,16 @@
       <c r="A142" s="4" t="s">
         <v>807</v>
       </c>
-      <c r="B142" s="8" t="s">
+      <c r="B142" s="9" t="s">
         <v>808</v>
       </c>
-      <c r="G142" s="7" t="s">
+      <c r="G142" s="8" t="s">
         <v>809</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="J142" s="6" t="s">
+      <c r="J142" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K142" s="1" t="str">
@@ -22549,16 +22562,16 @@
       <c r="A143" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="G143" s="7" t="s">
+      <c r="G143" s="8" t="s">
         <v>813</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="J143" s="6" t="s">
+      <c r="J143" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K143" s="1" t="str">
@@ -22578,16 +22591,16 @@
       <c r="A144" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="9" t="s">
         <v>816</v>
       </c>
-      <c r="G144" s="7" t="s">
+      <c r="G144" s="8" t="s">
         <v>817</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="J144" s="6" t="s">
+      <c r="J144" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K144" s="1" t="str">
@@ -22607,16 +22620,16 @@
       <c r="A145" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="B145" s="8" t="s">
+      <c r="B145" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="G145" s="7" t="s">
+      <c r="G145" s="8" t="s">
         <v>821</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="J145" s="6" t="s">
+      <c r="J145" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K145" s="1" t="str">
@@ -22636,16 +22649,16 @@
       <c r="A146" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="B146" s="8" t="s">
+      <c r="B146" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="G146" s="7" t="s">
+      <c r="G146" s="8" t="s">
         <v>825</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="J146" s="6" t="s">
+      <c r="J146" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K146" s="1" t="str">
@@ -22665,16 +22678,16 @@
       <c r="A147" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="B147" s="8" t="s">
+      <c r="B147" s="9" t="s">
         <v>828</v>
       </c>
-      <c r="G147" s="7" t="s">
+      <c r="G147" s="8" t="s">
         <v>829</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="J147" s="6" t="s">
+      <c r="J147" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K147" s="1" t="str">
@@ -22694,16 +22707,16 @@
       <c r="A148" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="B148" s="8" t="s">
+      <c r="B148" s="9" t="s">
         <v>832</v>
       </c>
-      <c r="G148" s="7" t="s">
+      <c r="G148" s="8" t="s">
         <v>833</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="J148" s="6" t="s">
+      <c r="J148" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K148" s="1" t="str">
@@ -22723,16 +22736,16 @@
       <c r="A149" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="B149" s="8" t="s">
+      <c r="B149" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="G149" s="7" t="s">
+      <c r="G149" s="8" t="s">
         <v>837</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="J149" s="6" t="s">
+      <c r="J149" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K149" s="1" t="str">
@@ -22752,16 +22765,16 @@
       <c r="A150" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B150" s="9" t="s">
         <v>840</v>
       </c>
-      <c r="G150" s="7" t="s">
+      <c r="G150" s="8" t="s">
         <v>841</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="J150" s="6" t="s">
+      <c r="J150" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K150" s="1" t="str">
@@ -22781,16 +22794,16 @@
       <c r="A151" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B151" s="9" t="s">
         <v>844</v>
       </c>
-      <c r="G151" s="7" t="s">
+      <c r="G151" s="8" t="s">
         <v>845</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="J151" s="6" t="s">
+      <c r="J151" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K151" s="1" t="str">
@@ -22810,16 +22823,16 @@
       <c r="A152" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="9" t="s">
         <v>848</v>
       </c>
-      <c r="G152" s="7" t="s">
+      <c r="G152" s="8" t="s">
         <v>849</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="J152" s="6" t="s">
+      <c r="J152" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K152" s="1" t="str">
@@ -22839,16 +22852,16 @@
       <c r="A153" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="9" t="s">
         <v>852</v>
       </c>
-      <c r="G153" s="7" t="s">
+      <c r="G153" s="8" t="s">
         <v>853</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="J153" s="6" t="s">
+      <c r="J153" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K153" s="1" t="str">
@@ -22868,16 +22881,16 @@
       <c r="A154" s="4" t="s">
         <v>855</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B154" s="9" t="s">
         <v>856</v>
       </c>
-      <c r="G154" s="7" t="s">
+      <c r="G154" s="8" t="s">
         <v>857</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="J154" s="6" t="s">
+      <c r="J154" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K154" s="1" t="str">
@@ -22897,16 +22910,16 @@
       <c r="A155" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B155" s="9" t="s">
         <v>860</v>
       </c>
-      <c r="G155" s="7" t="s">
+      <c r="G155" s="8" t="s">
         <v>861</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="J155" s="6" t="s">
+      <c r="J155" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K155" s="1" t="str">
@@ -22926,16 +22939,16 @@
       <c r="A156" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B156" s="9" t="s">
         <v>864</v>
       </c>
-      <c r="G156" s="7" t="s">
+      <c r="G156" s="8" t="s">
         <v>865</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="J156" s="6" t="s">
+      <c r="J156" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K156" s="1" t="str">
@@ -22955,16 +22968,16 @@
       <c r="A157" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="B157" s="8" t="s">
+      <c r="B157" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="G157" s="7" t="s">
+      <c r="G157" s="8" t="s">
         <v>869</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="J157" s="6" t="s">
+      <c r="J157" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K157" s="1" t="str">
@@ -22984,16 +22997,16 @@
       <c r="A158" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B158" s="9" t="s">
         <v>872</v>
       </c>
-      <c r="G158" s="7" t="s">
+      <c r="G158" s="8" t="s">
         <v>873</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="J158" s="6" t="s">
+      <c r="J158" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K158" s="1" t="str">
@@ -23013,16 +23026,16 @@
       <c r="A159" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B159" s="9" t="s">
         <v>876</v>
       </c>
-      <c r="G159" s="7" t="s">
+      <c r="G159" s="8" t="s">
         <v>877</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="J159" s="6" t="s">
+      <c r="J159" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K159" s="1" t="str">
@@ -23042,16 +23055,16 @@
       <c r="A160" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="B160" s="9" t="s">
         <v>880</v>
       </c>
-      <c r="G160" s="7" t="s">
+      <c r="G160" s="8" t="s">
         <v>881</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="J160" s="6" t="s">
+      <c r="J160" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K160" s="1" t="str">
@@ -23071,16 +23084,16 @@
       <c r="A161" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="B161" s="8" t="s">
+      <c r="B161" s="9" t="s">
         <v>884</v>
       </c>
-      <c r="G161" s="7" t="s">
+      <c r="G161" s="8" t="s">
         <v>885</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="J161" s="6" t="s">
+      <c r="J161" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K161" s="1" t="str">
@@ -23100,16 +23113,16 @@
       <c r="A162" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="G162" s="7" t="s">
+      <c r="G162" s="8" t="s">
         <v>889</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="J162" s="6" t="s">
+      <c r="J162" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K162" s="1" t="str">
@@ -23129,16 +23142,16 @@
       <c r="A163" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="B163" s="8" t="s">
+      <c r="B163" s="9" t="s">
         <v>892</v>
       </c>
-      <c r="G163" s="7" t="s">
+      <c r="G163" s="8" t="s">
         <v>893</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="J163" s="6" t="s">
+      <c r="J163" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K163" s="1" t="str">
@@ -23158,16 +23171,16 @@
       <c r="A164" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B164" s="9" t="s">
         <v>896</v>
       </c>
-      <c r="G164" s="7" t="s">
+      <c r="G164" s="8" t="s">
         <v>897</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="J164" s="6" t="s">
+      <c r="J164" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K164" s="1" t="str">
@@ -23184,19 +23197,19 @@
       <c r="O164" s="3"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="7" t="s">
+      <c r="A165" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="9" t="s">
         <v>900</v>
       </c>
-      <c r="G165" s="7" t="s">
+      <c r="G165" s="8" t="s">
         <v>901</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="J165" s="6" t="s">
+      <c r="J165" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K165" s="1" t="str">
@@ -23215,16 +23228,16 @@
       <c r="A166" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="B166" s="9" t="s">
         <v>904</v>
       </c>
-      <c r="G166" s="7" t="s">
+      <c r="G166" s="8" t="s">
         <v>905</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="J166" s="6" t="s">
+      <c r="J166" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K166" s="1" t="str">
@@ -23243,16 +23256,16 @@
       <c r="A167" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="B167" s="8" t="s">
+      <c r="B167" s="9" t="s">
         <v>908</v>
       </c>
-      <c r="G167" s="7" t="s">
+      <c r="G167" s="8" t="s">
         <v>909</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="J167" s="6" t="s">
+      <c r="J167" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K167" s="1" t="str">
@@ -23271,16 +23284,16 @@
       <c r="A168" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="B168" s="8" t="s">
+      <c r="B168" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="G168" s="7" t="s">
+      <c r="G168" s="8" t="s">
         <v>913</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="J168" s="6" t="s">
+      <c r="J168" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K168" s="1" t="str">
@@ -23299,16 +23312,16 @@
       <c r="A169" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="B169" s="8" t="s">
+      <c r="B169" s="9" t="s">
         <v>916</v>
       </c>
-      <c r="G169" s="7" t="s">
+      <c r="G169" s="8" t="s">
         <v>917</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="J169" s="6" t="s">
+      <c r="J169" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K169" s="1" t="str">
@@ -23327,16 +23340,16 @@
       <c r="A170" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="B170" s="9" t="s">
         <v>920</v>
       </c>
-      <c r="G170" s="7" t="s">
+      <c r="G170" s="8" t="s">
         <v>921</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="J170" s="6" t="s">
+      <c r="J170" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K170" s="1" t="str">
@@ -23355,16 +23368,16 @@
       <c r="A171" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="9" t="s">
         <v>924</v>
       </c>
-      <c r="G171" s="7" t="s">
+      <c r="G171" s="8" t="s">
         <v>925</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="J171" s="6" t="s">
+      <c r="J171" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K171" s="1" t="str">
@@ -23383,16 +23396,16 @@
       <c r="A172" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="B172" s="9" t="s">
         <v>928</v>
       </c>
-      <c r="G172" s="7" t="s">
+      <c r="G172" s="8" t="s">
         <v>929</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="J172" s="6" t="s">
+      <c r="J172" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K172" s="1" t="str">
@@ -23411,16 +23424,16 @@
       <c r="A173" s="4" t="s">
         <v>931</v>
       </c>
-      <c r="B173" s="8" t="s">
+      <c r="B173" s="9" t="s">
         <v>932</v>
       </c>
-      <c r="G173" s="7" t="s">
+      <c r="G173" s="8" t="s">
         <v>933</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="J173" s="6" t="s">
+      <c r="J173" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K173" s="1" t="str">
@@ -23439,16 +23452,16 @@
       <c r="A174" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="B174" s="8" t="s">
+      <c r="B174" s="9" t="s">
         <v>936</v>
       </c>
-      <c r="G174" s="7" t="s">
+      <c r="G174" s="8" t="s">
         <v>937</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="J174" s="6" t="s">
+      <c r="J174" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K174" s="1" t="str">
@@ -23467,16 +23480,16 @@
       <c r="A175" s="4" t="s">
         <v>939</v>
       </c>
-      <c r="B175" s="8" t="s">
+      <c r="B175" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="G175" s="7" t="s">
+      <c r="G175" s="8" t="s">
         <v>941</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="J175" s="6" t="s">
+      <c r="J175" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K175" s="1" t="str">
@@ -23495,16 +23508,16 @@
       <c r="A176" s="4" t="s">
         <v>943</v>
       </c>
-      <c r="B176" s="8" t="s">
+      <c r="B176" s="9" t="s">
         <v>944</v>
       </c>
-      <c r="G176" s="7" t="s">
+      <c r="G176" s="8" t="s">
         <v>945</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="J176" s="6" t="s">
+      <c r="J176" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K176" s="1" t="str">
@@ -23523,16 +23536,16 @@
       <c r="A177" s="4" t="s">
         <v>947</v>
       </c>
-      <c r="B177" s="8" t="s">
+      <c r="B177" s="9" t="s">
         <v>948</v>
       </c>
-      <c r="G177" s="7" t="s">
+      <c r="G177" s="8" t="s">
         <v>949</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="J177" s="6" t="s">
+      <c r="J177" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K177" s="1" t="str">
@@ -23551,16 +23564,16 @@
       <c r="A178" s="4" t="s">
         <v>951</v>
       </c>
-      <c r="B178" s="8" t="s">
+      <c r="B178" s="9" t="s">
         <v>952</v>
       </c>
-      <c r="G178" s="7" t="s">
+      <c r="G178" s="8" t="s">
         <v>953</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="J178" s="6" t="s">
+      <c r="J178" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K178" s="1" t="str">
@@ -23579,16 +23592,16 @@
       <c r="A179" s="4" t="s">
         <v>955</v>
       </c>
-      <c r="B179" s="8" t="s">
+      <c r="B179" s="9" t="s">
         <v>956</v>
       </c>
-      <c r="G179" s="7" t="s">
+      <c r="G179" s="8" t="s">
         <v>957</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="J179" s="6" t="s">
+      <c r="J179" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K179" s="1" t="str">
@@ -23607,16 +23620,16 @@
       <c r="A180" s="4" t="s">
         <v>959</v>
       </c>
-      <c r="B180" s="8" t="s">
+      <c r="B180" s="9" t="s">
         <v>960</v>
       </c>
-      <c r="G180" s="7" t="s">
+      <c r="G180" s="8" t="s">
         <v>961</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="J180" s="6" t="s">
+      <c r="J180" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K180" s="1" t="str">
@@ -23635,16 +23648,16 @@
       <c r="A181" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="B181" s="8" t="s">
+      <c r="B181" s="9" t="s">
         <v>964</v>
       </c>
-      <c r="G181" s="7" t="s">
+      <c r="G181" s="12" t="s">
         <v>965</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="J181" s="6" t="s">
+      <c r="J181" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K181" s="1" t="str">
@@ -23663,16 +23676,16 @@
       <c r="A182" s="4" t="s">
         <v>967</v>
       </c>
-      <c r="B182" s="8" t="s">
+      <c r="B182" s="9" t="s">
         <v>968</v>
       </c>
-      <c r="G182" s="7" t="s">
+      <c r="G182" s="8" t="s">
         <v>969</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="J182" s="6" t="s">
+      <c r="J182" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K182" s="1" t="str">
@@ -23692,16 +23705,16 @@
       <c r="A183" s="4" t="s">
         <v>971</v>
       </c>
-      <c r="B183" s="8" t="s">
+      <c r="B183" s="9" t="s">
         <v>972</v>
       </c>
-      <c r="G183" s="7" t="s">
+      <c r="G183" s="8" t="s">
         <v>973</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="J183" s="6" t="s">
+      <c r="J183" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K183" s="1" t="str">
@@ -23721,16 +23734,16 @@
       <c r="A184" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="B184" s="8" t="s">
+      <c r="B184" s="9" t="s">
         <v>976</v>
       </c>
-      <c r="G184" s="7" t="s">
+      <c r="G184" s="8" t="s">
         <v>977</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="J184" s="6" t="s">
+      <c r="J184" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K184" s="1" t="str">
@@ -23750,16 +23763,16 @@
       <c r="A185" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="B185" s="8" t="s">
+      <c r="B185" s="9" t="s">
         <v>980</v>
       </c>
-      <c r="G185" s="7" t="s">
+      <c r="G185" s="8" t="s">
         <v>981</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="J185" s="6" t="s">
+      <c r="J185" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K185" s="1" t="str">
@@ -23779,16 +23792,16 @@
       <c r="A186" s="4" t="s">
         <v>983</v>
       </c>
-      <c r="B186" s="8" t="s">
+      <c r="B186" s="9" t="s">
         <v>984</v>
       </c>
-      <c r="G186" s="7" t="s">
+      <c r="G186" s="8" t="s">
         <v>985</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="J186" s="6" t="s">
+      <c r="J186" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K186" s="1" t="str">
@@ -23808,16 +23821,16 @@
       <c r="A187" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="B187" s="8" t="s">
+      <c r="B187" s="9" t="s">
         <v>988</v>
       </c>
-      <c r="G187" s="7" t="s">
+      <c r="G187" s="8" t="s">
         <v>989</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="J187" s="6" t="s">
+      <c r="J187" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K187" s="1" t="str">
@@ -23837,16 +23850,16 @@
       <c r="A188" s="4" t="s">
         <v>991</v>
       </c>
-      <c r="B188" s="8" t="s">
+      <c r="B188" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="G188" s="7" t="s">
+      <c r="G188" s="8" t="s">
         <v>993</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="J188" s="6" t="s">
+      <c r="J188" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K188" s="1" t="str">
@@ -23866,16 +23879,16 @@
       <c r="A189" s="4" t="s">
         <v>995</v>
       </c>
-      <c r="B189" s="8" t="s">
+      <c r="B189" s="9" t="s">
         <v>996</v>
       </c>
-      <c r="G189" s="7" t="s">
+      <c r="G189" s="8" t="s">
         <v>997</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="J189" s="6" t="s">
+      <c r="J189" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K189" s="1" t="str">
@@ -23895,16 +23908,16 @@
       <c r="A190" s="4" t="s">
         <v>999</v>
       </c>
-      <c r="B190" s="8" t="s">
+      <c r="B190" s="9" t="s">
         <v>1000</v>
       </c>
-      <c r="G190" s="7" t="s">
+      <c r="G190" s="12" t="s">
         <v>1001</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="J190" s="6" t="s">
+      <c r="J190" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K190" s="1" t="str">
@@ -23924,16 +23937,16 @@
       <c r="A191" s="4" t="s">
         <v>1003</v>
       </c>
-      <c r="B191" s="8" t="s">
+      <c r="B191" s="9" t="s">
         <v>1004</v>
       </c>
-      <c r="G191" s="7" t="s">
+      <c r="G191" s="8" t="s">
         <v>1005</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="J191" s="6" t="s">
+      <c r="J191" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K191" s="1" t="str">
@@ -23953,16 +23966,16 @@
       <c r="A192" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="B192" s="8" t="s">
+      <c r="B192" s="9" t="s">
         <v>1008</v>
       </c>
-      <c r="G192" s="7" t="s">
+      <c r="G192" s="8" t="s">
         <v>1009</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="J192" s="6" t="s">
+      <c r="J192" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K192" s="1" t="str">
@@ -23982,16 +23995,16 @@
       <c r="A193" s="4" t="s">
         <v>1011</v>
       </c>
-      <c r="B193" s="8" t="s">
+      <c r="B193" s="9" t="s">
         <v>1012</v>
       </c>
-      <c r="G193" s="7" t="s">
+      <c r="G193" s="8" t="s">
         <v>1013</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="J193" s="6" t="s">
+      <c r="J193" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K193" s="1" t="str">
@@ -24011,16 +24024,16 @@
       <c r="A194" s="4" t="s">
         <v>1015</v>
       </c>
-      <c r="B194" s="8" t="s">
+      <c r="B194" s="9" t="s">
         <v>1016</v>
       </c>
-      <c r="G194" s="7" t="s">
+      <c r="G194" s="8" t="s">
         <v>1017</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="J194" s="6" t="s">
+      <c r="J194" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K194" s="1" t="str">
@@ -24040,16 +24053,16 @@
       <c r="A195" s="4" t="s">
         <v>1019</v>
       </c>
-      <c r="B195" s="8" t="s">
+      <c r="B195" s="9" t="s">
         <v>1020</v>
       </c>
-      <c r="G195" s="7" t="s">
+      <c r="G195" s="8" t="s">
         <v>1021</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="J195" s="6" t="s">
+      <c r="J195" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K195" s="1" t="str">
@@ -24069,16 +24082,16 @@
       <c r="A196" s="4" t="s">
         <v>1023</v>
       </c>
-      <c r="B196" s="8" t="s">
+      <c r="B196" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="G196" s="7" t="s">
+      <c r="G196" s="8" t="s">
         <v>1025</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="J196" s="6" t="s">
+      <c r="J196" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K196" s="1" t="str">
@@ -24098,16 +24111,16 @@
       <c r="A197" s="4" t="s">
         <v>1027</v>
       </c>
-      <c r="B197" s="8" t="s">
+      <c r="B197" s="9" t="s">
         <v>1028</v>
       </c>
-      <c r="G197" s="7" t="s">
+      <c r="G197" s="8" t="s">
         <v>1029</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="J197" s="6" t="s">
+      <c r="J197" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K197" s="1" t="str">
@@ -24127,16 +24140,16 @@
       <c r="A198" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="B198" s="8" t="s">
+      <c r="B198" s="9" t="s">
         <v>1032</v>
       </c>
-      <c r="G198" s="7" t="s">
+      <c r="G198" s="8" t="s">
         <v>1033</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="J198" s="6" t="s">
+      <c r="J198" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K198" s="1" t="str">
@@ -24156,16 +24169,16 @@
       <c r="A199" s="4" t="s">
         <v>1035</v>
       </c>
-      <c r="B199" s="8" t="s">
+      <c r="B199" s="9" t="s">
         <v>1036</v>
       </c>
-      <c r="G199" s="7" t="s">
+      <c r="G199" s="8" t="s">
         <v>1037</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="J199" s="6" t="s">
+      <c r="J199" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K199" s="1" t="str">
@@ -24185,16 +24198,16 @@
       <c r="A200" s="4" t="s">
         <v>1039</v>
       </c>
-      <c r="B200" s="8" t="s">
+      <c r="B200" s="9" t="s">
         <v>1040</v>
       </c>
-      <c r="G200" s="7" t="s">
+      <c r="G200" s="8" t="s">
         <v>1041</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="J200" s="6" t="s">
+      <c r="J200" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K200" s="1" t="str">
@@ -24214,16 +24227,16 @@
       <c r="A201" s="4" t="s">
         <v>1043</v>
       </c>
-      <c r="B201" s="8" t="s">
+      <c r="B201" s="9" t="s">
         <v>1044</v>
       </c>
-      <c r="G201" s="7" t="s">
+      <c r="G201" s="8" t="s">
         <v>1045</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="J201" s="6" t="s">
+      <c r="J201" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K201" s="1" t="str">
@@ -24243,16 +24256,16 @@
       <c r="A202" s="4" t="s">
         <v>1047</v>
       </c>
-      <c r="B202" s="8" t="s">
+      <c r="B202" s="9" t="s">
         <v>1048</v>
       </c>
-      <c r="G202" s="7" t="s">
+      <c r="G202" s="8" t="s">
         <v>1049</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="J202" s="6" t="s">
+      <c r="J202" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K202" s="1" t="str">
@@ -24272,16 +24285,16 @@
       <c r="A203" s="4" t="s">
         <v>1051</v>
       </c>
-      <c r="B203" s="8" t="s">
+      <c r="B203" s="9" t="s">
         <v>1052</v>
       </c>
-      <c r="G203" s="7" t="s">
+      <c r="G203" s="8" t="s">
         <v>1053</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="J203" s="6" t="s">
+      <c r="J203" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K203" s="1" t="str">
@@ -24301,16 +24314,16 @@
       <c r="A204" s="4" t="s">
         <v>1055</v>
       </c>
-      <c r="B204" s="8" t="s">
+      <c r="B204" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="G204" s="7" t="s">
+      <c r="G204" s="8" t="s">
         <v>1057</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="J204" s="6" t="s">
+      <c r="J204" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K204" s="1" t="str">
@@ -24330,16 +24343,16 @@
       <c r="A205" s="4" t="s">
         <v>1059</v>
       </c>
-      <c r="B205" s="8" t="s">
+      <c r="B205" s="9" t="s">
         <v>1060</v>
       </c>
-      <c r="G205" s="7" t="s">
+      <c r="G205" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="J205" s="6" t="s">
+      <c r="J205" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K205" s="1" t="str">
@@ -24359,16 +24372,16 @@
       <c r="A206" s="4" t="s">
         <v>1063</v>
       </c>
-      <c r="B206" s="8" t="s">
+      <c r="B206" s="9" t="s">
         <v>1064</v>
       </c>
-      <c r="G206" s="7" t="s">
+      <c r="G206" s="8" t="s">
         <v>1065</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="J206" s="6" t="s">
+      <c r="J206" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K206" s="1" t="str">
@@ -24388,16 +24401,16 @@
       <c r="A207" s="4" t="s">
         <v>1067</v>
       </c>
-      <c r="B207" s="8" t="s">
+      <c r="B207" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G207" s="7" t="s">
+      <c r="G207" s="8" t="s">
         <v>1069</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="J207" s="6" t="s">
+      <c r="J207" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K207" s="1" t="str">
@@ -24417,16 +24430,16 @@
       <c r="A208" s="4" t="s">
         <v>1071</v>
       </c>
-      <c r="B208" s="8" t="s">
+      <c r="B208" s="9" t="s">
         <v>1072</v>
       </c>
-      <c r="G208" s="7" t="s">
+      <c r="G208" s="8" t="s">
         <v>1073</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="J208" s="6" t="s">
+      <c r="J208" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K208" s="1" t="str">
@@ -24446,16 +24459,16 @@
       <c r="A209" s="4" t="s">
         <v>1075</v>
       </c>
-      <c r="B209" s="8" t="s">
+      <c r="B209" s="9" t="s">
         <v>1076</v>
       </c>
-      <c r="G209" s="7" t="s">
+      <c r="G209" s="8" t="s">
         <v>1077</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="J209" s="6" t="s">
+      <c r="J209" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K209" s="1" t="str">
@@ -24475,16 +24488,16 @@
       <c r="A210" s="4" t="s">
         <v>1079</v>
       </c>
-      <c r="B210" s="8" t="s">
+      <c r="B210" s="9" t="s">
         <v>1080</v>
       </c>
-      <c r="G210" s="7" t="s">
+      <c r="G210" s="8" t="s">
         <v>1081</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="J210" s="6" t="s">
+      <c r="J210" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K210" s="1" t="str">
@@ -24504,16 +24517,16 @@
       <c r="A211" s="4" t="s">
         <v>1083</v>
       </c>
-      <c r="B211" s="8" t="s">
+      <c r="B211" s="9" t="s">
         <v>1084</v>
       </c>
-      <c r="G211" s="7" t="s">
+      <c r="G211" s="8" t="s">
         <v>1085</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="J211" s="6" t="s">
+      <c r="J211" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K211" s="1" t="str">
@@ -24533,16 +24546,16 @@
       <c r="A212" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="G212" s="7" t="s">
+      <c r="G212" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="I212" s="9" t="s">
+      <c r="I212" s="11" t="s">
         <v>1090</v>
       </c>
-      <c r="J212" s="9" t="s">
+      <c r="J212" s="11" t="s">
         <v>731</v>
       </c>
       <c r="K212" s="1" t="str">
@@ -24562,16 +24575,16 @@
       <c r="A213" s="4" t="s">
         <v>1091</v>
       </c>
-      <c r="B213" s="8" t="s">
+      <c r="B213" s="9" t="s">
         <v>1092</v>
       </c>
-      <c r="G213" s="7" t="s">
+      <c r="G213" s="8" t="s">
         <v>1093</v>
       </c>
-      <c r="I213" s="9" t="s">
+      <c r="I213" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="J213" s="6" t="s">
+      <c r="J213" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K213" s="1" t="str">
@@ -24591,16 +24604,16 @@
       <c r="A214" s="4" t="s">
         <v>1095</v>
       </c>
-      <c r="B214" s="8" t="s">
+      <c r="B214" s="9" t="s">
         <v>1096</v>
       </c>
-      <c r="G214" s="7" t="s">
+      <c r="G214" s="8" t="s">
         <v>1097</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="J214" s="6" t="s">
+      <c r="J214" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K214" s="1" t="str">
@@ -24620,13 +24633,13 @@
       <c r="A215" s="4" t="s">
         <v>1099</v>
       </c>
-      <c r="B215" s="8" t="s">
+      <c r="B215" s="9" t="s">
         <v>1100</v>
       </c>
-      <c r="G215" s="7" t="s">
+      <c r="G215" s="8" t="s">
         <v>1101</v>
       </c>
-      <c r="I215" s="9" t="s">
+      <c r="I215" s="11" t="s">
         <v>1102</v>
       </c>
       <c r="O215" s="3"/>
@@ -24635,16 +24648,16 @@
       <c r="A216" s="4" t="s">
         <v>1103</v>
       </c>
-      <c r="B216" s="8" t="s">
+      <c r="B216" s="9" t="s">
         <v>1104</v>
       </c>
-      <c r="G216" s="7" t="s">
+      <c r="G216" s="8" t="s">
         <v>1105</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="J216" s="6" t="s">
+      <c r="J216" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K216" s="1" t="str">
@@ -24663,16 +24676,16 @@
       <c r="A217" s="4" t="s">
         <v>1107</v>
       </c>
-      <c r="B217" s="8" t="s">
+      <c r="B217" s="9" t="s">
         <v>1108</v>
       </c>
-      <c r="G217" s="7" t="s">
+      <c r="G217" s="8" t="s">
         <v>1109</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="J217" s="6" t="s">
+      <c r="J217" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K217" s="1" t="str">
@@ -24691,16 +24704,16 @@
       <c r="A218" s="4" t="s">
         <v>1111</v>
       </c>
-      <c r="B218" s="8" t="s">
+      <c r="B218" s="9" t="s">
         <v>1112</v>
       </c>
-      <c r="G218" s="7" t="s">
+      <c r="G218" s="8" t="s">
         <v>1113</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="J218" s="6" t="s">
+      <c r="J218" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K218" s="1" t="str">
@@ -24719,16 +24732,16 @@
       <c r="A219" s="4" t="s">
         <v>1115</v>
       </c>
-      <c r="B219" s="8" t="s">
+      <c r="B219" s="9" t="s">
         <v>1116</v>
       </c>
-      <c r="G219" s="7" t="s">
+      <c r="G219" s="8" t="s">
         <v>1117</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="J219" s="6" t="s">
+      <c r="J219" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K219" s="1" t="str">
@@ -24747,16 +24760,16 @@
       <c r="A220" s="4" t="s">
         <v>1119</v>
       </c>
-      <c r="B220" s="8" t="s">
+      <c r="B220" s="9" t="s">
         <v>1120</v>
       </c>
-      <c r="G220" s="7" t="s">
+      <c r="G220" s="8" t="s">
         <v>1121</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="J220" s="6" t="s">
+      <c r="J220" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K220" s="1" t="str">
@@ -24775,16 +24788,16 @@
       <c r="A221" s="4" t="s">
         <v>1123</v>
       </c>
-      <c r="B221" s="8" t="s">
+      <c r="B221" s="9" t="s">
         <v>1124</v>
       </c>
-      <c r="G221" s="7" t="s">
+      <c r="G221" s="8" t="s">
         <v>1125</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="J221" s="6" t="s">
+      <c r="J221" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K221" s="1" t="str">
@@ -24803,16 +24816,16 @@
       <c r="A222" s="4" t="s">
         <v>1127</v>
       </c>
-      <c r="B222" s="8" t="s">
+      <c r="B222" s="9" t="s">
         <v>1128</v>
       </c>
-      <c r="G222" s="7" t="s">
+      <c r="G222" s="8" t="s">
         <v>1129</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="J222" s="6" t="s">
+      <c r="J222" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K222" s="1" t="str">
@@ -24831,16 +24844,16 @@
       <c r="A223" s="4" t="s">
         <v>1131</v>
       </c>
-      <c r="B223" s="8" t="s">
+      <c r="B223" s="9" t="s">
         <v>1132</v>
       </c>
-      <c r="G223" s="7" t="s">
+      <c r="G223" s="8" t="s">
         <v>1133</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="J223" s="6" t="s">
+      <c r="J223" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K223" s="1" t="str">
@@ -24859,16 +24872,16 @@
       <c r="A224" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="B224" s="8" t="s">
+      <c r="B224" s="9" t="s">
         <v>1136</v>
       </c>
-      <c r="G224" s="7" t="s">
+      <c r="G224" s="8" t="s">
         <v>1137</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="J224" s="6" t="s">
+      <c r="J224" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K224" s="1" t="str">
@@ -24884,7 +24897,7 @@
       <c r="O224" s="3"/>
     </row>
     <row r="225" ht="14.25" customHeight="1">
-      <c r="A225" s="10" t="s">
+      <c r="A225" s="13" t="s">
         <v>1139</v>
       </c>
       <c r="B225" s="1" t="s">
@@ -24896,13 +24909,13 @@
       <c r="E225" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="G225" s="7" t="s">
+      <c r="G225" s="8" t="s">
         <v>1143</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="J225" s="6" t="s">
+      <c r="J225" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K225" s="1" t="str">
@@ -24918,7 +24931,7 @@
       <c r="O225" s="3"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="10" t="s">
+      <c r="A226" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B226" s="1" t="s">
@@ -24927,13 +24940,13 @@
       <c r="E226" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="G226" s="7" t="s">
+      <c r="G226" s="8" t="s">
         <v>1148</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="J226" s="6" t="s">
+      <c r="J226" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K226" s="1" t="str">
@@ -24949,7 +24962,7 @@
       <c r="O226" s="3"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
-      <c r="A227" s="10" t="s">
+      <c r="A227" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B227" s="1" t="s">
@@ -24958,13 +24971,13 @@
       <c r="E227" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="G227" s="7" t="s">
+      <c r="G227" s="8" t="s">
         <v>1152</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="J227" s="6" t="s">
+      <c r="J227" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K227" s="1" t="str">
@@ -24980,7 +24993,7 @@
       <c r="O227" s="3"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c r="A228" s="10" t="s">
+      <c r="A228" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B228" s="1" t="s">
@@ -24989,13 +25002,13 @@
       <c r="E228" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="G228" s="7" t="s">
+      <c r="G228" s="8" t="s">
         <v>1156</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="J228" s="6" t="s">
+      <c r="J228" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K228" s="1" t="str">
@@ -25011,7 +25024,7 @@
       <c r="O228" s="3"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="10" t="s">
+      <c r="A229" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B229" s="1" t="s">
@@ -25020,13 +25033,13 @@
       <c r="E229" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="G229" s="7" t="s">
+      <c r="G229" s="8" t="s">
         <v>1160</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="J229" s="6" t="s">
+      <c r="J229" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K229" s="1" t="str">
@@ -25042,7 +25055,7 @@
       <c r="O229" s="3"/>
     </row>
     <row r="230" ht="14.25" customHeight="1">
-      <c r="A230" s="10" t="s">
+      <c r="A230" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B230" s="1" t="s">
@@ -25051,13 +25064,13 @@
       <c r="E230" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="G230" s="7" t="s">
+      <c r="G230" s="8" t="s">
         <v>1164</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="J230" s="6" t="s">
+      <c r="J230" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K230" s="1" t="str">
@@ -25073,7 +25086,7 @@
       <c r="O230" s="3"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
-      <c r="A231" s="10" t="s">
+      <c r="A231" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B231" s="1" t="s">
@@ -25082,13 +25095,13 @@
       <c r="E231" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="G231" s="7" t="s">
+      <c r="G231" s="8" t="s">
         <v>1167</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="J231" s="6" t="s">
+      <c r="J231" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K231" s="1" t="str">
@@ -25104,7 +25117,7 @@
       <c r="O231" s="3"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c r="A232" s="10" t="s">
+      <c r="A232" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B232" s="1" t="s">
@@ -25113,13 +25126,13 @@
       <c r="E232" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="G232" s="7" t="s">
+      <c r="G232" s="8" t="s">
         <v>1171</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="J232" s="6" t="s">
+      <c r="J232" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K232" s="1" t="str">
@@ -25135,7 +25148,7 @@
       <c r="O232" s="3"/>
     </row>
     <row r="233" ht="14.25" customHeight="1">
-      <c r="A233" s="10" t="s">
+      <c r="A233" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B233" s="1" t="s">
@@ -25144,13 +25157,13 @@
       <c r="E233" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="G233" s="7" t="s">
+      <c r="G233" s="8" t="s">
         <v>1175</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="J233" s="6" t="s">
+      <c r="J233" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K233" s="1" t="str">
@@ -25166,7 +25179,7 @@
       <c r="O233" s="3"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="10" t="s">
+      <c r="A234" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B234" s="1" t="s">
@@ -25175,13 +25188,13 @@
       <c r="E234" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="G234" s="7" t="s">
+      <c r="G234" s="8" t="s">
         <v>1179</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="J234" s="6" t="s">
+      <c r="J234" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K234" s="1" t="str">
@@ -25197,7 +25210,7 @@
       <c r="O234" s="3"/>
     </row>
     <row r="235" ht="14.25" customHeight="1">
-      <c r="A235" s="10" t="s">
+      <c r="A235" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B235" s="1" t="s">
@@ -25206,13 +25219,13 @@
       <c r="E235" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="G235" s="7" t="s">
+      <c r="G235" s="8" t="s">
         <v>1183</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="J235" s="6" t="s">
+      <c r="J235" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K235" s="1" t="str">
@@ -25228,7 +25241,7 @@
       <c r="O235" s="3"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="10" t="s">
+      <c r="A236" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B236" s="1" t="s">
@@ -25237,13 +25250,13 @@
       <c r="E236" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="G236" s="7" t="s">
+      <c r="G236" s="8" t="s">
         <v>1187</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="J236" s="6" t="s">
+      <c r="J236" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K236" s="1" t="str">
@@ -25259,7 +25272,7 @@
       <c r="O236" s="3"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
-      <c r="A237" s="10" t="s">
+      <c r="A237" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B237" s="1" t="s">
@@ -25268,13 +25281,13 @@
       <c r="E237" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="G237" s="7" t="s">
+      <c r="G237" s="8" t="s">
         <v>1191</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="J237" s="6" t="s">
+      <c r="J237" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K237" s="1" t="str">
@@ -25290,7 +25303,7 @@
       <c r="O237" s="3"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="10" t="s">
+      <c r="A238" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B238" s="1" t="s">
@@ -25299,13 +25312,13 @@
       <c r="E238" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="G238" s="7" t="s">
+      <c r="G238" s="8" t="s">
         <v>1194</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="J238" s="6" t="s">
+      <c r="J238" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K238" s="1" t="str">
@@ -25321,7 +25334,7 @@
       <c r="O238" s="3"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c r="A239" s="10" t="s">
+      <c r="A239" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B239" s="1" t="s">
@@ -25330,13 +25343,13 @@
       <c r="E239" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="G239" s="7" t="s">
+      <c r="G239" s="8" t="s">
         <v>1197</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="J239" s="6" t="s">
+      <c r="J239" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K239" s="1" t="str">
@@ -25352,7 +25365,7 @@
       <c r="O239" s="3"/>
     </row>
     <row r="240" ht="14.25" customHeight="1">
-      <c r="A240" s="10" t="s">
+      <c r="A240" s="13" t="s">
         <v>1145</v>
       </c>
       <c r="B240" s="1" t="s">
@@ -25361,13 +25374,13 @@
       <c r="E240" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="G240" s="7" t="s">
+      <c r="G240" s="8" t="s">
         <v>1201</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="J240" s="6" t="s">
+      <c r="J240" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K240" s="1" t="str">
@@ -25383,7 +25396,7 @@
       <c r="O240" s="3"/>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c r="A241" s="10" t="s">
+      <c r="A241" s="13" t="s">
         <v>1203</v>
       </c>
       <c r="B241" s="1" t="s">
@@ -25392,13 +25405,13 @@
       <c r="E241" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G241" s="7" t="s">
+      <c r="G241" s="8" t="s">
         <v>1206</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="J241" s="6" t="s">
+      <c r="J241" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K241" s="1" t="str">
@@ -25414,7 +25427,7 @@
       <c r="O241" s="3"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
-      <c r="A242" s="10" t="s">
+      <c r="A242" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="B242" s="1" t="s">
@@ -25423,13 +25436,13 @@
       <c r="E242" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="G242" s="7" t="s">
+      <c r="G242" s="8" t="s">
         <v>1211</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="J242" s="6" t="s">
+      <c r="J242" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K242" s="1" t="str">
@@ -25445,7 +25458,7 @@
       <c r="O242" s="3"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="10" t="s">
+      <c r="A243" s="13" t="s">
         <v>1213</v>
       </c>
       <c r="B243" s="1" t="s">
@@ -25454,13 +25467,13 @@
       <c r="E243" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="G243" s="7" t="s">
+      <c r="G243" s="8" t="s">
         <v>1216</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="J243" s="6" t="s">
+      <c r="J243" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K243" s="1" t="str">
@@ -25476,7 +25489,7 @@
       <c r="O243" s="3"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="10" t="s">
+      <c r="A244" s="13" t="s">
         <v>1218</v>
       </c>
       <c r="B244" s="1" t="s">
@@ -25485,13 +25498,13 @@
       <c r="E244" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="G244" s="7" t="s">
+      <c r="G244" s="8" t="s">
         <v>1221</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="J244" s="6" t="s">
+      <c r="J244" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K244" s="1" t="str">
@@ -25507,7 +25520,7 @@
       <c r="O244" s="3"/>
     </row>
     <row r="245" ht="14.25" customHeight="1">
-      <c r="A245" s="10" t="s">
+      <c r="A245" s="13" t="s">
         <v>1223</v>
       </c>
       <c r="B245" s="1" t="s">
@@ -25516,13 +25529,13 @@
       <c r="E245" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="G245" s="7" t="s">
+      <c r="G245" s="8" t="s">
         <v>1226</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="J245" s="6" t="s">
+      <c r="J245" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K245" s="1" t="str">
@@ -25538,7 +25551,7 @@
       <c r="O245" s="3"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
-      <c r="A246" s="10" t="s">
+      <c r="A246" s="13" t="s">
         <v>1228</v>
       </c>
       <c r="B246" s="1" t="s">
@@ -25547,13 +25560,13 @@
       <c r="E246" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="G246" s="7" t="s">
+      <c r="G246" s="8" t="s">
         <v>1231</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="J246" s="6" t="s">
+      <c r="J246" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K246" s="1" t="str">
@@ -25569,7 +25582,7 @@
       <c r="O246" s="3"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="10" t="s">
+      <c r="A247" s="13" t="s">
         <v>1233</v>
       </c>
       <c r="B247" s="1" t="s">
@@ -25578,13 +25591,13 @@
       <c r="E247" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="G247" s="7" t="s">
+      <c r="G247" s="8" t="s">
         <v>1236</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="J247" s="6" t="s">
+      <c r="J247" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K247" s="1" t="str">
@@ -25600,7 +25613,7 @@
       <c r="O247" s="3"/>
     </row>
     <row r="248" ht="14.25" customHeight="1">
-      <c r="A248" s="10" t="s">
+      <c r="A248" s="13" t="s">
         <v>1238</v>
       </c>
       <c r="B248" s="1" t="s">
@@ -25609,13 +25622,13 @@
       <c r="E248" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="G248" s="7" t="s">
+      <c r="G248" s="8" t="s">
         <v>1241</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="J248" s="6" t="s">
+      <c r="J248" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K248" s="1" t="str">
@@ -25631,7 +25644,7 @@
       <c r="O248" s="3"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="10" t="s">
+      <c r="A249" s="13" t="s">
         <v>1243</v>
       </c>
       <c r="B249" s="1" t="s">
@@ -25640,13 +25653,13 @@
       <c r="E249" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="G249" s="7" t="s">
+      <c r="G249" s="8" t="s">
         <v>1245</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="J249" s="6" t="s">
+      <c r="J249" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K249" s="1" t="str">
@@ -25662,7 +25675,7 @@
       <c r="O249" s="3"/>
     </row>
     <row r="250" ht="14.25" customHeight="1">
-      <c r="A250" s="10" t="s">
+      <c r="A250" s="13" t="s">
         <v>1247</v>
       </c>
       <c r="B250" s="1" t="s">
@@ -25671,13 +25684,13 @@
       <c r="E250" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="G250" s="7" t="s">
+      <c r="G250" s="8" t="s">
         <v>1249</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="J250" s="6" t="s">
+      <c r="J250" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K250" s="1" t="str">
@@ -25693,7 +25706,7 @@
       <c r="O250" s="3"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="10" t="s">
+      <c r="A251" s="13" t="s">
         <v>1251</v>
       </c>
       <c r="B251" s="1" t="s">
@@ -25702,13 +25715,13 @@
       <c r="E251" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G251" s="7" t="s">
+      <c r="G251" s="8" t="s">
         <v>1253</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="J251" s="6" t="s">
+      <c r="J251" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K251" s="1" t="str">
@@ -25724,7 +25737,7 @@
       <c r="O251" s="3"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="10" t="s">
+      <c r="A252" s="13" t="s">
         <v>1255</v>
       </c>
       <c r="B252" s="1" t="s">
@@ -25733,13 +25746,13 @@
       <c r="E252" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="G252" s="7" t="s">
+      <c r="G252" s="8" t="s">
         <v>1258</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="J252" s="6" t="s">
+      <c r="J252" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K252" s="1" t="str">
@@ -25755,7 +25768,7 @@
       <c r="O252" s="3"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="10" t="s">
+      <c r="A253" s="13" t="s">
         <v>1260</v>
       </c>
       <c r="B253" s="1" t="s">
@@ -25764,13 +25777,13 @@
       <c r="E253" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="G253" s="7" t="s">
+      <c r="G253" s="8" t="s">
         <v>1263</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="J253" s="6" t="s">
+      <c r="J253" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K253" s="1" t="str">
@@ -25786,7 +25799,7 @@
       <c r="O253" s="3"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c r="A254" s="10" t="s">
+      <c r="A254" s="13" t="s">
         <v>1265</v>
       </c>
       <c r="B254" s="1" t="s">
@@ -25795,13 +25808,13 @@
       <c r="E254" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="G254" s="7" t="s">
+      <c r="G254" s="8" t="s">
         <v>1268</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="J254" s="6" t="s">
+      <c r="J254" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K254" s="1" t="str">
@@ -25817,7 +25830,7 @@
       <c r="O254" s="3"/>
     </row>
     <row r="255" ht="14.25" customHeight="1">
-      <c r="A255" s="10" t="s">
+      <c r="A255" s="13" t="s">
         <v>1270</v>
       </c>
       <c r="B255" s="1" t="s">
@@ -25826,13 +25839,13 @@
       <c r="E255" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="G255" s="7" t="s">
+      <c r="G255" s="8" t="s">
         <v>1273</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="J255" s="6" t="s">
+      <c r="J255" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K255" s="1" t="str">
@@ -25848,20 +25861,20 @@
       <c r="O255" s="3"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="10" t="s">
+      <c r="A256" s="13" t="s">
         <v>1275</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1276</v>
       </c>
       <c r="E256" s="1"/>
-      <c r="G256" s="7" t="s">
+      <c r="G256" s="8" t="s">
         <v>1277</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="J256" s="6" t="s">
+      <c r="J256" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K256" s="1" t="str">
@@ -25877,19 +25890,19 @@
       <c r="O256" s="3"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
-      <c r="A257" s="10" t="s">
+      <c r="A257" s="13" t="s">
         <v>1280</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="G257" s="7" t="s">
+      <c r="G257" s="8" t="s">
         <v>1282</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="J257" s="6" t="s">
+      <c r="J257" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K257" s="1" t="str">
@@ -25905,19 +25918,19 @@
       <c r="O257" s="3"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="10" t="s">
+      <c r="A258" s="13" t="s">
         <v>1284</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="G258" s="7" t="s">
+      <c r="G258" s="8" t="s">
         <v>1286</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="J258" s="6" t="s">
+      <c r="J258" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K258" s="1" t="str">
@@ -25933,19 +25946,19 @@
       <c r="O258" s="3"/>
     </row>
     <row r="259" ht="14.25" customHeight="1">
-      <c r="A259" s="10" t="s">
+      <c r="A259" s="13" t="s">
         <v>1288</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="G259" s="7" t="s">
+      <c r="G259" s="8" t="s">
         <v>1290</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="J259" s="6" t="s">
+      <c r="J259" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K259" s="1" t="str">
@@ -25961,19 +25974,19 @@
       <c r="O259" s="3"/>
     </row>
     <row r="260" ht="14.25" customHeight="1">
-      <c r="A260" s="10" t="s">
+      <c r="A260" s="13" t="s">
         <v>1292</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="G260" s="7" t="s">
+      <c r="G260" s="8" t="s">
         <v>1294</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="J260" s="6" t="s">
+      <c r="J260" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K260" s="1" t="str">
@@ -25989,19 +26002,19 @@
       <c r="O260" s="3"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="10" t="s">
+      <c r="A261" s="13" t="s">
         <v>1296</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="G261" s="7" t="s">
+      <c r="G261" s="8" t="s">
         <v>1298</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="J261" s="6" t="s">
+      <c r="J261" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K261" s="1" t="str">
@@ -26017,19 +26030,19 @@
       <c r="O261" s="3"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="10" t="s">
+      <c r="A262" s="13" t="s">
         <v>1300</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="G262" s="7" t="s">
+      <c r="G262" s="8" t="s">
         <v>1302</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="J262" s="6" t="s">
+      <c r="J262" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K262" s="1" t="str">
@@ -26045,19 +26058,19 @@
       <c r="O262" s="3"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c r="A263" s="10" t="s">
+      <c r="A263" s="13" t="s">
         <v>1304</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="G263" s="7" t="s">
+      <c r="G263" s="8" t="s">
         <v>1306</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="J263" s="6" t="s">
+      <c r="J263" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K263" s="1" t="str">
@@ -26073,19 +26086,19 @@
       <c r="O263" s="3"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="10" t="s">
+      <c r="A264" s="13" t="s">
         <v>1308</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="G264" s="7" t="s">
+      <c r="G264" s="8" t="s">
         <v>1310</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="J264" s="6" t="s">
+      <c r="J264" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K264" s="1" t="str">
@@ -26101,19 +26114,19 @@
       <c r="O264" s="3"/>
     </row>
     <row r="265" ht="14.25" customHeight="1">
-      <c r="A265" s="10" t="s">
+      <c r="A265" s="13" t="s">
         <v>1312</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="G265" s="7" t="s">
+      <c r="G265" s="8" t="s">
         <v>1314</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="J265" s="6" t="s">
+      <c r="J265" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K265" s="1" t="str">
@@ -26129,19 +26142,19 @@
       <c r="O265" s="3"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
-      <c r="A266" s="10" t="s">
+      <c r="A266" s="13" t="s">
         <v>1316</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="G266" s="7" t="s">
+      <c r="G266" s="8" t="s">
         <v>1318</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="J266" s="6" t="s">
+      <c r="J266" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K266" s="1" t="str">
@@ -26157,19 +26170,19 @@
       <c r="O266" s="3"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="10" t="s">
+      <c r="A267" s="13" t="s">
         <v>1320</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="G267" s="7" t="s">
+      <c r="G267" s="8" t="s">
         <v>1322</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="J267" s="6" t="s">
+      <c r="J267" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K267" s="1" t="str">
@@ -26185,19 +26198,19 @@
       <c r="O267" s="3"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c r="A268" s="10" t="s">
+      <c r="A268" s="13" t="s">
         <v>1324</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="G268" s="7" t="s">
+      <c r="G268" s="8" t="s">
         <v>1326</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="J268" s="6" t="s">
+      <c r="J268" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K268" s="1" t="str">
@@ -26213,19 +26226,19 @@
       <c r="O268" s="3"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="10" t="s">
+      <c r="A269" s="13" t="s">
         <v>1328</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="G269" s="7" t="s">
+      <c r="G269" s="8" t="s">
         <v>1330</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="J269" s="6" t="s">
+      <c r="J269" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K269" s="1" t="str">
@@ -26241,19 +26254,19 @@
       <c r="O269" s="3"/>
     </row>
     <row r="270" ht="14.25" customHeight="1">
-      <c r="A270" s="10" t="s">
+      <c r="A270" s="13" t="s">
         <v>1332</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="G270" s="7" t="s">
+      <c r="G270" s="8" t="s">
         <v>1334</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="J270" s="6" t="s">
+      <c r="J270" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K270" s="1" t="str">
@@ -26269,19 +26282,19 @@
       <c r="O270" s="3"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="10" t="s">
+      <c r="A271" s="13" t="s">
         <v>1336</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>1337</v>
       </c>
-      <c r="G271" s="7" t="s">
+      <c r="G271" s="8" t="s">
         <v>1338</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="J271" s="6" t="s">
+      <c r="J271" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K271" s="1" t="str">
@@ -26297,19 +26310,19 @@
       <c r="O271" s="3"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c r="A272" s="10" t="s">
+      <c r="A272" s="13" t="s">
         <v>1340</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="G272" s="7" t="s">
+      <c r="G272" s="8" t="s">
         <v>1342</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="J272" s="6" t="s">
+      <c r="J272" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K272" s="1" t="str">
@@ -26326,19 +26339,19 @@
       <c r="O272" s="3"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="10" t="s">
+      <c r="A273" s="13" t="s">
         <v>1344</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="G273" s="7" t="s">
+      <c r="G273" s="12" t="s">
         <v>1346</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="J273" s="6" t="s">
+      <c r="J273" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K273" s="1" t="str">
@@ -26355,19 +26368,19 @@
       <c r="O273" s="3"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
-      <c r="A274" s="10" t="s">
+      <c r="A274" s="13" t="s">
         <v>1348</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="G274" s="7" t="s">
+      <c r="G274" s="12" t="s">
         <v>1350</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="J274" s="6" t="s">
+      <c r="J274" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K274" s="1" t="str">
@@ -26384,19 +26397,19 @@
       <c r="O274" s="3"/>
     </row>
     <row r="275" ht="14.25" customHeight="1">
-      <c r="A275" s="10" t="s">
+      <c r="A275" s="13" t="s">
         <v>1352</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>1353</v>
       </c>
-      <c r="G275" s="7" t="s">
+      <c r="G275" s="8" t="s">
         <v>1354</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="J275" s="6" t="s">
+      <c r="J275" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K275" s="1" t="str">
@@ -26413,19 +26426,19 @@
       <c r="O275" s="3"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
-      <c r="A276" s="10" t="s">
+      <c r="A276" s="13" t="s">
         <v>1356</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="G276" s="7" t="s">
+      <c r="G276" s="8" t="s">
         <v>1358</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="J276" s="6" t="s">
+      <c r="J276" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K276" s="1" t="str">
@@ -26442,19 +26455,19 @@
       <c r="O276" s="3"/>
     </row>
     <row r="277" ht="14.25" customHeight="1">
-      <c r="A277" s="10" t="s">
+      <c r="A277" s="13" t="s">
         <v>1360</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="G277" s="7" t="s">
+      <c r="G277" s="12" t="s">
         <v>1362</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="J277" s="6" t="s">
+      <c r="J277" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K277" s="1" t="str">
@@ -26471,19 +26484,19 @@
       <c r="O277" s="3"/>
     </row>
     <row r="278" ht="14.25" customHeight="1">
-      <c r="A278" s="10" t="s">
+      <c r="A278" s="13" t="s">
         <v>1364</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="G278" s="7" t="s">
+      <c r="G278" s="8" t="s">
         <v>1366</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="J278" s="6" t="s">
+      <c r="J278" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K278" s="1" t="str">
@@ -26499,19 +26512,19 @@
       <c r="O278" s="3"/>
     </row>
     <row r="279" ht="14.25" customHeight="1">
-      <c r="A279" s="10" t="s">
+      <c r="A279" s="13" t="s">
         <v>1369</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="G279" s="7" t="s">
+      <c r="G279" s="12" t="s">
         <v>1371</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>1372</v>
       </c>
-      <c r="J279" s="6" t="s">
+      <c r="J279" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K279" s="1" t="str">
@@ -26527,19 +26540,19 @@
       <c r="O279" s="3"/>
     </row>
     <row r="280" ht="14.25" customHeight="1">
-      <c r="A280" s="10" t="s">
+      <c r="A280" s="13" t="s">
         <v>1373</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="G280" s="7" t="s">
+      <c r="G280" s="8" t="s">
         <v>1375</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="J280" s="6" t="s">
+      <c r="J280" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K280" s="1" t="str">
@@ -26555,19 +26568,19 @@
       <c r="O280" s="3"/>
     </row>
     <row r="281" ht="14.25" customHeight="1">
-      <c r="A281" s="10" t="s">
+      <c r="A281" s="13" t="s">
         <v>1377</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="G281" s="7" t="s">
+      <c r="G281" s="8" t="s">
         <v>1379</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="J281" s="6" t="s">
+      <c r="J281" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K281" s="1" t="str">
@@ -26583,19 +26596,19 @@
       <c r="O281" s="3"/>
     </row>
     <row r="282" ht="14.25" customHeight="1">
-      <c r="A282" s="10" t="s">
+      <c r="A282" s="13" t="s">
         <v>1381</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="G282" s="7" t="s">
+      <c r="G282" s="8" t="s">
         <v>1383</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="J282" s="6" t="s">
+      <c r="J282" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K282" s="1" t="str">
@@ -26611,19 +26624,19 @@
       <c r="O282" s="3"/>
     </row>
     <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="10" t="s">
+      <c r="A283" s="13" t="s">
         <v>1385</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="G283" s="7" t="s">
+      <c r="G283" s="8" t="s">
         <v>1387</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="J283" s="6" t="s">
+      <c r="J283" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K283" s="1" t="str">
@@ -26639,19 +26652,19 @@
       <c r="O283" s="3"/>
     </row>
     <row r="284" ht="14.25" customHeight="1">
-      <c r="A284" s="10" t="s">
+      <c r="A284" s="13" t="s">
         <v>1390</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="G284" s="7" t="s">
+      <c r="G284" s="8" t="s">
         <v>1392</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="J284" s="6" t="s">
+      <c r="J284" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K284" s="1" t="str">
@@ -26667,19 +26680,19 @@
       <c r="O284" s="3"/>
     </row>
     <row r="285" ht="14.25" customHeight="1">
-      <c r="A285" s="10" t="s">
+      <c r="A285" s="13" t="s">
         <v>1394</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="G285" s="7" t="s">
+      <c r="G285" s="8" t="s">
         <v>1396</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="J285" s="6" t="s">
+      <c r="J285" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K285" s="1" t="str">
@@ -26695,19 +26708,19 @@
       <c r="O285" s="3"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="10" t="s">
+      <c r="A286" s="13" t="s">
         <v>1398</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="G286" s="7" t="s">
+      <c r="G286" s="8" t="s">
         <v>1400</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="J286" s="6" t="s">
+      <c r="J286" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K286" s="1" t="str">
@@ -26729,13 +26742,13 @@
       <c r="B287" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="G287" s="7" t="s">
+      <c r="G287" s="8" t="s">
         <v>1404</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="J287" s="6" t="s">
+      <c r="J287" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K287" s="1" t="str">
@@ -26757,13 +26770,13 @@
       <c r="B288" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="G288" s="7" t="s">
+      <c r="G288" s="8" t="s">
         <v>1409</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="J288" s="6" t="s">
+      <c r="J288" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K288" s="1" t="str">
@@ -26785,13 +26798,13 @@
       <c r="B289" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="G289" s="7" t="s">
+      <c r="G289" s="14" t="s">
         <v>1413</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>1414</v>
       </c>
-      <c r="J289" s="6" t="s">
+      <c r="J289" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K289" s="1" t="str">
@@ -26813,13 +26826,13 @@
       <c r="B290" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="G290" s="7" t="s">
+      <c r="G290" s="8" t="s">
         <v>1417</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="J290" s="6" t="s">
+      <c r="J290" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K290" s="1" t="str">
@@ -26841,13 +26854,13 @@
       <c r="B291" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="G291" s="7" t="s">
+      <c r="G291" s="8" t="s">
         <v>1421</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="J291" s="6" t="s">
+      <c r="J291" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K291" s="1" t="str">
@@ -26869,13 +26882,13 @@
       <c r="B292" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="G292" s="7" t="s">
+      <c r="G292" s="8" t="s">
         <v>1425</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="J292" s="6" t="s">
+      <c r="J292" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K292" s="1" t="str">
@@ -26897,13 +26910,13 @@
       <c r="B293" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="G293" s="7" t="s">
+      <c r="G293" s="8" t="s">
         <v>1429</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="J293" s="6" t="s">
+      <c r="J293" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K293" s="1" t="str">
@@ -26925,13 +26938,13 @@
       <c r="B294" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="G294" s="7" t="s">
+      <c r="G294" s="8" t="s">
         <v>1433</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="J294" s="6" t="s">
+      <c r="J294" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K294" s="1" t="str">
@@ -26953,16 +26966,16 @@
       <c r="B295" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="C295" s="7" t="s">
+      <c r="C295" s="8" t="s">
         <v>1437</v>
       </c>
-      <c r="G295" s="7" t="s">
+      <c r="G295" s="8" t="s">
         <v>1438</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="J295" s="6" t="s">
+      <c r="J295" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K295" s="1" t="str">
@@ -26984,16 +26997,16 @@
       <c r="B296" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="C296" s="7" t="s">
+      <c r="C296" s="8" t="s">
         <v>1442</v>
       </c>
-      <c r="G296" s="7" t="s">
+      <c r="G296" s="8" t="s">
         <v>1443</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="J296" s="6" t="s">
+      <c r="J296" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K296" s="1" t="str">
@@ -27015,13 +27028,13 @@
       <c r="B297" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="G297" s="7" t="s">
+      <c r="G297" s="14" t="s">
         <v>1447</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="J297" s="6" t="s">
+      <c r="J297" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K297" s="1" t="str">
@@ -27043,13 +27056,13 @@
       <c r="B298" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="G298" s="7" t="s">
+      <c r="G298" s="8" t="s">
         <v>1451</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="J298" s="6" t="s">
+      <c r="J298" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K298" s="1" t="str">
@@ -27071,13 +27084,13 @@
       <c r="B299" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="G299" s="7" t="s">
+      <c r="G299" s="8" t="s">
         <v>1455</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="J299" s="6" t="s">
+      <c r="J299" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K299" s="1" t="str">
@@ -27099,13 +27112,13 @@
       <c r="B300" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="G300" s="7" t="s">
+      <c r="G300" s="8" t="s">
         <v>1459</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="J300" s="6" t="s">
+      <c r="J300" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K300" s="1" t="str">
@@ -27127,13 +27140,13 @@
       <c r="B301" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="G301" s="7" t="s">
+      <c r="G301" s="8" t="s">
         <v>1463</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="J301" s="6" t="s">
+      <c r="J301" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K301" s="1" t="str">
@@ -27155,13 +27168,13 @@
       <c r="B302" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="G302" s="7" t="s">
+      <c r="G302" s="8" t="s">
         <v>1467</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="J302" s="6" t="s">
+      <c r="J302" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K302" s="1" t="str">
@@ -27184,13 +27197,13 @@
       <c r="B303" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="G303" s="7" t="s">
+      <c r="G303" s="8" t="s">
         <v>1471</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="J303" s="6" t="s">
+      <c r="J303" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K303" s="1" t="str">
@@ -27213,13 +27226,13 @@
       <c r="B304" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="G304" s="7" t="s">
+      <c r="G304" s="8" t="s">
         <v>1475</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="J304" s="6" t="s">
+      <c r="J304" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K304" s="1" t="str">
@@ -27242,13 +27255,13 @@
       <c r="B305" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="G305" s="7" t="s">
+      <c r="G305" s="8" t="s">
         <v>1479</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="J305" s="6" t="s">
+      <c r="J305" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K305" s="1" t="str">
@@ -27277,7 +27290,7 @@
       <c r="I306" s="1" t="s">
         <v>1484</v>
       </c>
-      <c r="J306" s="6" t="s">
+      <c r="J306" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K306" s="1" t="str">
@@ -27305,7 +27318,7 @@
       <c r="I307" s="1" t="s">
         <v>1489</v>
       </c>
-      <c r="J307" s="6" t="s">
+      <c r="J307" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K307" s="1" t="str">
@@ -27333,7 +27346,7 @@
       <c r="I308" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="J308" s="6" t="s">
+      <c r="J308" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K308" s="1" t="str">
@@ -27361,7 +27374,7 @@
       <c r="I309" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="J309" s="6" t="s">
+      <c r="J309" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K309" s="1" t="str">
@@ -27389,7 +27402,7 @@
       <c r="I310" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="J310" s="6" t="s">
+      <c r="J310" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K310" s="1" t="str">
@@ -27417,7 +27430,7 @@
       <c r="I311" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="J311" s="6" t="s">
+      <c r="J311" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K311" s="1" t="str">
@@ -27445,7 +27458,7 @@
       <c r="I312" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="J312" s="6" t="s">
+      <c r="J312" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K312" s="1" t="str">
@@ -27473,7 +27486,7 @@
       <c r="I313" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="J313" s="6" t="s">
+      <c r="J313" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K313" s="1" t="str">
@@ -27501,7 +27514,7 @@
       <c r="I314" s="1" t="s">
         <v>1517</v>
       </c>
-      <c r="J314" s="6" t="s">
+      <c r="J314" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K314" s="1" t="str">
@@ -27529,7 +27542,7 @@
       <c r="I315" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="J315" s="6" t="s">
+      <c r="J315" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K315" s="1" t="str">
@@ -27554,10 +27567,10 @@
       <c r="G316" s="1" t="s">
         <v>1525</v>
       </c>
-      <c r="I316" s="9" t="s">
+      <c r="I316" s="11" t="s">
         <v>1526</v>
       </c>
-      <c r="J316" s="6" t="s">
+      <c r="J316" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K316" s="1" t="str">
@@ -27585,7 +27598,7 @@
       <c r="I317" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="J317" s="6" t="s">
+      <c r="J317" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K317" s="1" t="str">
@@ -27607,7 +27620,7 @@
       <c r="B318" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="C318" s="7" t="s">
+      <c r="C318" s="8" t="s">
         <v>1533</v>
       </c>
       <c r="G318" s="1" t="s">
@@ -27616,7 +27629,7 @@
       <c r="I318" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="J318" s="6" t="s">
+      <c r="J318" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K318" s="1" t="str">
@@ -27638,7 +27651,7 @@
       <c r="B319" s="1" t="s">
         <v>1538</v>
       </c>
-      <c r="C319" s="7" t="s">
+      <c r="C319" s="8" t="s">
         <v>1533</v>
       </c>
       <c r="G319" s="1" t="s">
@@ -27647,7 +27660,7 @@
       <c r="I319" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="J319" s="6" t="s">
+      <c r="J319" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K319" s="1" t="str">
@@ -27669,7 +27682,7 @@
       <c r="B320" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="C320" s="7" t="s">
+      <c r="C320" s="8" t="s">
         <v>1543</v>
       </c>
       <c r="G320" s="1" t="s">
@@ -27678,7 +27691,7 @@
       <c r="I320" s="1" t="s">
         <v>1545</v>
       </c>
-      <c r="J320" s="6" t="s">
+      <c r="J320" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K320" s="1" t="str">
@@ -27700,7 +27713,7 @@
       <c r="B321" s="1" t="s">
         <v>1547</v>
       </c>
-      <c r="C321" s="7" t="s">
+      <c r="C321" s="8" t="s">
         <v>1548</v>
       </c>
       <c r="G321" s="1" t="s">
@@ -27709,7 +27722,7 @@
       <c r="I321" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="J321" s="6" t="s">
+      <c r="J321" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K321" s="1" t="str">
@@ -27731,7 +27744,7 @@
       <c r="B322" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="C322" s="7" t="s">
+      <c r="C322" s="8" t="s">
         <v>1553</v>
       </c>
       <c r="G322" s="1" t="s">
@@ -27740,7 +27753,7 @@
       <c r="I322" s="1" t="s">
         <v>1555</v>
       </c>
-      <c r="J322" s="6" t="s">
+      <c r="J322" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K322" s="1" t="str">
@@ -27762,7 +27775,7 @@
       <c r="B323" s="1" t="s">
         <v>1557</v>
       </c>
-      <c r="C323" s="7" t="s">
+      <c r="C323" s="8" t="s">
         <v>1558</v>
       </c>
       <c r="G323" s="1" t="s">
@@ -27771,7 +27784,7 @@
       <c r="I323" s="1" t="s">
         <v>1560</v>
       </c>
-      <c r="J323" s="6" t="s">
+      <c r="J323" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K323" s="1" t="str">
@@ -27799,7 +27812,7 @@
       <c r="I324" s="1" t="s">
         <v>1564</v>
       </c>
-      <c r="J324" s="6" t="s">
+      <c r="J324" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K324" s="1" t="str">
@@ -27827,7 +27840,7 @@
       <c r="I325" s="1" t="s">
         <v>1568</v>
       </c>
-      <c r="J325" s="6" t="s">
+      <c r="J325" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K325" s="1" t="str">
@@ -27855,7 +27868,7 @@
       <c r="I326" s="1" t="s">
         <v>1572</v>
       </c>
-      <c r="J326" s="6" t="s">
+      <c r="J326" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K326" s="1" t="str">
@@ -27883,7 +27896,7 @@
       <c r="I327" s="1" t="s">
         <v>1576</v>
       </c>
-      <c r="J327" s="6" t="s">
+      <c r="J327" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K327" s="1" t="str">
@@ -27911,7 +27924,7 @@
       <c r="I328" s="1" t="s">
         <v>1580</v>
       </c>
-      <c r="J328" s="6" t="s">
+      <c r="J328" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K328" s="1" t="str">
@@ -27939,7 +27952,7 @@
       <c r="I329" s="1" t="s">
         <v>1584</v>
       </c>
-      <c r="J329" s="6" t="s">
+      <c r="J329" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K329" s="1" t="str">
@@ -27967,7 +27980,7 @@
       <c r="I330" s="1" t="s">
         <v>1588</v>
       </c>
-      <c r="J330" s="6" t="s">
+      <c r="J330" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K330" s="1" t="str">
@@ -27995,7 +28008,7 @@
       <c r="I331" s="1" t="s">
         <v>1592</v>
       </c>
-      <c r="J331" s="6" t="s">
+      <c r="J331" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K331" s="1" t="str">
@@ -28023,7 +28036,7 @@
       <c r="I332" s="1" t="s">
         <v>1596</v>
       </c>
-      <c r="J332" s="6" t="s">
+      <c r="J332" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K332" s="1" t="str">
@@ -28051,7 +28064,7 @@
       <c r="I333" s="1" t="s">
         <v>1600</v>
       </c>
-      <c r="J333" s="6" t="s">
+      <c r="J333" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K333" s="1" t="str">
@@ -28073,13 +28086,13 @@
       <c r="B334" s="1" t="s">
         <v>1602</v>
       </c>
-      <c r="G334" s="7" t="s">
+      <c r="G334" s="8" t="s">
         <v>1603</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>1604</v>
       </c>
-      <c r="J334" s="6" t="s">
+      <c r="J334" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K334" s="1" t="str">
@@ -28101,13 +28114,13 @@
       <c r="B335" s="1" t="s">
         <v>1606</v>
       </c>
-      <c r="G335" s="7" t="s">
+      <c r="G335" s="8" t="s">
         <v>1607</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>1608</v>
       </c>
-      <c r="J335" s="6" t="s">
+      <c r="J335" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K335" s="1" t="str">
@@ -28129,13 +28142,13 @@
       <c r="B336" s="1" t="s">
         <v>1610</v>
       </c>
-      <c r="G336" s="7" t="s">
+      <c r="G336" s="8" t="s">
         <v>1611</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>1612</v>
       </c>
-      <c r="J336" s="6" t="s">
+      <c r="J336" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K336" s="1" t="str">
@@ -28157,13 +28170,13 @@
       <c r="B337" s="1" t="s">
         <v>1614</v>
       </c>
-      <c r="G337" s="7" t="s">
+      <c r="G337" s="8" t="s">
         <v>1615</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="J337" s="6" t="s">
+      <c r="J337" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K337" s="1" t="str">
@@ -28191,7 +28204,7 @@
       <c r="I338" s="1" t="s">
         <v>1620</v>
       </c>
-      <c r="J338" s="6" t="s">
+      <c r="J338" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K338" s="1" t="str">
@@ -28219,7 +28232,7 @@
       <c r="I339" s="1" t="s">
         <v>1624</v>
       </c>
-      <c r="J339" s="6" t="s">
+      <c r="J339" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K339" s="1" t="str">
@@ -28241,13 +28254,13 @@
       <c r="B340" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="G340" s="7" t="s">
+      <c r="G340" s="8" t="s">
         <v>1627</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>1628</v>
       </c>
-      <c r="J340" s="6" t="s">
+      <c r="J340" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K340" s="1" t="str">
@@ -28269,13 +28282,13 @@
       <c r="B341" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="G341" s="7" t="s">
+      <c r="G341" s="8" t="s">
         <v>1631</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>1632</v>
       </c>
-      <c r="J341" s="6" t="s">
+      <c r="J341" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K341" s="1" t="str">
@@ -28297,13 +28310,13 @@
       <c r="B342" s="1" t="s">
         <v>1634</v>
       </c>
-      <c r="G342" s="7" t="s">
+      <c r="G342" s="8" t="s">
         <v>1635</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>1636</v>
       </c>
-      <c r="J342" s="6" t="s">
+      <c r="J342" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K342" s="1" t="str">
@@ -28325,13 +28338,13 @@
       <c r="B343" s="1" t="s">
         <v>1638</v>
       </c>
-      <c r="G343" s="7" t="s">
+      <c r="G343" s="8" t="s">
         <v>1639</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>1640</v>
       </c>
-      <c r="J343" s="6" t="s">
+      <c r="J343" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K343" s="1" t="str">
@@ -28353,13 +28366,13 @@
       <c r="B344" s="1" t="s">
         <v>1642</v>
       </c>
-      <c r="G344" s="7" t="s">
+      <c r="G344" s="8" t="s">
         <v>1643</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>1644</v>
       </c>
-      <c r="J344" s="6" t="s">
+      <c r="J344" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K344" s="1" t="str">
@@ -28381,13 +28394,13 @@
       <c r="B345" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="G345" s="7" t="s">
+      <c r="G345" s="8" t="s">
         <v>1647</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>1648</v>
       </c>
-      <c r="J345" s="6" t="s">
+      <c r="J345" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K345" s="1" t="str">
@@ -28409,13 +28422,13 @@
       <c r="B346" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="G346" s="7" t="s">
+      <c r="G346" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>1652</v>
       </c>
-      <c r="J346" s="6" t="s">
+      <c r="J346" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K346" s="1" t="str">
@@ -28437,13 +28450,13 @@
       <c r="B347" s="1" t="s">
         <v>1654</v>
       </c>
-      <c r="G347" s="7" t="s">
+      <c r="G347" s="8" t="s">
         <v>1655</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>1656</v>
       </c>
-      <c r="J347" s="6" t="s">
+      <c r="J347" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K347" s="1" t="str">
@@ -28465,13 +28478,13 @@
       <c r="B348" s="1" t="s">
         <v>1658</v>
       </c>
-      <c r="G348" s="7" t="s">
+      <c r="G348" s="8" t="s">
         <v>1659</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>1660</v>
       </c>
-      <c r="J348" s="6" t="s">
+      <c r="J348" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K348" s="1" t="str">
@@ -28493,13 +28506,13 @@
       <c r="B349" s="1" t="s">
         <v>1662</v>
       </c>
-      <c r="G349" s="7" t="s">
+      <c r="G349" s="8" t="s">
         <v>1663</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>1664</v>
       </c>
-      <c r="J349" s="6" t="s">
+      <c r="J349" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K349" s="1" t="str">
@@ -28521,13 +28534,13 @@
       <c r="B350" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="G350" s="7" t="s">
+      <c r="G350" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>1668</v>
       </c>
-      <c r="J350" s="6" t="s">
+      <c r="J350" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K350" s="1" t="str">
@@ -28549,13 +28562,13 @@
       <c r="B351" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="G351" s="7" t="s">
+      <c r="G351" s="8" t="s">
         <v>1670</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>1671</v>
       </c>
-      <c r="J351" s="6" t="s">
+      <c r="J351" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K351" s="1" t="str">
@@ -28578,13 +28591,13 @@
       <c r="B352" s="1" t="s">
         <v>1673</v>
       </c>
-      <c r="G352" s="7" t="s">
+      <c r="G352" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>1675</v>
       </c>
-      <c r="J352" s="6" t="s">
+      <c r="J352" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K352" s="1" t="str">
@@ -28607,13 +28620,13 @@
       <c r="B353" s="1" t="s">
         <v>1677</v>
       </c>
-      <c r="G353" s="7" t="s">
+      <c r="G353" s="8" t="s">
         <v>1678</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="J353" s="6" t="s">
+      <c r="J353" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K353" s="1" t="str">
@@ -28636,13 +28649,13 @@
       <c r="B354" s="1" t="s">
         <v>1681</v>
       </c>
-      <c r="G354" s="7" t="s">
+      <c r="G354" s="8" t="s">
         <v>1682</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>1683</v>
       </c>
-      <c r="J354" s="6" t="s">
+      <c r="J354" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K354" s="1" t="str">
@@ -28665,13 +28678,13 @@
       <c r="B355" s="1" t="s">
         <v>1685</v>
       </c>
-      <c r="G355" s="7" t="s">
+      <c r="G355" s="8" t="s">
         <v>1686</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>1687</v>
       </c>
-      <c r="J355" s="6" t="s">
+      <c r="J355" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K355" s="1" t="str">
@@ -28694,13 +28707,13 @@
       <c r="B356" s="1" t="s">
         <v>1689</v>
       </c>
-      <c r="G356" s="7" t="s">
+      <c r="G356" s="8" t="s">
         <v>1690</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="J356" s="6" t="s">
+      <c r="J356" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K356" s="1" t="str">
@@ -28723,13 +28736,13 @@
       <c r="B357" s="1" t="s">
         <v>1693</v>
       </c>
-      <c r="G357" s="7" t="s">
+      <c r="G357" s="8" t="s">
         <v>1694</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="J357" s="6" t="s">
+      <c r="J357" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K357" s="1" t="str">
@@ -28752,13 +28765,13 @@
       <c r="B358" s="1" t="s">
         <v>1697</v>
       </c>
-      <c r="G358" s="7" t="s">
+      <c r="G358" s="8" t="s">
         <v>1698</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>1699</v>
       </c>
-      <c r="J358" s="6" t="s">
+      <c r="J358" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K358" s="1" t="str">
@@ -28781,13 +28794,13 @@
       <c r="B359" s="1" t="s">
         <v>1701</v>
       </c>
-      <c r="G359" s="7" t="s">
+      <c r="G359" s="8" t="s">
         <v>1702</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="J359" s="6" t="s">
+      <c r="J359" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K359" s="1" t="str">
@@ -28810,13 +28823,13 @@
       <c r="B360" s="1" t="s">
         <v>1705</v>
       </c>
-      <c r="G360" s="7" t="s">
+      <c r="G360" s="8" t="s">
         <v>1706</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>1707</v>
       </c>
-      <c r="J360" s="6" t="s">
+      <c r="J360" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K360" s="1" t="str">
@@ -28839,13 +28852,13 @@
       <c r="B361" s="1" t="s">
         <v>1709</v>
       </c>
-      <c r="G361" s="7" t="s">
+      <c r="G361" s="8" t="s">
         <v>1710</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>1711</v>
       </c>
-      <c r="J361" s="6" t="s">
+      <c r="J361" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K361" s="1" t="str">
@@ -28874,7 +28887,7 @@
       <c r="I362" s="1" t="s">
         <v>1715</v>
       </c>
-      <c r="J362" s="6" t="s">
+      <c r="J362" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K362" s="1" t="str">
@@ -28902,7 +28915,7 @@
       <c r="I363" s="1" t="s">
         <v>1719</v>
       </c>
-      <c r="J363" s="6" t="s">
+      <c r="J363" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K363" s="1" t="str">
@@ -28930,7 +28943,7 @@
       <c r="I364" s="1" t="s">
         <v>1723</v>
       </c>
-      <c r="J364" s="6" t="s">
+      <c r="J364" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K364" s="1" t="str">
@@ -28958,7 +28971,7 @@
       <c r="I365" s="1" t="s">
         <v>1727</v>
       </c>
-      <c r="J365" s="6" t="s">
+      <c r="J365" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K365" s="1" t="str">
@@ -28980,13 +28993,13 @@
       <c r="B366" s="1" t="s">
         <v>1729</v>
       </c>
-      <c r="G366" s="7" t="s">
+      <c r="G366" s="8" t="s">
         <v>1730</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>1731</v>
       </c>
-      <c r="J366" s="6" t="s">
+      <c r="J366" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K366" s="1" t="str">
@@ -29008,13 +29021,13 @@
       <c r="B367" s="1" t="s">
         <v>1733</v>
       </c>
-      <c r="G367" s="7" t="s">
+      <c r="G367" s="8" t="s">
         <v>1734</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>1735</v>
       </c>
-      <c r="J367" s="6" t="s">
+      <c r="J367" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K367" s="1" t="str">
@@ -29036,13 +29049,13 @@
       <c r="B368" s="1" t="s">
         <v>1737</v>
       </c>
-      <c r="G368" s="7" t="s">
+      <c r="G368" s="8" t="s">
         <v>1738</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>1739</v>
       </c>
-      <c r="J368" s="6" t="s">
+      <c r="J368" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K368" s="1" t="str">
@@ -29064,13 +29077,13 @@
       <c r="B369" s="1" t="s">
         <v>1741</v>
       </c>
-      <c r="G369" s="7" t="s">
+      <c r="G369" s="8" t="s">
         <v>1742</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>1743</v>
       </c>
-      <c r="J369" s="6" t="s">
+      <c r="J369" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K369" s="1" t="str">
@@ -29092,13 +29105,13 @@
       <c r="B370" s="1" t="s">
         <v>1745</v>
       </c>
-      <c r="G370" s="7" t="s">
+      <c r="G370" s="8" t="s">
         <v>1746</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>1747</v>
       </c>
-      <c r="J370" s="6" t="s">
+      <c r="J370" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K370" s="1" t="str">
@@ -29120,13 +29133,13 @@
       <c r="B371" s="1" t="s">
         <v>1749</v>
       </c>
-      <c r="G371" s="7" t="s">
+      <c r="G371" s="8" t="s">
         <v>1750</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>1751</v>
       </c>
-      <c r="J371" s="6" t="s">
+      <c r="J371" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K371" s="1" t="str">
@@ -29148,13 +29161,13 @@
       <c r="B372" s="1" t="s">
         <v>1753</v>
       </c>
-      <c r="G372" s="7" t="s">
+      <c r="G372" s="8" t="s">
         <v>1754</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>1755</v>
       </c>
-      <c r="J372" s="6" t="s">
+      <c r="J372" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K372" s="1" t="str">
@@ -29176,13 +29189,13 @@
       <c r="B373" s="1" t="s">
         <v>1757</v>
       </c>
-      <c r="G373" s="7" t="s">
+      <c r="G373" s="8" t="s">
         <v>1758</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="J373" s="6" t="s">
+      <c r="J373" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K373" s="1" t="str">
@@ -29204,13 +29217,13 @@
       <c r="B374" s="1" t="s">
         <v>1761</v>
       </c>
-      <c r="G374" s="7" t="s">
+      <c r="G374" s="8" t="s">
         <v>1762</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>1763</v>
       </c>
-      <c r="J374" s="6" t="s">
+      <c r="J374" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K374" s="1" t="str">
@@ -29232,13 +29245,13 @@
       <c r="B375" s="1" t="s">
         <v>1765</v>
       </c>
-      <c r="G375" s="7" t="s">
+      <c r="G375" s="8" t="s">
         <v>1766</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>1767</v>
       </c>
-      <c r="J375" s="6" t="s">
+      <c r="J375" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K375" s="1" t="str">
@@ -29260,13 +29273,13 @@
       <c r="B376" s="1" t="s">
         <v>1769</v>
       </c>
-      <c r="G376" s="7" t="s">
+      <c r="G376" s="8" t="s">
         <v>1770</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>1771</v>
       </c>
-      <c r="J376" s="6" t="s">
+      <c r="J376" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K376" s="1" t="str">
@@ -29288,13 +29301,13 @@
       <c r="B377" s="1" t="s">
         <v>1773</v>
       </c>
-      <c r="G377" s="11" t="s">
+      <c r="G377" s="12" t="s">
         <v>1774</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>1775</v>
       </c>
-      <c r="J377" s="6" t="s">
+      <c r="J377" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K377" s="1" t="str">
@@ -29316,13 +29329,13 @@
       <c r="B378" s="1" t="s">
         <v>1777</v>
       </c>
-      <c r="G378" s="7" t="s">
+      <c r="G378" s="8" t="s">
         <v>1778</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>1779</v>
       </c>
-      <c r="J378" s="6" t="s">
+      <c r="J378" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K378" s="1" t="str">
@@ -29344,13 +29357,13 @@
       <c r="B379" s="1" t="s">
         <v>1781</v>
       </c>
-      <c r="G379" s="7" t="s">
+      <c r="G379" s="8" t="s">
         <v>1782</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>1783</v>
       </c>
-      <c r="J379" s="6" t="s">
+      <c r="J379" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K379" s="1" t="str">
@@ -29372,13 +29385,13 @@
       <c r="B380" s="1" t="s">
         <v>1785</v>
       </c>
-      <c r="G380" s="7" t="s">
+      <c r="G380" s="8" t="s">
         <v>1786</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>1787</v>
       </c>
-      <c r="J380" s="6" t="s">
+      <c r="J380" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K380" s="1" t="str">
@@ -29400,13 +29413,13 @@
       <c r="B381" s="1" t="s">
         <v>1789</v>
       </c>
-      <c r="G381" s="7" t="s">
+      <c r="G381" s="8" t="s">
         <v>1790</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>1791</v>
       </c>
-      <c r="J381" s="6" t="s">
+      <c r="J381" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K381" s="1" t="str">
@@ -29428,13 +29441,13 @@
       <c r="B382" s="1" t="s">
         <v>1793</v>
       </c>
-      <c r="G382" s="7" t="s">
+      <c r="G382" s="8" t="s">
         <v>1794</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>1795</v>
       </c>
-      <c r="J382" s="6" t="s">
+      <c r="J382" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K382" s="1" t="str">
@@ -29456,13 +29469,13 @@
       <c r="B383" s="1" t="s">
         <v>1797</v>
       </c>
-      <c r="G383" s="7" t="s">
+      <c r="G383" s="8" t="s">
         <v>1798</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>1799</v>
       </c>
-      <c r="J383" s="6" t="s">
+      <c r="J383" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K383" s="1" t="str">
@@ -29484,13 +29497,13 @@
       <c r="B384" s="1" t="s">
         <v>1801</v>
       </c>
-      <c r="G384" s="7" t="s">
+      <c r="G384" s="8" t="s">
         <v>1802</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>1803</v>
       </c>
-      <c r="J384" s="6" t="s">
+      <c r="J384" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K384" s="1" t="str">
@@ -29513,13 +29526,13 @@
       <c r="B385" s="1" t="s">
         <v>1805</v>
       </c>
-      <c r="G385" s="7" t="s">
+      <c r="G385" s="8" t="s">
         <v>1806</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>1807</v>
       </c>
-      <c r="J385" s="6" t="s">
+      <c r="J385" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K385" s="1" t="str">
@@ -29541,13 +29554,13 @@
       <c r="B386" s="1" t="s">
         <v>1810</v>
       </c>
-      <c r="G386" s="7" t="s">
+      <c r="G386" s="8" t="s">
         <v>1811</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>1812</v>
       </c>
-      <c r="J386" s="6" t="s">
+      <c r="J386" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K386" s="1" t="str">
@@ -29569,13 +29582,13 @@
       <c r="B387" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="G387" s="7" t="s">
+      <c r="G387" s="8" t="s">
         <v>1815</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>1816</v>
       </c>
-      <c r="J387" s="6" t="s">
+      <c r="J387" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K387" s="1" t="str">
@@ -29597,13 +29610,13 @@
       <c r="B388" s="1" t="s">
         <v>1818</v>
       </c>
-      <c r="G388" s="7" t="s">
+      <c r="G388" s="8" t="s">
         <v>1819</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>1820</v>
       </c>
-      <c r="J388" s="6" t="s">
+      <c r="J388" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K388" s="1" t="str">
@@ -29625,13 +29638,13 @@
       <c r="B389" s="1" t="s">
         <v>1822</v>
       </c>
-      <c r="G389" s="7" t="s">
+      <c r="G389" s="8" t="s">
         <v>1823</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>1824</v>
       </c>
-      <c r="J389" s="6" t="s">
+      <c r="J389" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K389" s="1" t="str">
@@ -29653,13 +29666,13 @@
       <c r="B390" s="1" t="s">
         <v>1826</v>
       </c>
-      <c r="G390" s="7" t="s">
+      <c r="G390" s="8" t="s">
         <v>1827</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>1828</v>
       </c>
-      <c r="J390" s="6" t="s">
+      <c r="J390" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K390" s="1" t="str">
@@ -29681,13 +29694,13 @@
       <c r="B391" s="1" t="s">
         <v>1830</v>
       </c>
-      <c r="G391" s="7" t="s">
+      <c r="G391" s="8" t="s">
         <v>1831</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="J391" s="6" t="s">
+      <c r="J391" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K391" s="1" t="str">
@@ -29709,13 +29722,13 @@
       <c r="B392" s="1" t="s">
         <v>1834</v>
       </c>
-      <c r="G392" s="7" t="s">
+      <c r="G392" s="8" t="s">
         <v>1835</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>1836</v>
       </c>
-      <c r="J392" s="6" t="s">
+      <c r="J392" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K392" s="1" t="str">
@@ -29737,13 +29750,13 @@
       <c r="B393" s="1" t="s">
         <v>1838</v>
       </c>
-      <c r="G393" s="7" t="s">
+      <c r="G393" s="8" t="s">
         <v>1839</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="J393" s="6" t="s">
+      <c r="J393" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K393" s="1" t="str">
@@ -29765,13 +29778,13 @@
       <c r="B394" s="1" t="s">
         <v>1843</v>
       </c>
-      <c r="G394" s="7" t="s">
+      <c r="G394" s="8" t="s">
         <v>1844</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>1845</v>
       </c>
-      <c r="J394" s="6" t="s">
+      <c r="J394" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K394" s="1" t="str">
@@ -29793,13 +29806,13 @@
       <c r="B395" s="1" t="s">
         <v>1847</v>
       </c>
-      <c r="G395" s="7" t="s">
+      <c r="G395" s="8" t="s">
         <v>1848</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>1849</v>
       </c>
-      <c r="J395" s="6" t="s">
+      <c r="J395" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K395" s="1" t="str">
@@ -29821,13 +29834,13 @@
       <c r="B396" s="1" t="s">
         <v>1851</v>
       </c>
-      <c r="G396" s="7" t="s">
+      <c r="G396" s="8" t="s">
         <v>1852</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>1853</v>
       </c>
-      <c r="J396" s="6" t="s">
+      <c r="J396" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K396" s="1" t="str">
@@ -29849,13 +29862,13 @@
       <c r="B397" s="1" t="s">
         <v>1855</v>
       </c>
-      <c r="G397" s="7" t="s">
+      <c r="G397" s="8" t="s">
         <v>1856</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>1857</v>
       </c>
-      <c r="J397" s="6" t="s">
+      <c r="J397" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K397" s="1" t="str">
@@ -29877,13 +29890,13 @@
       <c r="B398" s="1" t="s">
         <v>1859</v>
       </c>
-      <c r="G398" s="7" t="s">
+      <c r="G398" s="8" t="s">
         <v>1860</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>1861</v>
       </c>
-      <c r="J398" s="6" t="s">
+      <c r="J398" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K398" s="1" t="str">
@@ -29905,13 +29918,13 @@
       <c r="B399" s="1" t="s">
         <v>1863</v>
       </c>
-      <c r="G399" s="7" t="s">
+      <c r="G399" s="8" t="s">
         <v>1864</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>1865</v>
       </c>
-      <c r="J399" s="6" t="s">
+      <c r="J399" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K399" s="1" t="str">
@@ -29933,13 +29946,13 @@
       <c r="B400" s="1" t="s">
         <v>1868</v>
       </c>
-      <c r="G400" s="7" t="s">
+      <c r="G400" s="8" t="s">
         <v>1869</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>1870</v>
       </c>
-      <c r="J400" s="6" t="s">
+      <c r="J400" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K400" s="1" t="str">
@@ -29961,13 +29974,13 @@
       <c r="B401" s="1" t="s">
         <v>1872</v>
       </c>
-      <c r="G401" s="7" t="s">
+      <c r="G401" s="8" t="s">
         <v>1873</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>1874</v>
       </c>
-      <c r="J401" s="6" t="s">
+      <c r="J401" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K401" s="1" t="str">
@@ -29989,13 +30002,13 @@
       <c r="B402" s="1" t="s">
         <v>1876</v>
       </c>
-      <c r="G402" s="7" t="s">
+      <c r="G402" s="8" t="s">
         <v>1877</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>1878</v>
       </c>
-      <c r="J402" s="6" t="s">
+      <c r="J402" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K402" s="1" t="str">
@@ -30017,13 +30030,13 @@
       <c r="B403" s="1" t="s">
         <v>1880</v>
       </c>
-      <c r="G403" s="7" t="s">
+      <c r="G403" s="8" t="s">
         <v>1881</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>1882</v>
       </c>
-      <c r="J403" s="6" t="s">
+      <c r="J403" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K403" s="1" t="str">
@@ -30045,13 +30058,13 @@
       <c r="B404" s="1" t="s">
         <v>1884</v>
       </c>
-      <c r="G404" s="7" t="s">
+      <c r="G404" s="8" t="s">
         <v>1885</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>1886</v>
       </c>
-      <c r="J404" s="6" t="s">
+      <c r="J404" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K404" s="1" t="str">
@@ -30073,13 +30086,13 @@
       <c r="B405" s="1" t="s">
         <v>1888</v>
       </c>
-      <c r="G405" s="7" t="s">
+      <c r="G405" s="8" t="s">
         <v>1889</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>1890</v>
       </c>
-      <c r="J405" s="6" t="s">
+      <c r="J405" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K405" s="1" t="str">
@@ -30101,13 +30114,13 @@
       <c r="B406" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="G406" s="7" t="s">
+      <c r="G406" s="8" t="s">
         <v>1893</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>1894</v>
       </c>
-      <c r="J406" s="6" t="s">
+      <c r="J406" s="7" t="s">
         <v>731</v>
       </c>
       <c r="K406" s="1" t="str">
@@ -33026,406 +33039,406 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1895</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>1935.0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>1895</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>734</v>
       </c>
       <c r="D3" s="1">
         <v>1927.0</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>108</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>1895</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>739</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <v>1941.0</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>1895</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <v>1958.0</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>1895</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <v>1961.0</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>559</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>1895</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="8" t="s">
         <v>1895</v>
       </c>
     </row>

--- a/計画-事例集.xlsx
+++ b/計画-事例集.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="1896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3287" uniqueCount="1907">
   <si>
     <t>ジャンル</t>
   </si>
@@ -7657,7 +7657,7 @@
     <t>りえんと多摩平</t>
   </si>
   <si>
-    <t>豊かな自然に囲まれ,多世代が交流する団地型シェアハウスであり,キッチン・ラウンシ・テラスなどの共用部を中心に,良好なコミュニティが育まれることを意図している。家具付きの個室は, 3 室で 1 ュニットを構成し,プライノ ヾシ ー を確保しながら協同生活を送ることができる。</t>
+    <t>豊かな自然に囲まれ,多世代が交流する団地型シェアハウスであり,キッチン・ラウンシ・テラスなどの共用部を中心に,良好なコミュニティが育まれることを意図している。家具付きの個室は, 3 室で 1ユニットを構成し,プライバシーを確保しながら協同生活を送ることができる。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//07_41.png</t>
@@ -9719,7 +9719,7 @@
     <t>海の博物館</t>
   </si>
   <si>
-    <t>漁具(漁船・漁網など)の収蔵・展示・研究を目的に建設され,3 つの収蔵庫棟, 2 つの展示棟,研究管理棟からなる。収蔵庫棟が施設の特徴の一つで,重要文化財等を扱うため,性能,コスト,耐久性がきめ細かく検討され,船の保存等に必要な湿度維持のためのたたき土間の床や,アルカリ成分の影響を抑えるためのプレキャストコンクリ ー トの採用,塩害に対する瓦屋根の採用など,地域性を踏まえながら,「収蔵品のための空間」を実現している。展示棟は,構造用集成材を用いた立体木造トラス構法による間仕切壁のない大空間で,外装は,黒いタ ー ル状の塗装をかけた板張りで仕上げられている。</t>
+    <t>展示棟は,構造用集成材を用いた立体木造トラス構法による間仕切壁のない大空間で,外装は,黒いタ ー ル状の塗装をかけた板張りで仕上げられている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_03.png</t>
@@ -9995,7 +9995,7 @@
     <t>大阪府立近つ飛鳥博物館</t>
   </si>
   <si>
-    <t>史跡公園の「近っ飛鳥風土記の丘」に建つ人文科学系博物館。屋根全体を大階段の展望広場とし,その大階段を二分するスリット状のアプロ ー チが人 々 をエントランスに導くように計画されている。</t>
+    <t>屋根全体を大階段の展望広場とし,その大階段を二分するスリット状のアプロ ー チが人 々 をエントランスに導くように計画されている。</t>
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//11_09.png</t>
@@ -17176,6 +17176,39 @@
   </si>
   <si>
     <t>https://raw.github.com/huzixiaodao21-blip/architect-keikaku/main/images//24_08.png</t>
+  </si>
+  <si>
+    <t>25_予想問題</t>
+  </si>
+  <si>
+    <t>有明体操競技場</t>
+  </si>
+  <si>
+    <t>「張弦梁構造による約90mのスパン」「大会後に展示場へ転用する計画」「仮設客席の分離」</t>
+  </si>
+  <si>
+    <t>開成町役場</t>
+  </si>
+  <si>
+    <t>「国内初の新築Nearly ZEB庁舎」「放射空調」「地中熱（井水熱）利用」「基礎免震とRC・S混構造」</t>
+  </si>
+  <si>
+    <t>富山ガラス美術館</t>
+  </si>
+  <si>
+    <t>「立体的な開放感（スパイラル状の吹き抜け）」地場産業を意識した「異素材（アルミ・ガラス・木）の融合」</t>
+  </si>
+  <si>
+    <t>角川武蔵野ミュージアム</t>
+  </si>
+  <si>
+    <t>「本棚劇場（圧倒的な高天井空間）」「外殻構造」「約2万枚の花崗岩（御影石）」</t>
+  </si>
+  <si>
+    <t>渋谷スクランブルスクエア</t>
+  </si>
+  <si>
+    <t>「アーバン・コア（縦の動線処理）」「日本最大級の開放型展望空間（約2,500㎡」「最新の制振（震）デバイス」</t>
   </si>
   <si>
     <t>5_独立住宅</t>
@@ -24346,7 +24379,7 @@
       <c r="B205" s="9" t="s">
         <v>1060</v>
       </c>
-      <c r="G205" s="8" t="s">
+      <c r="G205" s="12" t="s">
         <v>1061</v>
       </c>
       <c r="I205" s="1" t="s">
@@ -25924,7 +25957,7 @@
       <c r="B258" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="G258" s="8" t="s">
+      <c r="G258" s="12" t="s">
         <v>1286</v>
       </c>
       <c r="I258" s="1" t="s">
@@ -26092,7 +26125,7 @@
       <c r="B264" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="G264" s="8" t="s">
+      <c r="G264" s="12" t="s">
         <v>1310</v>
       </c>
       <c r="I264" s="1" t="s">
@@ -30136,42 +30169,82 @@
       <c r="O406" s="3"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c r="A407" s="4"/>
-      <c r="B407" s="1"/>
+      <c r="A407" s="13" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B407" s="6" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G407" s="12" t="s">
+        <v>1897</v>
+      </c>
       <c r="J407" s="3"/>
       <c r="L407" s="3"/>
       <c r="M407" s="3"/>
       <c r="O407" s="3"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
-      <c r="B408" s="1"/>
+      <c r="A408" s="13" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G408" s="12" t="s">
+        <v>1899</v>
+      </c>
       <c r="J408" s="3"/>
       <c r="L408" s="3"/>
       <c r="M408" s="3"/>
       <c r="O408" s="3"/>
     </row>
     <row r="409" ht="14.25" customHeight="1">
-      <c r="B409" s="1"/>
+      <c r="A409" s="13" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B409" s="6" t="s">
+        <v>1900</v>
+      </c>
+      <c r="G409" s="12" t="s">
+        <v>1901</v>
+      </c>
       <c r="J409" s="3"/>
       <c r="L409" s="3"/>
       <c r="M409" s="3"/>
       <c r="O409" s="3"/>
     </row>
     <row r="410" ht="14.25" customHeight="1">
-      <c r="B410" s="1"/>
+      <c r="A410" s="13" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B410" s="6" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G410" s="12" t="s">
+        <v>1903</v>
+      </c>
       <c r="J410" s="3"/>
       <c r="L410" s="3"/>
       <c r="M410" s="3"/>
       <c r="O410" s="3"/>
     </row>
     <row r="411" ht="14.25" customHeight="1">
-      <c r="B411" s="1"/>
+      <c r="A411" s="13" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B411" s="6" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G411" s="12" t="s">
+        <v>1905</v>
+      </c>
       <c r="J411" s="3"/>
       <c r="L411" s="3"/>
       <c r="M411" s="3"/>
       <c r="O411" s="3"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
+      <c r="A412" s="13"/>
       <c r="B412" s="1"/>
       <c r="J412" s="3"/>
       <c r="L412" s="3"/>
@@ -33069,7 +33142,7 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>726</v>
@@ -33095,7 +33168,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>733</v>
@@ -33121,7 +33194,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>739</v>
@@ -33147,7 +33220,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>745</v>
@@ -33173,7 +33246,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>751</v>
@@ -33199,247 +33272,247 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>1895</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1"/>
